--- a/PVA second supplier initiative/PVA_Second_Supplier_Leadership_Model.xlsx
+++ b/PVA second supplier initiative/PVA_Second_Supplier_Leadership_Model.xlsx
@@ -20,18 +20,20 @@
     <definedName name="LbWk">Inputs!$C$8</definedName>
     <definedName name="Weeks">Inputs!$C$9</definedName>
     <definedName name="Growth">Inputs!$C$10</definedName>
-    <definedName name="Share">Inputs!$C$11</definedName>
-    <definedName name="WarmShare">Inputs!$C$12</definedName>
-    <definedName name="PCIlo">Inputs!$C$13</definedName>
-    <definedName name="PCImid">Inputs!$C$14</definedName>
-    <definedName name="PCIhi">Inputs!$C$15</definedName>
-    <definedName name="MktLo">Inputs!$C$16</definedName>
-    <definedName name="MktBase">Inputs!$C$17</definedName>
-    <definedName name="MktHi">Inputs!$C$18</definedName>
-    <definedName name="CJBlb">Inputs!$C$19</definedName>
-    <definedName name="QualCost">Inputs!$C$20</definedName>
-    <definedName name="Pdis">Inputs!$C$21</definedName>
-    <definedName name="Dcost">Inputs!$C$22</definedName>
+    <definedName name="MinDrumsWk">Inputs!$C$11</definedName>
+    <definedName name="MinShare">Inputs!$C$12</definedName>
+    <definedName name="Share">Inputs!$C$13</definedName>
+    <definedName name="EffShare">Inputs!$C$14</definedName>
+    <definedName name="PCIlo">Inputs!$C$15</definedName>
+    <definedName name="PCImid">Inputs!$C$16</definedName>
+    <definedName name="PCIhi">Inputs!$C$17</definedName>
+    <definedName name="MktLo">Inputs!$C$18</definedName>
+    <definedName name="MktBase">Inputs!$C$19</definedName>
+    <definedName name="MktHi">Inputs!$C$20</definedName>
+    <definedName name="CJBlb">Inputs!$C$21</definedName>
+    <definedName name="QualCost">Inputs!$C$22</definedName>
+    <definedName name="Pdis">Inputs!$C$23</definedName>
+    <definedName name="Dcost">Inputs!$C$24</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -45,7 +47,7 @@
     <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0"/>
     <numFmt numFmtId="167" formatCode="0.0&quot;x&quot;"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -87,8 +89,14 @@
       <color rgb="00595959"/>
       <sz val="9"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="001F3864"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -113,6 +121,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00D6DCE5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
   </fills>
@@ -142,7 +155,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -153,10 +166,13 @@
     <xf numFmtId="3" fontId="5" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="5" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="9" fontId="5" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="5" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="5" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="5" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -167,6 +183,10 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -538,12 +558,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:D22"/>
+  <dimension ref="B2:D24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="46" customWidth="1" min="2" max="2"/>
+    <col width="52" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="70" customWidth="1" min="4" max="4"/>
+    <col width="78" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="2">
@@ -556,7 +576,7 @@
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Yellow = editable. Everything else recalculates. Define acronyms: PVA = polyvinyl alcohol; SNP = incumbent supplier; PCI = candidate second source.</t>
+          <t>Yellow = editable. PVA = polyvinyl alcohol. SNP Inc. = incumbent. PCI Manufacturing = candidate second source. The second source gets the LARGER of 1/3 of demand and its 1-drum/week minimum — or nothing.</t>
         </is>
       </c>
     </row>
@@ -588,14 +608,14 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Confirmed (SNP: 1/450-lb drum)</t>
+          <t>Confirmed (SNP Inc.: 1/450-lb drum)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>SNP price ($/lb delivered, all-in)</t>
+          <t>SNP Inc. price ($/lb delivered, all-in)</t>
         </is>
       </c>
       <c r="C7" s="6" t="n">
@@ -603,7 +623,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Real quote — SNP Est 012726-1</t>
+          <t>Real quote — SNP Estimate 012726-1</t>
         </is>
       </c>
     </row>
@@ -651,178 +671,210 @@
     <row r="11">
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Share of volume to 2nd source (Option A)</t>
-        </is>
-      </c>
-      <c r="C11" s="8" t="n">
-        <v>0.3333333333333333</v>
+          <t>Smallest volume a second source will accept (drums/week)</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>1</v>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>One-third of business</t>
+          <t>Supplier condition — below this they will not engage</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>Share for a 'warm' backup (Option C)</t>
-        </is>
-      </c>
-      <c r="C12" s="7" t="n">
-        <v>0.05</v>
+          <t xml:space="preserve">  = share of today's demand</t>
+        </is>
+      </c>
+      <c r="C12" s="8">
+        <f>MinDrumsWk*DrumLb/LbWk</f>
+        <v/>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>~1 drum every 7 weeks</t>
+          <t>~35%. This is the smallest insurance available.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>PCI price — LOW ($/lb)</t>
-        </is>
-      </c>
-      <c r="C13" s="6" t="n">
-        <v>2.5</v>
+          <t>Target share of demand (Option A)</t>
+        </is>
+      </c>
+      <c r="C13" s="9" t="n">
+        <v>0.3333333333333333</v>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Forecast floor</t>
+          <t>One-third. Year 1: 1/3 = 0.96 drums/wk, so the minimum (1.0) governs; from Year 2 the 1/3 governs.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>PCI price — MID ($/lb)</t>
-        </is>
-      </c>
-      <c r="C14" s="6" t="n">
-        <v>3.75</v>
+          <t xml:space="preserve">  = effective share, Year 1</t>
+        </is>
+      </c>
+      <c r="C14" s="8">
+        <f>MAX(Share,MinShare)</f>
+        <v/>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Midpoint of range</t>
+          <t>max(target, minimum)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>PCI price — HIGH ($/lb)</t>
+          <t>PCI price — LOW ($/lb)</t>
         </is>
       </c>
       <c r="C15" s="6" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Forecast ceiling</t>
+          <t>Forecast floor</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Market reference — LOW ($/lb)</t>
+          <t>PCI price — MID ($/lb)</t>
         </is>
       </c>
       <c r="C16" s="6" t="n">
-        <v>0.85</v>
+        <v>3.75</v>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Triangulated (resin floor + labor bottom-up)</t>
+          <t>Midpoint of range</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Market reference — BASE ($/lb)</t>
+          <t>PCI price — HIGH ($/lb)</t>
         </is>
       </c>
       <c r="C17" s="6" t="n">
-        <v>1.4</v>
+        <v>5</v>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Triangulated</t>
+          <t>Forecast ceiling</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>Market reference — HIGH ($/lb)</t>
+          <t>Market reference — LOW ($/lb)</t>
         </is>
       </c>
       <c r="C18" s="6" t="n">
-        <v>2.55</v>
+        <v>0.85</v>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Triangulated (retail ceiling)</t>
+          <t>Triangulated (resin floor + labor bottom-up)</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>CJB quote, landed ($/lb) — reference only</t>
+          <t>Market reference — BASE ($/lb)</t>
         </is>
       </c>
       <c r="C19" s="6" t="n">
-        <v>8.42</v>
+        <v>1.4</v>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>$8-8.50 toll excl. materials + $75/drum resin; ~11x SNP</t>
+          <t>Triangulated</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>One-time qualification cost ($)</t>
-        </is>
-      </c>
-      <c r="C20" s="9" t="n">
-        <v>15000</v>
+          <t>Market reference — HIGH ($/lb)</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="n">
+        <v>2.55</v>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>PLACEHOLDER — engineering hrs, samples, hydrogel tests, SQA, audit. Confirm.</t>
+          <t>Triangulated (retail ceiling)</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Disruption probability per year (for break-even)</t>
-        </is>
-      </c>
-      <c r="C21" s="7" t="n">
-        <v>0.05</v>
+          <t>CJB Applied Technologies quote, landed ($/lb) — reference</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="n">
+        <v>8.42</v>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>PLACEHOLDER — leadership judgement</t>
+          <t>$8-8.50 toll excl. materials + $75/drum resin; ~11x SNP</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>Cost of a 6-month SNP outage ($)</t>
-        </is>
-      </c>
-      <c r="C22" s="9" t="n">
+          <t>One-time qualification cost ($)</t>
+        </is>
+      </c>
+      <c r="C22" s="10" t="n">
+        <v>15000</v>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>PLACEHOLDER — engineering hrs, samples, hydrogel tests, quality agreement. Confirm.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>Disruption probability per year (for break-even)</t>
+        </is>
+      </c>
+      <c r="C23" s="7" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>PLACEHOLDER — leadership judgement</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>Cost of a 6-month SNP Inc. outage ($)</t>
+        </is>
+      </c>
+      <c r="C24" s="10" t="n">
         <v>500000</v>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>PLACEHOLDER — revenue at risk + expedite + line-down. NEEDED FROM FINANCE/OPS.</t>
         </is>
@@ -839,32 +891,34 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:K13"/>
+  <dimension ref="B2:M13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
     <col width="9" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
     <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
     <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>Five-year cost of Option A (dual-source at the chosen share)</t>
+          <t>Five-year cost of Option A</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Premium = share x (PCI price - SNP price) x annual lb. It scales 1:1 with volume, so growth compounds it.</t>
+          <t>Each year the second source gets max(1/3 of demand, 1 drum/week). Premium = share x (PCI price - SNP price) x annual lb; it grows with volume.</t>
         </is>
       </c>
     </row>
@@ -886,295 +940,345 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
+          <t>Effective share</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>Drums/wk to PCI</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
           <t>All-SNP baseline</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="H5" s="3" t="inlineStr">
         <is>
           <t>Option A @ PCI LOW</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="I5" s="3" t="inlineStr">
         <is>
           <t>Option A @ PCI MID</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr">
+      <c r="J5" s="3" t="inlineStr">
         <is>
           <t>Option A @ PCI HIGH</t>
         </is>
       </c>
-      <c r="I5" s="3" t="inlineStr">
+      <c r="K5" s="3" t="inlineStr">
         <is>
           <t>Premium LOW</t>
         </is>
       </c>
-      <c r="J5" s="3" t="inlineStr">
+      <c r="L5" s="3" t="inlineStr">
         <is>
           <t>Premium MID</t>
         </is>
       </c>
-      <c r="K5" s="3" t="inlineStr">
+      <c r="M5" s="3" t="inlineStr">
         <is>
           <t>Premium HIGH</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="10" t="n">
+      <c r="B6" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="C6" s="11">
+      <c r="C6" s="12">
         <f>LbWk*Weeks*(1+Growth)^(1-1)</f>
         <v/>
       </c>
-      <c r="D6" s="11">
+      <c r="D6" s="12">
         <f>C6/DrumLb</f>
         <v/>
       </c>
-      <c r="E6" s="12">
+      <c r="E6" s="13">
+        <f>MAX(Share,MinDrumsWk*Weeks*DrumLb/C6)</f>
+        <v/>
+      </c>
+      <c r="F6" s="14">
+        <f>D6*E6/Weeks</f>
+        <v/>
+      </c>
+      <c r="G6" s="15">
         <f>C6*SNPlb</f>
         <v/>
       </c>
-      <c r="F6" s="12">
-        <f>C6*(1-Share)*SNPlb+C6*Share*PCIlo</f>
-        <v/>
-      </c>
-      <c r="G6" s="12">
-        <f>C6*(1-Share)*SNPlb+C6*Share*PCImid</f>
-        <v/>
-      </c>
-      <c r="H6" s="12">
-        <f>C6*(1-Share)*SNPlb+C6*Share*PCIhi</f>
-        <v/>
-      </c>
-      <c r="I6" s="13">
-        <f>F6-E6</f>
-        <v/>
-      </c>
-      <c r="J6" s="13">
-        <f>G6-E6</f>
-        <v/>
-      </c>
-      <c r="K6" s="13">
-        <f>H6-E6</f>
+      <c r="H6" s="15">
+        <f>C6*(1-E6)*SNPlb+C6*E6*PCIlo</f>
+        <v/>
+      </c>
+      <c r="I6" s="15">
+        <f>C6*(1-E6)*SNPlb+C6*E6*PCImid</f>
+        <v/>
+      </c>
+      <c r="J6" s="15">
+        <f>C6*(1-E6)*SNPlb+C6*E6*PCIhi</f>
+        <v/>
+      </c>
+      <c r="K6" s="16">
+        <f>H6-G6</f>
+        <v/>
+      </c>
+      <c r="L6" s="16">
+        <f>I6-G6</f>
+        <v/>
+      </c>
+      <c r="M6" s="16">
+        <f>J6-G6</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="10" t="n">
+      <c r="B7" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="C7" s="11">
+      <c r="C7" s="12">
         <f>LbWk*Weeks*(1+Growth)^(2-1)</f>
         <v/>
       </c>
-      <c r="D7" s="11">
+      <c r="D7" s="12">
         <f>C7/DrumLb</f>
         <v/>
       </c>
-      <c r="E7" s="12">
+      <c r="E7" s="13">
+        <f>MAX(Share,MinDrumsWk*Weeks*DrumLb/C7)</f>
+        <v/>
+      </c>
+      <c r="F7" s="14">
+        <f>D7*E7/Weeks</f>
+        <v/>
+      </c>
+      <c r="G7" s="15">
         <f>C7*SNPlb</f>
         <v/>
       </c>
-      <c r="F7" s="12">
-        <f>C7*(1-Share)*SNPlb+C7*Share*PCIlo</f>
-        <v/>
-      </c>
-      <c r="G7" s="12">
-        <f>C7*(1-Share)*SNPlb+C7*Share*PCImid</f>
-        <v/>
-      </c>
-      <c r="H7" s="12">
-        <f>C7*(1-Share)*SNPlb+C7*Share*PCIhi</f>
-        <v/>
-      </c>
-      <c r="I7" s="13">
-        <f>F7-E7</f>
-        <v/>
-      </c>
-      <c r="J7" s="13">
-        <f>G7-E7</f>
-        <v/>
-      </c>
-      <c r="K7" s="13">
-        <f>H7-E7</f>
+      <c r="H7" s="15">
+        <f>C7*(1-E7)*SNPlb+C7*E7*PCIlo</f>
+        <v/>
+      </c>
+      <c r="I7" s="15">
+        <f>C7*(1-E7)*SNPlb+C7*E7*PCImid</f>
+        <v/>
+      </c>
+      <c r="J7" s="15">
+        <f>C7*(1-E7)*SNPlb+C7*E7*PCIhi</f>
+        <v/>
+      </c>
+      <c r="K7" s="16">
+        <f>H7-G7</f>
+        <v/>
+      </c>
+      <c r="L7" s="16">
+        <f>I7-G7</f>
+        <v/>
+      </c>
+      <c r="M7" s="16">
+        <f>J7-G7</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="10" t="n">
+      <c r="B8" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="C8" s="11">
+      <c r="C8" s="12">
         <f>LbWk*Weeks*(1+Growth)^(3-1)</f>
         <v/>
       </c>
-      <c r="D8" s="11">
+      <c r="D8" s="12">
         <f>C8/DrumLb</f>
         <v/>
       </c>
-      <c r="E8" s="12">
+      <c r="E8" s="13">
+        <f>MAX(Share,MinDrumsWk*Weeks*DrumLb/C8)</f>
+        <v/>
+      </c>
+      <c r="F8" s="14">
+        <f>D8*E8/Weeks</f>
+        <v/>
+      </c>
+      <c r="G8" s="15">
         <f>C8*SNPlb</f>
         <v/>
       </c>
-      <c r="F8" s="12">
-        <f>C8*(1-Share)*SNPlb+C8*Share*PCIlo</f>
-        <v/>
-      </c>
-      <c r="G8" s="12">
-        <f>C8*(1-Share)*SNPlb+C8*Share*PCImid</f>
-        <v/>
-      </c>
-      <c r="H8" s="12">
-        <f>C8*(1-Share)*SNPlb+C8*Share*PCIhi</f>
-        <v/>
-      </c>
-      <c r="I8" s="13">
-        <f>F8-E8</f>
-        <v/>
-      </c>
-      <c r="J8" s="13">
-        <f>G8-E8</f>
-        <v/>
-      </c>
-      <c r="K8" s="13">
-        <f>H8-E8</f>
+      <c r="H8" s="15">
+        <f>C8*(1-E8)*SNPlb+C8*E8*PCIlo</f>
+        <v/>
+      </c>
+      <c r="I8" s="15">
+        <f>C8*(1-E8)*SNPlb+C8*E8*PCImid</f>
+        <v/>
+      </c>
+      <c r="J8" s="15">
+        <f>C8*(1-E8)*SNPlb+C8*E8*PCIhi</f>
+        <v/>
+      </c>
+      <c r="K8" s="16">
+        <f>H8-G8</f>
+        <v/>
+      </c>
+      <c r="L8" s="16">
+        <f>I8-G8</f>
+        <v/>
+      </c>
+      <c r="M8" s="16">
+        <f>J8-G8</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="10" t="n">
+      <c r="B9" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="C9" s="11">
+      <c r="C9" s="12">
         <f>LbWk*Weeks*(1+Growth)^(4-1)</f>
         <v/>
       </c>
-      <c r="D9" s="11">
+      <c r="D9" s="12">
         <f>C9/DrumLb</f>
         <v/>
       </c>
-      <c r="E9" s="12">
+      <c r="E9" s="13">
+        <f>MAX(Share,MinDrumsWk*Weeks*DrumLb/C9)</f>
+        <v/>
+      </c>
+      <c r="F9" s="14">
+        <f>D9*E9/Weeks</f>
+        <v/>
+      </c>
+      <c r="G9" s="15">
         <f>C9*SNPlb</f>
         <v/>
       </c>
-      <c r="F9" s="12">
-        <f>C9*(1-Share)*SNPlb+C9*Share*PCIlo</f>
-        <v/>
-      </c>
-      <c r="G9" s="12">
-        <f>C9*(1-Share)*SNPlb+C9*Share*PCImid</f>
-        <v/>
-      </c>
-      <c r="H9" s="12">
-        <f>C9*(1-Share)*SNPlb+C9*Share*PCIhi</f>
-        <v/>
-      </c>
-      <c r="I9" s="13">
-        <f>F9-E9</f>
-        <v/>
-      </c>
-      <c r="J9" s="13">
-        <f>G9-E9</f>
-        <v/>
-      </c>
-      <c r="K9" s="13">
-        <f>H9-E9</f>
+      <c r="H9" s="15">
+        <f>C9*(1-E9)*SNPlb+C9*E9*PCIlo</f>
+        <v/>
+      </c>
+      <c r="I9" s="15">
+        <f>C9*(1-E9)*SNPlb+C9*E9*PCImid</f>
+        <v/>
+      </c>
+      <c r="J9" s="15">
+        <f>C9*(1-E9)*SNPlb+C9*E9*PCIhi</f>
+        <v/>
+      </c>
+      <c r="K9" s="16">
+        <f>H9-G9</f>
+        <v/>
+      </c>
+      <c r="L9" s="16">
+        <f>I9-G9</f>
+        <v/>
+      </c>
+      <c r="M9" s="16">
+        <f>J9-G9</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="10" t="n">
+      <c r="B10" s="11" t="n">
         <v>5</v>
       </c>
-      <c r="C10" s="11">
+      <c r="C10" s="12">
         <f>LbWk*Weeks*(1+Growth)^(5-1)</f>
         <v/>
       </c>
-      <c r="D10" s="11">
+      <c r="D10" s="12">
         <f>C10/DrumLb</f>
         <v/>
       </c>
-      <c r="E10" s="12">
+      <c r="E10" s="13">
+        <f>MAX(Share,MinDrumsWk*Weeks*DrumLb/C10)</f>
+        <v/>
+      </c>
+      <c r="F10" s="14">
+        <f>D10*E10/Weeks</f>
+        <v/>
+      </c>
+      <c r="G10" s="15">
         <f>C10*SNPlb</f>
         <v/>
       </c>
-      <c r="F10" s="12">
-        <f>C10*(1-Share)*SNPlb+C10*Share*PCIlo</f>
-        <v/>
-      </c>
-      <c r="G10" s="12">
-        <f>C10*(1-Share)*SNPlb+C10*Share*PCImid</f>
-        <v/>
-      </c>
-      <c r="H10" s="12">
-        <f>C10*(1-Share)*SNPlb+C10*Share*PCIhi</f>
-        <v/>
-      </c>
-      <c r="I10" s="13">
-        <f>F10-E10</f>
-        <v/>
-      </c>
-      <c r="J10" s="13">
-        <f>G10-E10</f>
-        <v/>
-      </c>
-      <c r="K10" s="13">
-        <f>H10-E10</f>
+      <c r="H10" s="15">
+        <f>C10*(1-E10)*SNPlb+C10*E10*PCIlo</f>
+        <v/>
+      </c>
+      <c r="I10" s="15">
+        <f>C10*(1-E10)*SNPlb+C10*E10*PCImid</f>
+        <v/>
+      </c>
+      <c r="J10" s="15">
+        <f>C10*(1-E10)*SNPlb+C10*E10*PCIhi</f>
+        <v/>
+      </c>
+      <c r="K10" s="16">
+        <f>H10-G10</f>
+        <v/>
+      </c>
+      <c r="L10" s="16">
+        <f>I10-G10</f>
+        <v/>
+      </c>
+      <c r="M10" s="16">
+        <f>J10-G10</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="14" t="inlineStr">
+      <c r="B11" s="17" t="inlineStr">
         <is>
           <t>5-yr total</t>
         </is>
       </c>
-      <c r="C11" s="15">
+      <c r="C11" s="18">
         <f>SUM(C6:C10)</f>
         <v/>
       </c>
-      <c r="D11" s="15">
+      <c r="D11" s="18">
         <f>SUM(D6:D10)</f>
         <v/>
       </c>
-      <c r="E11" s="16">
-        <f>SUM(E6:E10)</f>
-        <v/>
-      </c>
-      <c r="F11" s="16">
-        <f>SUM(F6:F10)</f>
-        <v/>
-      </c>
-      <c r="G11" s="16">
+      <c r="G11" s="19">
         <f>SUM(G6:G10)</f>
         <v/>
       </c>
-      <c r="H11" s="16">
+      <c r="H11" s="19">
         <f>SUM(H6:H10)</f>
         <v/>
       </c>
-      <c r="I11" s="16">
+      <c r="I11" s="19">
         <f>SUM(I6:I10)</f>
         <v/>
       </c>
-      <c r="J11" s="16">
+      <c r="J11" s="19">
         <f>SUM(J6:J10)</f>
         <v/>
       </c>
-      <c r="K11" s="16">
+      <c r="K11" s="19">
         <f>SUM(K6:K10)</f>
+        <v/>
+      </c>
+      <c r="L11" s="19">
+        <f>SUM(L6:L10)</f>
+        <v/>
+      </c>
+      <c r="M11" s="19">
+        <f>SUM(M6:M10)</f>
         <v/>
       </c>
     </row>
     <row r="13">
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Plus one-time qualification cost (Inputs) — applies to any second source, warm or active:</t>
-        </is>
-      </c>
-      <c r="E13" s="17">
+          <t>Plus one-time qualification cost (Inputs):</t>
+        </is>
+      </c>
+      <c r="G13" s="20">
         <f>QualCost</f>
         <v/>
       </c>
@@ -1190,27 +1294,26 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:F23"/>
+  <dimension ref="B2:E24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="2" max="2"/>
     <col width="26" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>What drives the premium: 2nd-source price and share (Year 1)</t>
+          <t>What drives the premium (Year 1, at the supplier minimum ≈ 1/3)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Premium is linear in both. The share is the lever we control; the price is what the market gives us.</t>
+          <t>Price is what the market gives us. Share is NOT a free lever: anything below the supplier minimum is not available.</t>
         </is>
       </c>
     </row>
@@ -1227,377 +1330,332 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>Premium @ 1/3 share</t>
+          <t>Premium (Year 1)</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>x baseline</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>Premium @ 5% (warm)</t>
+          <t>x today's PVA spend</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="18">
+      <c r="B6" s="21">
         <f>MktLo</f>
         <v/>
       </c>
-      <c r="C6" s="19" t="inlineStr">
+      <c r="C6" s="22" t="inlineStr">
         <is>
           <t>Market LOW</t>
         </is>
       </c>
-      <c r="D6" s="12">
-        <f>LbWk*Weeks*Share*(B6-SNPlb)</f>
-        <v/>
-      </c>
-      <c r="E6" s="20">
+      <c r="D6" s="15">
+        <f>LbWk*Weeks*EffShare*(B6-SNPlb)</f>
+        <v/>
+      </c>
+      <c r="E6" s="23">
         <f>D6/(LbWk*Weeks*SNPlb)</f>
         <v/>
       </c>
-      <c r="F6" s="12">
-        <f>LbWk*Weeks*WarmShare*(B6-SNPlb)</f>
-        <v/>
-      </c>
     </row>
     <row r="7">
-      <c r="B7" s="18">
+      <c r="B7" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" s="22" t="inlineStr">
+        <is>
+          <t>Upside case / assumed in July (low)</t>
+        </is>
+      </c>
+      <c r="D7" s="15">
+        <f>LbWk*Weeks*EffShare*(B7-SNPlb)</f>
+        <v/>
+      </c>
+      <c r="E7" s="23">
+        <f>D7/(LbWk*Weeks*SNPlb)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="21" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="C8" s="22" t="inlineStr">
+        <is>
+          <t>Upside case / assumed in July (high)</t>
+        </is>
+      </c>
+      <c r="D8" s="15">
+        <f>LbWk*Weeks*EffShare*(B8-SNPlb)</f>
+        <v/>
+      </c>
+      <c r="E8" s="23">
+        <f>D8/(LbWk*Weeks*SNPlb)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="21">
         <f>MktBase</f>
         <v/>
       </c>
-      <c r="C7" s="19" t="inlineStr">
+      <c r="C9" s="22" t="inlineStr">
         <is>
           <t>Market BASE</t>
         </is>
       </c>
-      <c r="D7" s="12">
-        <f>LbWk*Weeks*Share*(B7-SNPlb)</f>
-        <v/>
-      </c>
-      <c r="E7" s="20">
-        <f>D7/(LbWk*Weeks*SNPlb)</f>
-        <v/>
-      </c>
-      <c r="F7" s="12">
-        <f>LbWk*Weeks*WarmShare*(B7-SNPlb)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8">
-      <c r="B8" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="C8" s="19" t="inlineStr">
-        <is>
-          <t>Told to leadership (low)</t>
-        </is>
-      </c>
-      <c r="D8" s="12">
-        <f>LbWk*Weeks*Share*(B8-SNPlb)</f>
-        <v/>
-      </c>
-      <c r="E8" s="20">
-        <f>D8/(LbWk*Weeks*SNPlb)</f>
-        <v/>
-      </c>
-      <c r="F8" s="12">
-        <f>LbWk*Weeks*WarmShare*(B8-SNPlb)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9">
-      <c r="B9" s="18" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="C9" s="19" t="inlineStr">
-        <is>
-          <t>Told to leadership (high)</t>
-        </is>
-      </c>
-      <c r="D9" s="12">
-        <f>LbWk*Weeks*Share*(B9-SNPlb)</f>
-        <v/>
-      </c>
-      <c r="E9" s="20">
+      <c r="D9" s="15">
+        <f>LbWk*Weeks*EffShare*(B9-SNPlb)</f>
+        <v/>
+      </c>
+      <c r="E9" s="23">
         <f>D9/(LbWk*Weeks*SNPlb)</f>
         <v/>
       </c>
-      <c r="F9" s="12">
-        <f>LbWk*Weeks*WarmShare*(B9-SNPlb)</f>
-        <v/>
-      </c>
     </row>
     <row r="10">
-      <c r="B10" s="18">
+      <c r="B10" s="21" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="C10" s="22" t="inlineStr">
+        <is>
+          <t>Upside case — trigger price</t>
+        </is>
+      </c>
+      <c r="D10" s="15">
+        <f>LbWk*Weeks*EffShare*(B10-SNPlb)</f>
+        <v/>
+      </c>
+      <c r="E10" s="23">
+        <f>D10/(LbWk*Weeks*SNPlb)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="C11" s="22" t="inlineStr">
+        <is>
+          <t>Upside case — borderline</t>
+        </is>
+      </c>
+      <c r="D11" s="15">
+        <f>LbWk*Weeks*EffShare*(B11-SNPlb)</f>
+        <v/>
+      </c>
+      <c r="E11" s="23">
+        <f>D11/(LbWk*Weeks*SNPlb)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="21">
         <f>MktHi</f>
         <v/>
       </c>
-      <c r="C10" s="19" t="inlineStr">
+      <c r="C12" s="22" t="inlineStr">
         <is>
           <t>Market HIGH</t>
         </is>
       </c>
-      <c r="D10" s="12">
-        <f>LbWk*Weeks*Share*(B10-SNPlb)</f>
-        <v/>
-      </c>
-      <c r="E10" s="20">
-        <f>D10/(LbWk*Weeks*SNPlb)</f>
-        <v/>
-      </c>
-      <c r="F10" s="12">
-        <f>LbWk*Weeks*WarmShare*(B10-SNPlb)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11">
-      <c r="B11" s="18">
+      <c r="D12" s="15">
+        <f>LbWk*Weeks*EffShare*(B12-SNPlb)</f>
+        <v/>
+      </c>
+      <c r="E12" s="23">
+        <f>D12/(LbWk*Weeks*SNPlb)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="21">
         <f>PCIlo</f>
         <v/>
       </c>
-      <c r="C11" s="19" t="inlineStr">
+      <c r="C13" s="22" t="inlineStr">
         <is>
           <t>PCI LOW</t>
         </is>
       </c>
-      <c r="D11" s="12">
-        <f>LbWk*Weeks*Share*(B11-SNPlb)</f>
-        <v/>
-      </c>
-      <c r="E11" s="20">
-        <f>D11/(LbWk*Weeks*SNPlb)</f>
-        <v/>
-      </c>
-      <c r="F11" s="12">
-        <f>LbWk*Weeks*WarmShare*(B11-SNPlb)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12">
-      <c r="B12" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="C12" s="19" t="inlineStr">
-        <is>
-          <t>PCI original assumption</t>
-        </is>
-      </c>
-      <c r="D12" s="12">
-        <f>LbWk*Weeks*Share*(B12-SNPlb)</f>
-        <v/>
-      </c>
-      <c r="E12" s="20">
-        <f>D12/(LbWk*Weeks*SNPlb)</f>
-        <v/>
-      </c>
-      <c r="F12" s="12">
-        <f>LbWk*Weeks*WarmShare*(B12-SNPlb)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13">
-      <c r="B13" s="18">
+      <c r="D13" s="15">
+        <f>LbWk*Weeks*EffShare*(B13-SNPlb)</f>
+        <v/>
+      </c>
+      <c r="E13" s="23">
+        <f>D13/(LbWk*Weeks*SNPlb)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="21">
         <f>PCImid</f>
         <v/>
       </c>
-      <c r="C13" s="19" t="inlineStr">
+      <c r="C14" s="22" t="inlineStr">
         <is>
           <t>PCI MID</t>
         </is>
       </c>
-      <c r="D13" s="12">
-        <f>LbWk*Weeks*Share*(B13-SNPlb)</f>
-        <v/>
-      </c>
-      <c r="E13" s="20">
-        <f>D13/(LbWk*Weeks*SNPlb)</f>
-        <v/>
-      </c>
-      <c r="F13" s="12">
-        <f>LbWk*Weeks*WarmShare*(B13-SNPlb)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14">
-      <c r="B14" s="18">
+      <c r="D14" s="15">
+        <f>LbWk*Weeks*EffShare*(B14-SNPlb)</f>
+        <v/>
+      </c>
+      <c r="E14" s="23">
+        <f>D14/(LbWk*Weeks*SNPlb)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="21">
         <f>PCIhi</f>
         <v/>
       </c>
-      <c r="C14" s="19" t="inlineStr">
+      <c r="C15" s="22" t="inlineStr">
         <is>
           <t>PCI HIGH</t>
         </is>
       </c>
-      <c r="D14" s="12">
-        <f>LbWk*Weeks*Share*(B14-SNPlb)</f>
-        <v/>
-      </c>
-      <c r="E14" s="20">
-        <f>D14/(LbWk*Weeks*SNPlb)</f>
-        <v/>
-      </c>
-      <c r="F14" s="12">
-        <f>LbWk*Weeks*WarmShare*(B14-SNPlb)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15">
-      <c r="B15" s="18">
+      <c r="D15" s="15">
+        <f>LbWk*Weeks*EffShare*(B15-SNPlb)</f>
+        <v/>
+      </c>
+      <c r="E15" s="23">
+        <f>D15/(LbWk*Weeks*SNPlb)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="21">
         <f>CJBlb</f>
         <v/>
       </c>
-      <c r="C15" s="19" t="inlineStr">
+      <c r="C16" s="22" t="inlineStr">
         <is>
           <t>CJB quote (landed)</t>
         </is>
       </c>
-      <c r="D15" s="12">
-        <f>LbWk*Weeks*Share*(B15-SNPlb)</f>
-        <v/>
-      </c>
-      <c r="E15" s="20">
-        <f>D15/(LbWk*Weeks*SNPlb)</f>
-        <v/>
-      </c>
-      <c r="F15" s="12">
-        <f>LbWk*Weeks*WarmShare*(B15-SNPlb)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" ht="30" customHeight="1">
-      <c r="B18" s="3" t="inlineStr">
+      <c r="D16" s="15">
+        <f>LbWk*Weeks*EffShare*(B16-SNPlb)</f>
+        <v/>
+      </c>
+      <c r="E16" s="23">
+        <f>D16/(LbWk*Weeks*SNPlb)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="30" customHeight="1">
+      <c r="B17" s="3" t="inlineStr">
         <is>
           <t>Share to 2nd source</t>
         </is>
       </c>
-      <c r="C18" s="3" t="inlineStr">
-        <is>
-          <t>Drums/yr</t>
-        </is>
-      </c>
-      <c r="D18" s="3" t="inlineStr">
-        <is>
-          <t>Premium @ PCI LOW</t>
-        </is>
-      </c>
-      <c r="E18" s="3" t="inlineStr">
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>Drums/week</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>Available?</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
         <is>
           <t>Premium @ PCI MID</t>
         </is>
       </c>
-      <c r="F18" s="3" t="inlineStr">
-        <is>
-          <t>Premium @ PCI HIGH</t>
-        </is>
+    </row>
+    <row r="18">
+      <c r="B18" s="24" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="C18" s="14">
+        <f>LbWk*B18/DrumLb</f>
+        <v/>
+      </c>
+      <c r="D18" s="25">
+        <f>IF(C18&gt;=MinDrumsWk,"Yes",IF(B18&gt;=0.3,"Rounds up to the 1-drum minimum","NO — below supplier minimum"))</f>
+        <v/>
+      </c>
+      <c r="E18" s="26">
+        <f>IF(B18&gt;=0.3,LbWk*Weeks*MAX(B18,MinShare)*(PCImid-SNPlb),"n/a")</f>
+        <v/>
       </c>
     </row>
     <row r="19">
-      <c r="B19" s="21" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="C19" s="11">
-        <f>LbWk*Weeks*B19/DrumLb</f>
-        <v/>
-      </c>
-      <c r="D19" s="12">
-        <f>LbWk*Weeks*B19*(PCIlo-SNPlb)</f>
-        <v/>
-      </c>
-      <c r="E19" s="12">
-        <f>LbWk*Weeks*B19*(PCImid-SNPlb)</f>
-        <v/>
-      </c>
-      <c r="F19" s="12">
-        <f>LbWk*Weeks*B19*(PCIhi-SNPlb)</f>
+      <c r="B19" s="24" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C19" s="14">
+        <f>LbWk*B19/DrumLb</f>
+        <v/>
+      </c>
+      <c r="D19" s="25">
+        <f>IF(C19&gt;=MinDrumsWk,"Yes",IF(B19&gt;=0.3,"Rounds up to the 1-drum minimum","NO — below supplier minimum"))</f>
+        <v/>
+      </c>
+      <c r="E19" s="26">
+        <f>IF(B19&gt;=0.3,LbWk*Weeks*MAX(B19,MinShare)*(PCImid-SNPlb),"n/a")</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="B20" s="21" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="C20" s="11">
-        <f>LbWk*Weeks*B20/DrumLb</f>
-        <v/>
-      </c>
-      <c r="D20" s="12">
-        <f>LbWk*Weeks*B20*(PCIlo-SNPlb)</f>
-        <v/>
-      </c>
-      <c r="E20" s="12">
-        <f>LbWk*Weeks*B20*(PCImid-SNPlb)</f>
-        <v/>
-      </c>
-      <c r="F20" s="12">
-        <f>LbWk*Weeks*B20*(PCIhi-SNPlb)</f>
+      <c r="B20" s="24" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="C20" s="14">
+        <f>LbWk*B20/DrumLb</f>
+        <v/>
+      </c>
+      <c r="D20" s="25">
+        <f>IF(C20&gt;=MinDrumsWk,"Yes",IF(B20&gt;=0.3,"Rounds up to the 1-drum minimum","NO — below supplier minimum"))</f>
+        <v/>
+      </c>
+      <c r="E20" s="26">
+        <f>IF(B20&gt;=0.3,LbWk*Weeks*MAX(B20,MinShare)*(PCImid-SNPlb),"n/a")</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="B21" s="21" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="C21" s="11">
-        <f>LbWk*Weeks*B21/DrumLb</f>
-        <v/>
-      </c>
-      <c r="D21" s="12">
-        <f>LbWk*Weeks*B21*(PCIlo-SNPlb)</f>
-        <v/>
-      </c>
-      <c r="E21" s="12">
-        <f>LbWk*Weeks*B21*(PCImid-SNPlb)</f>
-        <v/>
-      </c>
-      <c r="F21" s="12">
-        <f>LbWk*Weeks*B21*(PCIhi-SNPlb)</f>
+      <c r="B21" s="24" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="C21" s="14">
+        <f>LbWk*B21/DrumLb</f>
+        <v/>
+      </c>
+      <c r="D21" s="27">
+        <f>IF(C21&gt;=MinDrumsWk,"Yes",IF(B21&gt;=0.3,"Rounds up to the 1-drum minimum","NO — below supplier minimum"))</f>
+        <v/>
+      </c>
+      <c r="E21" s="15">
+        <f>IF(B21&gt;=0.3,LbWk*Weeks*MAX(B21,MinShare)*(PCImid-SNPlb),"n/a")</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="B22" s="21" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="C22" s="11">
-        <f>LbWk*Weeks*B22/DrumLb</f>
-        <v/>
-      </c>
-      <c r="D22" s="12">
-        <f>LbWk*Weeks*B22*(PCIlo-SNPlb)</f>
-        <v/>
-      </c>
-      <c r="E22" s="12">
-        <f>LbWk*Weeks*B22*(PCImid-SNPlb)</f>
-        <v/>
-      </c>
-      <c r="F22" s="12">
-        <f>LbWk*Weeks*B22*(PCIhi-SNPlb)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23">
-      <c r="B23" s="21" t="n">
+      <c r="B22" s="24" t="n">
         <v>0.5</v>
       </c>
-      <c r="C23" s="11">
-        <f>LbWk*Weeks*B23/DrumLb</f>
-        <v/>
-      </c>
-      <c r="D23" s="12">
-        <f>LbWk*Weeks*B23*(PCIlo-SNPlb)</f>
-        <v/>
-      </c>
-      <c r="E23" s="12">
-        <f>LbWk*Weeks*B23*(PCImid-SNPlb)</f>
-        <v/>
-      </c>
-      <c r="F23" s="12">
-        <f>LbWk*Weeks*B23*(PCIhi-SNPlb)</f>
-        <v/>
+      <c r="C22" s="14">
+        <f>LbWk*B22/DrumLb</f>
+        <v/>
+      </c>
+      <c r="D22" s="27">
+        <f>IF(C22&gt;=MinDrumsWk,"Yes",IF(B22&gt;=0.3,"Rounds up to the 1-drum minimum","NO — below supplier minimum"))</f>
+        <v/>
+      </c>
+      <c r="E22" s="15">
+        <f>IF(B22&gt;=0.3,LbWk*Weeks*MAX(B22,MinShare)*(PCImid-SNPlb),"n/a")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="28" t="inlineStr">
+        <is>
+          <t>This is why there is no 'low-cost insurance' version of Option A: the smallest second source anyone will sell us is one drum a week.</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -1616,7 +1674,7 @@
   <cols>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
@@ -1625,14 +1683,14 @@
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>If SNP raises price on the volume it keeps (Year 1, PCI MID)</t>
+          <t>If SNP Inc. raises price on the volume it keeps (Year 1, PCI MID)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Losing a third of our volume may cost SNP its batch efficiency. A surcharge on the retained two-thirds compounds the premium.</t>
+          <t>Losing a third of our volume may cost SNP its batch efficiency. A surcharge on the retained ~2/3 compounds the premium.</t>
         </is>
       </c>
     </row>
@@ -1649,12 +1707,12 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>SNP annual (2/3)</t>
+          <t>SNP annual (retained)</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>PCI annual (1/3)</t>
+          <t>PCI annual</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
@@ -1669,126 +1727,126 @@
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="21" t="n">
+      <c r="B6" s="24" t="n">
         <v>0</v>
       </c>
-      <c r="C6" s="18">
+      <c r="C6" s="21">
         <f>SNPlb*(1+B6)</f>
         <v/>
       </c>
-      <c r="D6" s="12">
-        <f>LbWk*Weeks*(1-Share)*C6</f>
-        <v/>
-      </c>
-      <c r="E6" s="12">
-        <f>LbWk*Weeks*Share*PCImid</f>
-        <v/>
-      </c>
-      <c r="F6" s="12">
+      <c r="D6" s="15">
+        <f>LbWk*Weeks*(1-EffShare)*C6</f>
+        <v/>
+      </c>
+      <c r="E6" s="15">
+        <f>LbWk*Weeks*EffShare*PCImid</f>
+        <v/>
+      </c>
+      <c r="F6" s="15">
         <f>D6+E6</f>
         <v/>
       </c>
-      <c r="G6" s="12">
+      <c r="G6" s="15">
         <f>F6-LbWk*Weeks*SNPlb</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="21" t="n">
+      <c r="B7" s="24" t="n">
         <v>0.05</v>
       </c>
-      <c r="C7" s="18">
+      <c r="C7" s="21">
         <f>SNPlb*(1+B7)</f>
         <v/>
       </c>
-      <c r="D7" s="12">
-        <f>LbWk*Weeks*(1-Share)*C7</f>
-        <v/>
-      </c>
-      <c r="E7" s="12">
-        <f>LbWk*Weeks*Share*PCImid</f>
-        <v/>
-      </c>
-      <c r="F7" s="12">
+      <c r="D7" s="15">
+        <f>LbWk*Weeks*(1-EffShare)*C7</f>
+        <v/>
+      </c>
+      <c r="E7" s="15">
+        <f>LbWk*Weeks*EffShare*PCImid</f>
+        <v/>
+      </c>
+      <c r="F7" s="15">
         <f>D7+E7</f>
         <v/>
       </c>
-      <c r="G7" s="12">
+      <c r="G7" s="15">
         <f>F7-LbWk*Weeks*SNPlb</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="21" t="n">
+      <c r="B8" s="24" t="n">
         <v>0.1</v>
       </c>
-      <c r="C8" s="18">
+      <c r="C8" s="21">
         <f>SNPlb*(1+B8)</f>
         <v/>
       </c>
-      <c r="D8" s="12">
-        <f>LbWk*Weeks*(1-Share)*C8</f>
-        <v/>
-      </c>
-      <c r="E8" s="12">
-        <f>LbWk*Weeks*Share*PCImid</f>
-        <v/>
-      </c>
-      <c r="F8" s="12">
+      <c r="D8" s="15">
+        <f>LbWk*Weeks*(1-EffShare)*C8</f>
+        <v/>
+      </c>
+      <c r="E8" s="15">
+        <f>LbWk*Weeks*EffShare*PCImid</f>
+        <v/>
+      </c>
+      <c r="F8" s="15">
         <f>D8+E8</f>
         <v/>
       </c>
-      <c r="G8" s="12">
+      <c r="G8" s="15">
         <f>F8-LbWk*Weeks*SNPlb</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="21" t="n">
+      <c r="B9" s="24" t="n">
         <v>0.2</v>
       </c>
-      <c r="C9" s="18">
+      <c r="C9" s="21">
         <f>SNPlb*(1+B9)</f>
         <v/>
       </c>
-      <c r="D9" s="12">
-        <f>LbWk*Weeks*(1-Share)*C9</f>
-        <v/>
-      </c>
-      <c r="E9" s="12">
-        <f>LbWk*Weeks*Share*PCImid</f>
-        <v/>
-      </c>
-      <c r="F9" s="12">
+      <c r="D9" s="15">
+        <f>LbWk*Weeks*(1-EffShare)*C9</f>
+        <v/>
+      </c>
+      <c r="E9" s="15">
+        <f>LbWk*Weeks*EffShare*PCImid</f>
+        <v/>
+      </c>
+      <c r="F9" s="15">
         <f>D9+E9</f>
         <v/>
       </c>
-      <c r="G9" s="12">
+      <c r="G9" s="15">
         <f>F9-LbWk*Weeks*SNPlb</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="21" t="n">
+      <c r="B10" s="24" t="n">
         <v>0.33</v>
       </c>
-      <c r="C10" s="18">
+      <c r="C10" s="21">
         <f>SNPlb*(1+B10)</f>
         <v/>
       </c>
-      <c r="D10" s="12">
-        <f>LbWk*Weeks*(1-Share)*C10</f>
-        <v/>
-      </c>
-      <c r="E10" s="12">
-        <f>LbWk*Weeks*Share*PCImid</f>
-        <v/>
-      </c>
-      <c r="F10" s="12">
+      <c r="D10" s="15">
+        <f>LbWk*Weeks*(1-EffShare)*C10</f>
+        <v/>
+      </c>
+      <c r="E10" s="15">
+        <f>LbWk*Weeks*EffShare*PCImid</f>
+        <v/>
+      </c>
+      <c r="F10" s="15">
         <f>D10+E10</f>
         <v/>
       </c>
-      <c r="G10" s="12">
+      <c r="G10" s="15">
         <f>F10-LbWk*Weeks*SNPlb</f>
         <v/>
       </c>
@@ -1804,10 +1862,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:G14"/>
+  <dimension ref="B2:G13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
@@ -1825,14 +1883,14 @@
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>A second source is justified only if: annual premium &lt;= P(SNP disruption in a year) x loss the second source would AVOID. Note: at 1/3 share, 2/3 of volume is still exposed unless the second source can ramp.</t>
+          <t>Option A is justified only if: annual premium &lt;= P(SNP disruption in a year) x loss the second source would AVOID. ~2/3 of volume is still exposed until PCI can ramp.</t>
         </is>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1">
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Option</t>
+          <t>Option A price case</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
@@ -1862,139 +1920,112 @@
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="10" t="inlineStr">
-        <is>
-          <t>A — dual @ PCI LOW</t>
-        </is>
-      </c>
-      <c r="C6" s="12">
-        <f>LbWk*Weeks*Share*(PCIlo-SNPlb)</f>
-        <v/>
-      </c>
-      <c r="D6" s="12">
+      <c r="B6" s="11" t="inlineStr">
+        <is>
+          <t>PCI LOW $2.50</t>
+        </is>
+      </c>
+      <c r="C6" s="15">
+        <f>LbWk*Weeks*EffShare*(PCIlo-SNPlb)</f>
+        <v/>
+      </c>
+      <c r="D6" s="15">
         <f>C6/0.02</f>
         <v/>
       </c>
-      <c r="E6" s="12">
+      <c r="E6" s="15">
         <f>C6/0.05</f>
         <v/>
       </c>
-      <c r="F6" s="12">
+      <c r="F6" s="15">
         <f>C6/0.1</f>
         <v/>
       </c>
-      <c r="G6" s="12">
+      <c r="G6" s="15">
         <f>C6/0.2</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="10" t="inlineStr">
-        <is>
-          <t>A — dual @ PCI MID</t>
-        </is>
-      </c>
-      <c r="C7" s="12">
-        <f>LbWk*Weeks*Share*(PCImid-SNPlb)</f>
-        <v/>
-      </c>
-      <c r="D7" s="12">
+      <c r="B7" s="11" t="inlineStr">
+        <is>
+          <t>PCI MID $3.75</t>
+        </is>
+      </c>
+      <c r="C7" s="15">
+        <f>LbWk*Weeks*EffShare*(PCImid-SNPlb)</f>
+        <v/>
+      </c>
+      <c r="D7" s="15">
         <f>C7/0.02</f>
         <v/>
       </c>
-      <c r="E7" s="12">
+      <c r="E7" s="15">
         <f>C7/0.05</f>
         <v/>
       </c>
-      <c r="F7" s="12">
+      <c r="F7" s="15">
         <f>C7/0.1</f>
         <v/>
       </c>
-      <c r="G7" s="12">
+      <c r="G7" s="15">
         <f>C7/0.2</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="10" t="inlineStr">
-        <is>
-          <t>A — dual @ PCI HIGH</t>
-        </is>
-      </c>
-      <c r="C8" s="12">
-        <f>LbWk*Weeks*Share*(PCIhi-SNPlb)</f>
-        <v/>
-      </c>
-      <c r="D8" s="12">
+      <c r="B8" s="11" t="inlineStr">
+        <is>
+          <t>PCI HIGH $5.00</t>
+        </is>
+      </c>
+      <c r="C8" s="15">
+        <f>LbWk*Weeks*EffShare*(PCIhi-SNPlb)</f>
+        <v/>
+      </c>
+      <c r="D8" s="15">
         <f>C8/0.02</f>
         <v/>
       </c>
-      <c r="E8" s="12">
+      <c r="E8" s="15">
         <f>C8/0.05</f>
         <v/>
       </c>
-      <c r="F8" s="12">
+      <c r="F8" s="15">
         <f>C8/0.1</f>
         <v/>
       </c>
-      <c r="G8" s="12">
+      <c r="G8" s="15">
         <f>C8/0.2</f>
         <v/>
       </c>
     </row>
-    <row r="9">
-      <c r="B9" s="10" t="inlineStr">
-        <is>
-          <t>C — warm 5% @ PCI MID</t>
-        </is>
-      </c>
-      <c r="C9" s="12">
-        <f>LbWk*Weeks*WarmShare*(PCImid-SNPlb)</f>
-        <v/>
-      </c>
-      <c r="D9" s="12">
-        <f>C9/0.02</f>
-        <v/>
-      </c>
-      <c r="E9" s="12">
-        <f>C9/0.05</f>
-        <v/>
-      </c>
-      <c r="F9" s="12">
-        <f>C9/0.1</f>
-        <v/>
-      </c>
-      <c r="G9" s="12">
-        <f>C9/0.2</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11">
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>Read: each cell = the avoided loss a disruption would have to cause for the premium to pay off. Compare to Inputs 'Cost of a 6-month SNP outage'.</t>
-        </is>
+    <row r="10">
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Read: each cell = the avoided loss an SNP outage would have to cause for the premium to pay off. Compare to Inputs 'Cost of a 6-month SNP Inc. outage'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="17" t="inlineStr">
+        <is>
+          <t>Expected annual loss with NO second source = Pdis x Dcost:</t>
+        </is>
+      </c>
+      <c r="D12" s="20">
+        <f>Pdis*Dcost</f>
+        <v/>
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="14" t="inlineStr">
-        <is>
-          <t>Expected annual loss with NO second source = Pdis x Dcost:</t>
-        </is>
-      </c>
-      <c r="D13" s="17">
-        <f>Pdis*Dcost</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14">
-      <c r="B14" s="14" t="inlineStr">
-        <is>
-          <t>Verdict @ PCI MID, 1/3 share:</t>
-        </is>
-      </c>
-      <c r="D14">
-        <f>IF(D13&gt;=C7,"Premium is justified","Premium exceeds expected loss")</f>
+      <c r="B13" s="17" t="inlineStr">
+        <is>
+          <t>Verdict @ PCI MID:</t>
+        </is>
+      </c>
+      <c r="D13">
+        <f>IF(D12&gt;=C7,"Option A is justified","Premium exceeds expected loss — Option B")</f>
         <v/>
       </c>
     </row>
@@ -2009,19 +2040,25 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:E13"/>
+  <dimension ref="B2:D13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="28" customWidth="1" min="5" max="5"/>
+    <col width="42" customWidth="1" min="3" max="3"/>
+    <col width="42" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>The three options, side by side (Year 1, PCI MID unless noted)</t>
+          <t>The two options, side by side (Year 1, PCI MID unless noted)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>There is no smaller version of A: the supplier minimum is one drum a week.</t>
         </is>
       </c>
     </row>
@@ -2029,184 +2066,143 @@
       <c r="B5" s="3" t="inlineStr"/>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>A — Dual-source now (1/3)</t>
+          <t>A — Second source (PCI Manufacturing) at ~1/3</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>B — Single + strengthen SNP</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>C — Warm backup (5%)</t>
+          <t>B — Single source (SNP Inc.) + strengthen</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="14" t="inlineStr">
+      <c r="B6" s="17" t="inlineStr">
         <is>
           <t>Annual purchase cost</t>
         </is>
       </c>
-      <c r="C6" s="22">
-        <f>LbWk*Weeks*(1-Share)*SNPlb+LbWk*Weeks*Share*PCImid</f>
-        <v/>
-      </c>
-      <c r="D6" s="22">
+      <c r="C6" s="29">
+        <f>LbWk*Weeks*(1-EffShare)*SNPlb+LbWk*Weeks*EffShare*PCImid</f>
+        <v/>
+      </c>
+      <c r="D6" s="29">
         <f>LbWk*Weeks*SNPlb</f>
         <v/>
       </c>
-      <c r="E6" s="22">
-        <f>LbWk*Weeks*(1-WarmShare)*SNPlb+LbWk*Weeks*WarmShare*PCImid</f>
-        <v/>
-      </c>
     </row>
     <row r="7">
-      <c r="B7" s="14" t="inlineStr">
+      <c r="B7" s="17" t="inlineStr">
         <is>
           <t>Premium vs today</t>
         </is>
       </c>
-      <c r="C7" s="22">
+      <c r="C7" s="29">
         <f>B6-LbWk*Weeks*SNPlb</f>
         <v/>
       </c>
-      <c r="D7" s="23" t="inlineStr">
+      <c r="D7" s="30" t="inlineStr">
+        <is>
+          <t>0 (+ small continuity spend)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="17" t="inlineStr">
+        <is>
+          <t>One-time qualification</t>
+        </is>
+      </c>
+      <c r="C8" s="29">
+        <f>QualCost</f>
+        <v/>
+      </c>
+      <c r="D8" s="30" t="inlineStr">
+        <is>
+          <t>0 (plan/document only)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="17" t="inlineStr">
+        <is>
+          <t>5-yr premium (10% growth)</t>
+        </is>
+      </c>
+      <c r="C9" s="29">
+        <f>'5-Year'!L11</f>
+        <v/>
+      </c>
+      <c r="D9" s="30" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E7" s="22">
-        <f>D6-LbWk*Weeks*SNPlb</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8">
-      <c r="B8" s="14" t="inlineStr">
-        <is>
-          <t>One-time qualification</t>
-        </is>
-      </c>
-      <c r="C8" s="22">
-        <f>QualCost</f>
-        <v/>
-      </c>
-      <c r="D8" s="23" t="inlineStr">
-        <is>
-          <t>0 (plan/document only)</t>
-        </is>
-      </c>
-      <c r="E8" s="22">
-        <f>QualCost</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9">
-      <c r="B9" s="14" t="inlineStr">
-        <is>
-          <t>5-yr premium (10% growth)</t>
-        </is>
-      </c>
-      <c r="C9" s="22">
-        <f>B7*(1+(1+Growth)+(1+Growth)^2+(1+Growth)^3+(1+Growth)^4)</f>
-        <v/>
-      </c>
-      <c r="D9" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E9" s="22">
-        <f>D7*(1+(1+Growth)+(1+Growth)^2+(1+Growth)^3+(1+Growth)^4)</f>
-        <v/>
-      </c>
     </row>
     <row r="10">
-      <c r="B10" s="14" t="inlineStr">
+      <c r="B10" s="17" t="inlineStr">
         <is>
           <t>Volume still exposed if SNP fails</t>
         </is>
       </c>
-      <c r="C10" s="23" t="inlineStr">
-        <is>
-          <t>2/3 (until PCI ramps)</t>
-        </is>
-      </c>
-      <c r="D10" s="23" t="inlineStr">
+      <c r="C10" s="30" t="inlineStr">
+        <is>
+          <t>~2/3 (until PCI ramps — unconfirmed)</t>
+        </is>
+      </c>
+      <c r="D10" s="30" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="E10" s="23" t="inlineStr">
-        <is>
-          <t>95% (until PCI ramps)</t>
-        </is>
-      </c>
     </row>
     <row r="11">
-      <c r="B11" s="14" t="inlineStr">
+      <c r="B11" s="17" t="inlineStr">
         <is>
           <t>Time to recover if SNP fails</t>
         </is>
       </c>
-      <c r="C11" s="23" t="inlineStr">
+      <c r="C11" s="30" t="inlineStr">
         <is>
           <t>weeks (PCI ramp)</t>
         </is>
       </c>
-      <c r="D11" s="23" t="inlineStr">
-        <is>
-          <t>6-12 months (cold start)</t>
-        </is>
-      </c>
-      <c r="E11" s="23" t="inlineStr">
-        <is>
-          <t>weeks-months (re-activate)</t>
+      <c r="D11" s="30" t="inlineStr">
+        <is>
+          <t>6-12 months cold start; 3-4 with kit current</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="14" t="inlineStr">
-        <is>
-          <t>Signal to SNP</t>
-        </is>
-      </c>
-      <c r="C12" s="23" t="inlineStr">
-        <is>
-          <t>Lost a third of volume</t>
-        </is>
-      </c>
-      <c r="D12" s="23" t="inlineStr">
+      <c r="B12" s="17" t="inlineStr">
+        <is>
+          <t>Signal to SNP Inc.</t>
+        </is>
+      </c>
+      <c r="C12" s="30" t="inlineStr">
+        <is>
+          <t>Lost a third of its volume</t>
+        </is>
+      </c>
+      <c r="D12" s="30" t="inlineStr">
         <is>
           <t>Deeper partnership</t>
         </is>
       </c>
-      <c r="E12" s="23" t="inlineStr">
-        <is>
-          <t>Minor</t>
-        </is>
-      </c>
     </row>
     <row r="13">
-      <c r="B13" s="14" t="inlineStr">
+      <c r="B13" s="17" t="inlineStr">
         <is>
           <t>Compliance posture</t>
         </is>
       </c>
-      <c r="C13" s="23" t="inlineStr">
+      <c r="C13" s="30" t="inlineStr">
         <is>
           <t>Strong</t>
         </is>
       </c>
-      <c r="D13" s="23" t="inlineStr">
-        <is>
-          <t>Defensible if documented</t>
-        </is>
-      </c>
-      <c r="E13" s="23" t="inlineStr">
-        <is>
-          <t>Strong</t>
+      <c r="D13" s="30" t="inlineStr">
+        <is>
+          <t>Defensible if risk + plan documented</t>
         </is>
       </c>
     </row>

--- a/PVA second supplier initiative/PVA_Second_Supplier_Leadership_Model.xlsx
+++ b/PVA second supplier initiative/PVA_Second_Supplier_Leadership_Model.xlsx
@@ -8,11 +8,14 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Inputs" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5-Year" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sensitivity" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SNP Re-price" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Break-even" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Options" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Supplier Quotes" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PCI Quote Scenarios" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PCI Experiment" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5-Year" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sensitivity" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SNP Re-price" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Break-even" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Options" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="DrumLb">Inputs!$C$6</definedName>
@@ -34,6 +37,9 @@
     <definedName name="QualCost">Inputs!$C$22</definedName>
     <definedName name="Pdis">Inputs!$C$23</definedName>
     <definedName name="Dcost">Inputs!$C$24</definedName>
+    <definedName name="PCIq">Inputs!$C$27</definedName>
+    <definedName name="PCIsub">Inputs!$C$28</definedName>
+    <definedName name="PCIbatch">Inputs!$C$29</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -41,13 +47,15 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="6">
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
     <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0"/>
     <numFmt numFmtId="167" formatCode="0.0&quot;x&quot;"/>
+    <numFmt numFmtId="168" formatCode="0.00&quot;x&quot;"/>
+    <numFmt numFmtId="169" formatCode="0.0"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -95,8 +103,20 @@
       <color rgb="001F3864"/>
       <sz val="9"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="001F3864"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="001F3864"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -128,6 +148,16 @@
         <fgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFEB9C"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -155,7 +185,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -191,6 +221,48 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="0" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -558,7 +630,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:D24"/>
+  <dimension ref="B2:D30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="2" max="2"/>
@@ -880,12 +952,1253 @@
         </is>
       </c>
     </row>
+    <row r="26">
+      <c r="B26" s="31" t="inlineStr">
+        <is>
+          <t>PCI MANUFACTURING — REAL QUOTE (2026-09-28)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>PCI quoted price — one batch of 5 drums ($/lb)</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>Real quote. CONFIRM: delivered? materials, drum, freight included? validity period?</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>PCI price — orders below one batch ($/lb)</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>Real quote. Makes any sub-batch (e.g. 1 drum/week) uneconomic.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>PCI batch size (drums)</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>One batch = 5 drums = 2,250 lb = ~12 days of full demand</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>The $2.50 / $3.75 / $5.00 rows above were the pre-quote forecast; keep for history. The quote ($3.50) sits at the forecast mid.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B2:G15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="44" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="58" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="2">
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>All price points on the table — real quotes vs references</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>One place for every $/lb figure used anywhere in the analysis, with its basis. Real quotes in green; references in grey; superseded assumptions in amber.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1">
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>$/lb finished</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>Basis / terms</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>Date / reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="32" t="inlineStr">
+        <is>
+          <t>SNP Inc. (Durham, NC) — incumbent</t>
+        </is>
+      </c>
+      <c r="C6" s="33" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="D6" s="34" t="inlineStr">
+        <is>
+          <t>Delivered, all-in. 1/450-lb drum. ~2.9 drums/week today.</t>
+        </is>
+      </c>
+      <c r="E6" s="34" t="inlineStr">
+        <is>
+          <t>REAL QUOTE</t>
+        </is>
+      </c>
+      <c r="F6" s="34" t="inlineStr">
+        <is>
+          <t>Active sole source</t>
+        </is>
+      </c>
+      <c r="G6" s="34" t="inlineStr">
+        <is>
+          <t>SNP Estimate 012726-1</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="32" t="inlineStr">
+        <is>
+          <t>PCI Manufacturing (St. Louis, MO) — one 5-drum batch</t>
+        </is>
+      </c>
+      <c r="C7" s="33" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D7" s="34" t="inlineStr">
+        <is>
+          <t>One batch = 5 drums (2,250 lb). Confirm delivered/all-in and validity.</t>
+        </is>
+      </c>
+      <c r="E7" s="34" t="inlineStr">
+        <is>
+          <t>REAL QUOTE</t>
+        </is>
+      </c>
+      <c r="F7" s="34" t="inlineStr">
+        <is>
+          <t>Capable — experiment successful; not yet contracted</t>
+        </is>
+      </c>
+      <c r="G7" s="34" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="32" t="inlineStr">
+        <is>
+          <t>PCI Manufacturing — below one batch</t>
+        </is>
+      </c>
+      <c r="C8" s="33" t="n">
+        <v>6</v>
+      </c>
+      <c r="D8" s="34" t="inlineStr">
+        <is>
+          <t>Any order smaller than 5 drums (e.g. 1 drum/week).</t>
+        </is>
+      </c>
+      <c r="E8" s="34" t="inlineStr">
+        <is>
+          <t>REAL QUOTE</t>
+        </is>
+      </c>
+      <c r="F8" s="34" t="inlineStr">
+        <is>
+          <t>Uneconomic version</t>
+        </is>
+      </c>
+      <c r="G8" s="34" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="32" t="inlineStr">
+        <is>
+          <t>CJB Applied Technologies (Valdosta, GA)</t>
+        </is>
+      </c>
+      <c r="C9" s="33" t="n">
+        <v>8.42</v>
+      </c>
+      <c r="D9" s="34" t="inlineStr">
+        <is>
+          <t>$8.00–8.50/lb toll EXCLUDING materials + ~$75/drum resin = ~$8.42 landed. Qual fee $4,900.</t>
+        </is>
+      </c>
+      <c r="E9" s="34" t="inlineStr">
+        <is>
+          <t>REAL QUOTE</t>
+        </is>
+      </c>
+      <c r="F9" s="34" t="inlineStr">
+        <is>
+          <t>Eliminated on price (~11x SNP)</t>
+        </is>
+      </c>
+      <c r="G9" s="34" t="inlineStr">
+        <is>
+          <t>CJB email 'RE: mix test'</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="35" t="inlineStr">
+        <is>
+          <t>Market reference — LOW</t>
+        </is>
+      </c>
+      <c r="C10" s="36" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="D10" s="37" t="inlineStr">
+        <is>
+          <t>Resin floor + lean labor ($40/hr, 25% margin) + regional 1-drum freight</t>
+        </is>
+      </c>
+      <c r="E10" s="37" t="inlineStr">
+        <is>
+          <t>TRIANGULATED</t>
+        </is>
+      </c>
+      <c r="F10" s="37" t="inlineStr">
+        <is>
+          <t>Reference</t>
+        </is>
+      </c>
+      <c r="G10" s="37" t="inlineStr">
+        <is>
+          <t>Market Research tab (cost-scenarios workbook)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="35" t="inlineStr">
+        <is>
+          <t>Market reference — BASE</t>
+        </is>
+      </c>
+      <c r="C11" s="36" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="D11" s="37" t="inlineStr">
+        <is>
+          <t>Same build-up at typical conversion</t>
+        </is>
+      </c>
+      <c r="E11" s="37" t="inlineStr">
+        <is>
+          <t>TRIANGULATED</t>
+        </is>
+      </c>
+      <c r="F11" s="37" t="inlineStr">
+        <is>
+          <t>Reference</t>
+        </is>
+      </c>
+      <c r="G11" s="37" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="B12" s="35" t="inlineStr">
+        <is>
+          <t>Market reference — HIGH</t>
+        </is>
+      </c>
+      <c r="C12" s="36" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="D12" s="37" t="inlineStr">
+        <is>
+          <t>Anchored by retail comp ~$2.03/lb bulk PVA solution + freight</t>
+        </is>
+      </c>
+      <c r="E12" s="37" t="inlineStr">
+        <is>
+          <t>TRIANGULATED</t>
+        </is>
+      </c>
+      <c r="F12" s="37" t="inlineStr">
+        <is>
+          <t>Reference</t>
+        </is>
+      </c>
+      <c r="G12" s="37" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="B13" s="35" t="inlineStr">
+        <is>
+          <t>Material floor</t>
+        </is>
+      </c>
+      <c r="C13" s="36" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="D13" s="37" t="inlineStr">
+        <is>
+          <t>PVA resin $1.26–1.60/lb x 11% solids = $0.16–0.20</t>
+        </is>
+      </c>
+      <c r="E13" s="37" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
+        </is>
+      </c>
+      <c r="F13" s="37" t="inlineStr">
+        <is>
+          <t>Reference</t>
+        </is>
+      </c>
+      <c r="G13" s="37" t="inlineStr">
+        <is>
+          <t>ChemAnalyst / IMARC 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="38" t="inlineStr">
+        <is>
+          <t>July 2026 assumption (KPI deck)</t>
+        </is>
+      </c>
+      <c r="C14" s="39" t="n">
+        <v>1.125</v>
+      </c>
+      <c r="D14" s="40" t="inlineStr">
+        <is>
+          <t>'$1.00–1.25/lb, ~35% share, ~$6–12k/yr insurance'</t>
+        </is>
+      </c>
+      <c r="E14" s="40" t="inlineStr">
+        <is>
+          <t>ASSUMPTION</t>
+        </is>
+      </c>
+      <c r="F14" s="40" t="inlineStr">
+        <is>
+          <t>SUPERSEDED by PCI quote</t>
+        </is>
+      </c>
+      <c r="G14" s="40" t="inlineStr">
+        <is>
+          <t>KPI review deck 2026-07-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="38" t="inlineStr">
+        <is>
+          <t>Pre-quote forecast (this deck, Sept)</t>
+        </is>
+      </c>
+      <c r="C15" s="39" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="D15" s="40" t="inlineStr">
+        <is>
+          <t>$2.50 low / $3.75 mid / $5.00 high</t>
+        </is>
+      </c>
+      <c r="E15" s="40" t="inlineStr">
+        <is>
+          <t>ASSUMPTION</t>
+        </is>
+      </c>
+      <c r="F15" s="40" t="inlineStr">
+        <is>
+          <t>SUPERSEDED by PCI quote (quote = mid)</t>
+        </is>
+      </c>
+      <c r="G15" s="40" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B2:I31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="46" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="2">
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>What PCI's real quote means — Year 1 and five years</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Second source at one-third of demand = 50 drums/yr = 10 batches of 5. Formulas reference Inputs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1">
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Scenario</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Drums to PCI / yr</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>PCI $/lb</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>PCI annual $</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>SNP annual $ (retained)</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>Total $</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>Premium vs all-SNP</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>x today's spend</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="11" t="inlineStr">
+        <is>
+          <t>All-SNP (today)</t>
+        </is>
+      </c>
+      <c r="C6" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="21">
+        <f>SNPlb</f>
+        <v/>
+      </c>
+      <c r="E6" s="15">
+        <f>C6*DrumLb*D6</f>
+        <v/>
+      </c>
+      <c r="F6" s="15">
+        <f>(LbWk*Weeks-C6*DrumLb)*SNPlb</f>
+        <v/>
+      </c>
+      <c r="G6" s="15">
+        <f>E6+F6</f>
+        <v/>
+      </c>
+      <c r="H6" s="15">
+        <f>G6-LbWk*Weeks*SNPlb</f>
+        <v/>
+      </c>
+      <c r="I6" s="41">
+        <f>H6/(LbWk*Weeks*SNPlb)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="42" t="inlineStr">
+        <is>
+          <t>A — PCI at 1/3, 5-drum batches (10/yr)</t>
+        </is>
+      </c>
+      <c r="C7" s="43" t="n">
+        <v>50</v>
+      </c>
+      <c r="D7" s="44">
+        <f>PCIq</f>
+        <v/>
+      </c>
+      <c r="E7" s="45">
+        <f>C7*DrumLb*D7</f>
+        <v/>
+      </c>
+      <c r="F7" s="45">
+        <f>(LbWk*Weeks-C7*DrumLb)*SNPlb</f>
+        <v/>
+      </c>
+      <c r="G7" s="45">
+        <f>E7+F7</f>
+        <v/>
+      </c>
+      <c r="H7" s="45">
+        <f>G7-LbWk*Weeks*SNPlb</f>
+        <v/>
+      </c>
+      <c r="I7" s="46">
+        <f>H7/(LbWk*Weeks*SNPlb)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="11" t="inlineStr">
+        <is>
+          <t>A — PCI 1 drum/week, below-batch price</t>
+        </is>
+      </c>
+      <c r="C8" s="12" t="n">
+        <v>52</v>
+      </c>
+      <c r="D8" s="21">
+        <f>PCIsub</f>
+        <v/>
+      </c>
+      <c r="E8" s="15">
+        <f>C8*DrumLb*D8</f>
+        <v/>
+      </c>
+      <c r="F8" s="15">
+        <f>(LbWk*Weeks-C8*DrumLb)*SNPlb</f>
+        <v/>
+      </c>
+      <c r="G8" s="15">
+        <f>E8+F8</f>
+        <v/>
+      </c>
+      <c r="H8" s="15">
+        <f>G8-LbWk*Weeks*SNPlb</f>
+        <v/>
+      </c>
+      <c r="I8" s="41">
+        <f>H8/(LbWk*Weeks*SNPlb)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="11" t="inlineStr">
+        <is>
+          <t>A — PCI at 1/3 but below-batch price (for reference)</t>
+        </is>
+      </c>
+      <c r="C9" s="12" t="n">
+        <v>50</v>
+      </c>
+      <c r="D9" s="21">
+        <f>PCIsub</f>
+        <v/>
+      </c>
+      <c r="E9" s="15">
+        <f>C9*DrumLb*D9</f>
+        <v/>
+      </c>
+      <c r="F9" s="15">
+        <f>(LbWk*Weeks-C9*DrumLb)*SNPlb</f>
+        <v/>
+      </c>
+      <c r="G9" s="15">
+        <f>E9+F9</f>
+        <v/>
+      </c>
+      <c r="H9" s="15">
+        <f>G9-LbWk*Weeks*SNPlb</f>
+        <v/>
+      </c>
+      <c r="I9" s="41">
+        <f>H9/(LbWk*Weeks*SNPlb)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="11" t="inlineStr">
+        <is>
+          <t>CJB at 1/3 (for scale)</t>
+        </is>
+      </c>
+      <c r="C10" s="12" t="n">
+        <v>50</v>
+      </c>
+      <c r="D10" s="21">
+        <f>CJBlb</f>
+        <v/>
+      </c>
+      <c r="E10" s="15">
+        <f>C10*DrumLb*D10</f>
+        <v/>
+      </c>
+      <c r="F10" s="15">
+        <f>(LbWk*Weeks-C10*DrumLb)*SNPlb</f>
+        <v/>
+      </c>
+      <c r="G10" s="15">
+        <f>E10+F10</f>
+        <v/>
+      </c>
+      <c r="H10" s="15">
+        <f>G10-LbWk*Weeks*SNPlb</f>
+        <v/>
+      </c>
+      <c r="I10" s="41">
+        <f>H10/(LbWk*Weeks*SNPlb)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="47" t="inlineStr">
+        <is>
+          <t>Five years at 1/3 share, PCI $3.50, volume +10%/yr</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="30" customHeight="1">
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Year</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>Volume (lb)</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>Lb to PCI (1/3)</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>Batches of 5 (rounded)</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>Premium ($2.75/lb x lb to PCI)</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>Cumulative</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" s="12">
+        <f>LbWk*Weeks*(1+Growth)^(1-1)</f>
+        <v/>
+      </c>
+      <c r="D14" s="12">
+        <f>C14/3</f>
+        <v/>
+      </c>
+      <c r="E14" s="12">
+        <f>ROUND(D14/DrumLb/PCIbatch,0)</f>
+        <v/>
+      </c>
+      <c r="F14" s="15">
+        <f>D14*(PCIq-SNPlb)</f>
+        <v/>
+      </c>
+      <c r="G14" s="15">
+        <f>F14</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="C15" s="12">
+        <f>LbWk*Weeks*(1+Growth)^(2-1)</f>
+        <v/>
+      </c>
+      <c r="D15" s="12">
+        <f>C15/3</f>
+        <v/>
+      </c>
+      <c r="E15" s="12">
+        <f>ROUND(D15/DrumLb/PCIbatch,0)</f>
+        <v/>
+      </c>
+      <c r="F15" s="15">
+        <f>D15*(PCIq-SNPlb)</f>
+        <v/>
+      </c>
+      <c r="G15" s="15">
+        <f>G14+F15</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="C16" s="12">
+        <f>LbWk*Weeks*(1+Growth)^(3-1)</f>
+        <v/>
+      </c>
+      <c r="D16" s="12">
+        <f>C16/3</f>
+        <v/>
+      </c>
+      <c r="E16" s="12">
+        <f>ROUND(D16/DrumLb/PCIbatch,0)</f>
+        <v/>
+      </c>
+      <c r="F16" s="15">
+        <f>D16*(PCIq-SNPlb)</f>
+        <v/>
+      </c>
+      <c r="G16" s="15">
+        <f>G15+F16</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="C17" s="12">
+        <f>LbWk*Weeks*(1+Growth)^(4-1)</f>
+        <v/>
+      </c>
+      <c r="D17" s="12">
+        <f>C17/3</f>
+        <v/>
+      </c>
+      <c r="E17" s="12">
+        <f>ROUND(D17/DrumLb/PCIbatch,0)</f>
+        <v/>
+      </c>
+      <c r="F17" s="15">
+        <f>D17*(PCIq-SNPlb)</f>
+        <v/>
+      </c>
+      <c r="G17" s="15">
+        <f>G16+F17</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="C18" s="12">
+        <f>LbWk*Weeks*(1+Growth)^(5-1)</f>
+        <v/>
+      </c>
+      <c r="D18" s="12">
+        <f>C18/3</f>
+        <v/>
+      </c>
+      <c r="E18" s="12">
+        <f>ROUND(D18/DrumLb/PCIbatch,0)</f>
+        <v/>
+      </c>
+      <c r="F18" s="15">
+        <f>D18*(PCIq-SNPlb)</f>
+        <v/>
+      </c>
+      <c r="G18" s="15">
+        <f>G17+F18</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="47" t="inlineStr">
+        <is>
+          <t>Break-even — outage cost that justifies the premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="30" customHeight="1">
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>Premium (Y1)</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>p = 2%</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>p = 5%</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>p = 10%</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>p = 20%</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="15">
+        <f>H7</f>
+        <v/>
+      </c>
+      <c r="C22" s="15">
+        <f>B22/0.02</f>
+        <v/>
+      </c>
+      <c r="D22" s="15">
+        <f>B22/0.05</f>
+        <v/>
+      </c>
+      <c r="E22" s="15">
+        <f>B22/0.1</f>
+        <v/>
+      </c>
+      <c r="F22" s="15">
+        <f>B22/0.2</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="47" t="inlineStr">
+        <is>
+          <t>Block-rotation logistics of a 5-drum batch (shelf life 18 days)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="17" t="inlineStr">
+        <is>
+          <t>Batch size (lb)</t>
+        </is>
+      </c>
+      <c r="C25" s="12">
+        <f>PCIbatch*DrumLb</f>
+        <v/>
+      </c>
+      <c r="D25" s="2" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="B26" s="17" t="inlineStr">
+        <is>
+          <t>Days of FULL demand in one batch</t>
+        </is>
+      </c>
+      <c r="C26" s="48">
+        <f>B25/(LbWk/7)</f>
+        <v/>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>Must be consumed within the 18-day shelf life -&gt; use at full rate on receipt</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="17" t="inlineStr">
+        <is>
+          <t>Cycle length at 1/3 share (weeks)</t>
+        </is>
+      </c>
+      <c r="C27" s="48">
+        <f>B25/(LbWk/3)</f>
+        <v/>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>One PCI batch every ~5 weeks</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" s="17" t="inlineStr">
+        <is>
+          <t>Weeks on SNP material per cycle</t>
+        </is>
+      </c>
+      <c r="C28" s="48">
+        <f>B27-B25/LbWk</f>
+        <v/>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>SNP sees a ~12-day gap every cycle: LUMPY demand</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="17" t="inlineStr">
+        <is>
+          <t>Days to consume a batch at 2/3 rate (needs 30-day shelf life)</t>
+        </is>
+      </c>
+      <c r="C29" s="48">
+        <f>B25/(LbWk*2/3/7)</f>
+        <v/>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>With a validated 30-day life, SNP can keep supplying at 1/3 rate during a PCI batch -&gt; smoother</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="17" t="inlineStr">
+        <is>
+          <t>One qualification batch — cost</t>
+        </is>
+      </c>
+      <c r="C30" s="15">
+        <f>B25*PCIq</f>
+        <v/>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>A single production-scale batch (Option B-plus)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" s="17" t="inlineStr">
+        <is>
+          <t>One qualification batch — premium over SNP</t>
+        </is>
+      </c>
+      <c r="C31" s="15">
+        <f>B25*(PCIq-SNPlb)</f>
+        <v/>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>~4% of annual volume; invisible to SNP's year</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B2:D16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="100" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="2">
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>PCI Manufacturing — qualification experiment record</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>What was tested, what was found, what is still open. Source: email-chain summary 2026-09-22 + quote 2026-09-28.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1">
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Attribute</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>Result / detail</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="32" customHeight="1">
+      <c r="B6" s="32" t="inlineStr">
+        <is>
+          <t>Capability — 90–95 °C cook</t>
+        </is>
+      </c>
+      <c r="C6" s="34" t="inlineStr">
+        <is>
+          <t>PROVEN</t>
+        </is>
+      </c>
+      <c r="D6" s="34" t="inlineStr">
+        <is>
+          <t>Lab batches produced; dissolution achieved</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="32" customHeight="1">
+      <c r="B7" s="32" t="inlineStr">
+        <is>
+          <t>Viscosity (primary concern)</t>
+        </is>
+      </c>
+      <c r="C7" s="34" t="inlineStr">
+        <is>
+          <t>ROOT CAUSE FOUND</t>
+        </is>
+      </c>
+      <c r="D7" s="34" t="inlineStr">
+        <is>
+          <t>First sample 2,420 cP vs ~1,000 target; dilution to 10.8% solids -&gt; 1,590 cP; cause = elevated solids from water loss during processing; fix = water adjustment at end of mix</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="32" customHeight="1">
+      <c r="B8" s="32" t="inlineStr">
+        <is>
+          <t>Agreed fresh-material spec</t>
+        </is>
+      </c>
+      <c r="C8" s="34" t="inlineStr">
+        <is>
+          <t>LOCKED</t>
+        </is>
+      </c>
+      <c r="D8" s="34" t="inlineStr">
+        <is>
+          <t>11% total solids; 900–1,100 cP fresh (Brookfield #3, 10 rpm, 25 °C); &lt;2,500 cP ceiling</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="32" customHeight="1">
+      <c r="B9" s="38" t="inlineStr">
+        <is>
+          <t>Colour</t>
+        </is>
+      </c>
+      <c r="C9" s="40" t="inlineStr">
+        <is>
+          <t>NOT A CRITERION</t>
+        </is>
+      </c>
+      <c r="D9" s="40" t="inlineStr">
+        <is>
+          <t>No formal spec; minor mismatch acceptable</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="32" customHeight="1">
+      <c r="B10" s="38" t="inlineStr">
+        <is>
+          <t>Shelf-life study</t>
+        </is>
+      </c>
+      <c r="C10" s="40" t="inlineStr">
+        <is>
+          <t>REQUESTED</t>
+        </is>
+      </c>
+      <c r="D10" s="40" t="inlineStr">
+        <is>
+          <t>Viscosity every 3–5 days; trend to usable life (18 vs 30 days matters for batch logistics)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="32" customHeight="1">
+      <c r="B11" s="38" t="inlineStr">
+        <is>
+          <t>Hydrogel compression strength</t>
+        </is>
+      </c>
+      <c r="C11" s="40" t="inlineStr">
+        <is>
+          <t>PLANNED</t>
+        </is>
+      </c>
+      <c r="D11" s="40" t="inlineStr">
+        <is>
+          <t>vs current material — must hold on 100% PCI material under block rotation</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="32" customHeight="1">
+      <c r="B12" s="49" t="inlineStr">
+        <is>
+          <t>Cleaning / residual film</t>
+        </is>
+      </c>
+      <c r="C12" s="50" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="D12" s="50" t="inlineStr">
+        <is>
+          <t>Film observed during processing; vinegar partially effective; procedure not final</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="32" customHeight="1">
+      <c r="B13" s="49" t="inlineStr">
+        <is>
+          <t>Viscometer method basis</t>
+        </is>
+      </c>
+      <c r="C13" s="50" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="D13" s="50" t="inlineStr">
+        <is>
+          <t>10 vs 60 rpm, LV vs RV series — all cP comparisons depend on it</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="32" customHeight="1">
+      <c r="B14" s="32" t="inlineStr">
+        <is>
+          <t>Commercial — price</t>
+        </is>
+      </c>
+      <c r="C14" s="34" t="inlineStr">
+        <is>
+          <t>QUOTED</t>
+        </is>
+      </c>
+      <c r="D14" s="34" t="inlineStr">
+        <is>
+          <t>$3.50/lb at one 5-drum batch; $6.00/lb below a batch</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="32" customHeight="1">
+      <c r="B15" s="49" t="inlineStr">
+        <is>
+          <t>Commercial — terms to confirm</t>
+        </is>
+      </c>
+      <c r="C15" s="50" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="D15" s="50" t="inlineStr">
+        <is>
+          <t>Delivered/all-in? Validity? ~10 batches/yr on a ~5-week rhythm acceptable? Crisis ramp to ~3 batches/month? Resin grade/producer (sub-tier convergence with SNP)?</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="32" customHeight="1">
+      <c r="B16" s="38" t="inlineStr">
+        <is>
+          <t>What PCI has invested (unpaid)</t>
+        </is>
+      </c>
+      <c r="C16" s="40" t="inlineStr">
+        <is>
+          <t>NOTED</t>
+        </is>
+      </c>
+      <c r="D16" s="40" t="inlineStr">
+        <is>
+          <t>Two+ lab batches, dilution study, method work, revised process — months of engineering on a ~$50k/yr account</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1288,7 +2601,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1663,7 +2976,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1856,7 +3169,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2034,7 +3347,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/PVA second supplier initiative/PVA_Second_Supplier_Leadership_Model.xlsx
+++ b/PVA second supplier initiative/PVA_Second_Supplier_Leadership_Model.xlsx
@@ -7,15 +7,17 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Inputs" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Supplier Quotes" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PCI Quote Scenarios" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PCI Experiment" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5-Year" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sensitivity" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SNP Re-price" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Break-even" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Options" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Inputs" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Supplier Quotes" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Market Study" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PCI Quote Scenarios" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PCI Experiment" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5-Year" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sensitivity" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SNP Re-price" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Break-even" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Options" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames>
     <definedName name="DrumLb">Inputs!$C$6</definedName>
@@ -185,7 +187,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="68">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -265,6 +267,35 @@
     <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="4" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -630,32 +661,32 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:D30"/>
+  <dimension ref="B2:D29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="52" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="78" customWidth="1" min="4" max="4"/>
+    <col width="58" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>Second-Supplier Decision — Inputs</t>
+          <t>Summary — the figures on the leadership slides (all formulas; change Inputs and this tab follows)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Yellow = editable. PVA = polyvinyl alcohol. SNP Inc. = incumbent. PCI Manufacturing = candidate second source. The second source gets the LARGER of 1/3 of demand and its 1-drum/week minimum — or nothing.</t>
+          <t>Second source = one-third of demand rounded down to whole 5-drum batches (Year 1: 10 batches = 50 drums = 22,500 lb), identical in every option. Internal hours and one-time costs are on the slides, not here.</t>
         </is>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1">
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Input</t>
+          <t>Figure</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
@@ -665,349 +696,746 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>Source / note</t>
+          <t>Where it is used</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>Drum net weight (lb)</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="n">
-        <v>450</v>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>Confirmed (SNP Inc.: 1/450-lb drum)</t>
+      <c r="B6" s="11" t="inlineStr">
+        <is>
+          <t>Demand, Year 1 (lb)</t>
+        </is>
+      </c>
+      <c r="C6" s="51">
+        <f>LbWk*Weeks</f>
+        <v/>
+      </c>
+      <c r="D6" s="52" t="inlineStr">
+        <is>
+          <t>Slide 5 — identical in every bar</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>SNP Inc. price ($/lb delivered, all-in)</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>Real quote — SNP Estimate 012726-1</t>
+      <c r="B7" s="11" t="inlineStr">
+        <is>
+          <t>Demand, Year 1 (drums)</t>
+        </is>
+      </c>
+      <c r="C7" s="53">
+        <f>LbWk*Weeks/DrumLb</f>
+        <v/>
+      </c>
+      <c r="D7" s="52" t="inlineStr">
+        <is>
+          <t>Slide 5</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>Demand today (lb/week)</t>
-        </is>
-      </c>
-      <c r="C8" s="5" t="n">
-        <v>1300</v>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>Confirmed 2026-06-26</t>
+      <c r="B8" s="11" t="inlineStr">
+        <is>
+          <t>Second source, Year 1 (lb)</t>
+        </is>
+      </c>
+      <c r="C8" s="51">
+        <f>EffShare*LbWk*Weeks</f>
+        <v/>
+      </c>
+      <c r="D8" s="52" t="inlineStr">
+        <is>
+          <t>Slide 5 — every option</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>Weeks / year</t>
-        </is>
-      </c>
-      <c r="C9" s="5" t="n">
-        <v>52</v>
-      </c>
-      <c r="D9" s="2" t="inlineStr"/>
+      <c r="B9" s="11" t="inlineStr">
+        <is>
+          <t>Second source (drums / batches)</t>
+        </is>
+      </c>
+      <c r="C9" s="52">
+        <f>ROUND(EffShare*LbWk*Weeks/DrumLb,0)&amp;" drums / "&amp;ROUND(EffShare*LbWk*Weeks/(DrumLb*PCIbatch),0)&amp;" batches of 5"</f>
+        <v/>
+      </c>
+      <c r="D9" s="52" t="inlineStr">
+        <is>
+          <t>Slides 3, 5, 7, 8</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>Volume growth per year</t>
-        </is>
-      </c>
-      <c r="C10" s="7" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>Leadership assumption</t>
+      <c r="B10" s="11" t="inlineStr">
+        <is>
+          <t>All-SNP annual spend (today)</t>
+        </is>
+      </c>
+      <c r="C10" s="54">
+        <f>LbWk*Weeks*SNPlb</f>
+        <v/>
+      </c>
+      <c r="D10" s="52" t="inlineStr">
+        <is>
+          <t>Slide 5</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>Smallest volume a second source will accept (drums/week)</t>
-        </is>
-      </c>
-      <c r="C11" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>Supplier condition — below this they will not engage</t>
+      <c r="B11" s="11" t="inlineStr">
+        <is>
+          <t>SNP Inc. retained spend (2/3) — same in every option</t>
+        </is>
+      </c>
+      <c r="C11" s="54">
+        <f>(1-EffShare)*LbWk*Weeks*SNPlb</f>
+        <v/>
+      </c>
+      <c r="D11" s="52" t="inlineStr">
+        <is>
+          <t>Slide 5</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  = share of today's demand</t>
-        </is>
-      </c>
-      <c r="C12" s="8">
-        <f>MinDrumsWk*DrumLb/LbWk</f>
-        <v/>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>~35%. This is the smallest insurance available.</t>
+      <c r="B12" s="11" t="inlineStr">
+        <is>
+          <t>Option A annual — PCI $3.50</t>
+        </is>
+      </c>
+      <c r="C12" s="54">
+        <f>(1-EffShare)*LbWk*Weeks*SNPlb+EffShare*LbWk*Weeks*PCIq</f>
+        <v/>
+      </c>
+      <c r="D12" s="52" t="inlineStr">
+        <is>
+          <t>Slides 5, 8</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>Target share of demand (Option A)</t>
-        </is>
-      </c>
-      <c r="C13" s="9" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>One-third. Year 1: 1/3 = 0.96 drums/wk, so the minimum (1.0) governs; from Year 2 the 1/3 governs.</t>
+      <c r="B13" s="42" t="inlineStr">
+        <is>
+          <t>Premium vs today (Year 1)</t>
+        </is>
+      </c>
+      <c r="C13" s="55">
+        <f>B12-B10</f>
+        <v/>
+      </c>
+      <c r="D13" s="56" t="inlineStr">
+        <is>
+          <t>Slides 5, 6, 8, 11</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  = effective share, Year 1</t>
-        </is>
-      </c>
-      <c r="C14" s="8">
-        <f>MAX(Share,MinShare)</f>
-        <v/>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>max(target, minimum)</t>
+      <c r="B14" s="11" t="inlineStr">
+        <is>
+          <t>Premium as % of today's spend</t>
+        </is>
+      </c>
+      <c r="C14" s="57">
+        <f>B13/B10</f>
+        <v/>
+      </c>
+      <c r="D14" s="52" t="inlineStr">
+        <is>
+          <t>Slide 5</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>PCI price — LOW ($/lb)</t>
-        </is>
-      </c>
-      <c r="C15" s="6" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>Forecast floor</t>
+      <c r="B15" s="11" t="inlineStr">
+        <is>
+          <t>Same 1/3 at PCI's below-batch price $6.00</t>
+        </is>
+      </c>
+      <c r="C15" s="54">
+        <f>(1-EffShare)*LbWk*Weeks*SNPlb+EffShare*LbWk*Weeks*PCIsub</f>
+        <v/>
+      </c>
+      <c r="D15" s="52" t="inlineStr">
+        <is>
+          <t>Slide 5</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>PCI price — MID ($/lb)</t>
-        </is>
-      </c>
-      <c r="C16" s="6" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>Midpoint of range</t>
+      <c r="B16" s="11" t="inlineStr">
+        <is>
+          <t>Same 1/3 at CJB $8.42 (for scale)</t>
+        </is>
+      </c>
+      <c r="C16" s="54">
+        <f>(1-EffShare)*LbWk*Weeks*SNPlb+EffShare*LbWk*Weeks*CJBlb</f>
+        <v/>
+      </c>
+      <c r="D16" s="52" t="inlineStr">
+        <is>
+          <t>Slide 5</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="B17" s="4" t="inlineStr">
-        <is>
-          <t>PCI price — HIGH ($/lb)</t>
-        </is>
-      </c>
-      <c r="C17" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>Forecast ceiling</t>
+      <c r="B17" s="11" t="inlineStr">
+        <is>
+          <t>Five-year premium at $3.50 (exact third, +10%/yr, undiscounted)</t>
+        </is>
+      </c>
+      <c r="C17" s="54">
+        <f>'5-Year'!L11</f>
+        <v/>
+      </c>
+      <c r="D17" s="52" t="inlineStr">
+        <is>
+          <t>Slides 6, 8</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="4" t="inlineStr">
-        <is>
-          <t>Market reference — LOW ($/lb)</t>
-        </is>
-      </c>
-      <c r="C18" s="6" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>Triangulated (resin floor + labor bottom-up)</t>
+      <c r="B18" s="11" t="inlineStr">
+        <is>
+          <t>Break-even avoided loss @ p = 10%/yr</t>
+        </is>
+      </c>
+      <c r="C18" s="54">
+        <f>B13/0.10</f>
+        <v/>
+      </c>
+      <c r="D18" s="52" t="inlineStr">
+        <is>
+          <t>Slide 11</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t>Market reference — BASE ($/lb)</t>
-        </is>
-      </c>
-      <c r="C19" s="6" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>Triangulated</t>
+      <c r="B19" s="11" t="inlineStr">
+        <is>
+          <t>Break-even avoided loss @ p = 5%/yr</t>
+        </is>
+      </c>
+      <c r="C19" s="54">
+        <f>B13/0.05</f>
+        <v/>
+      </c>
+      <c r="D19" s="52" t="inlineStr">
+        <is>
+          <t>Slide 11</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="B20" s="4" t="inlineStr">
-        <is>
-          <t>Market reference — HIGH ($/lb)</t>
-        </is>
-      </c>
-      <c r="C20" s="6" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>Triangulated (retail ceiling)</t>
+      <c r="B20" s="11" t="inlineStr">
+        <is>
+          <t>Break-even avoided loss @ p = 2%/yr</t>
+        </is>
+      </c>
+      <c r="C20" s="54">
+        <f>B13/0.02</f>
+        <v/>
+      </c>
+      <c r="D20" s="52" t="inlineStr">
+        <is>
+          <t>Appendix</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="B21" s="4" t="inlineStr">
-        <is>
-          <t>CJB Applied Technologies quote, landed ($/lb) — reference</t>
-        </is>
-      </c>
-      <c r="C21" s="6" t="n">
-        <v>8.42</v>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>$8-8.50 toll excl. materials + $75/drum resin; ~11x SNP</t>
+      <c r="B21" s="11" t="inlineStr">
+        <is>
+          <t>One 5-drum batch — cost (gross)</t>
+        </is>
+      </c>
+      <c r="C21" s="54">
+        <f>PCIbatch*DrumLb*PCIq</f>
+        <v/>
+      </c>
+      <c r="D21" s="52" t="inlineStr">
+        <is>
+          <t>Slides 6, 8, 9, 11</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="B22" s="4" t="inlineStr">
-        <is>
-          <t>One-time qualification cost ($)</t>
-        </is>
-      </c>
-      <c r="C22" s="10" t="n">
-        <v>15000</v>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER — engineering hrs, samples, hydrogel tests, quality agreement. Confirm.</t>
+      <c r="B22" s="11" t="inlineStr">
+        <is>
+          <t>One 5-drum batch — premium over SNP</t>
+        </is>
+      </c>
+      <c r="C22" s="54">
+        <f>PCIbatch*DrumLb*(PCIq-SNPlb)</f>
+        <v/>
+      </c>
+      <c r="D22" s="52" t="inlineStr">
+        <is>
+          <t>Slides 6, 9</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="B23" s="4" t="inlineStr">
-        <is>
-          <t>Disruption probability per year (for break-even)</t>
-        </is>
-      </c>
-      <c r="C23" s="7" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER — leadership judgement</t>
+      <c r="B23" s="11" t="inlineStr">
+        <is>
+          <t>One batch as % of annual volume</t>
+        </is>
+      </c>
+      <c r="C23" s="58">
+        <f>PCIbatch*DrumLb/(LbWk*Weeks)</f>
+        <v/>
+      </c>
+      <c r="D23" s="52" t="inlineStr">
+        <is>
+          <t>Slides 6, 8</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="B24" s="4" t="inlineStr">
-        <is>
-          <t>Cost of a 6-month SNP Inc. outage ($)</t>
-        </is>
-      </c>
-      <c r="C24" s="10" t="n">
-        <v>500000</v>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER — revenue at risk + expedite + line-down. NEEDED FROM FINANCE/OPS.</t>
+      <c r="B24" s="11" t="inlineStr">
+        <is>
+          <t>Batch = days of full demand</t>
+        </is>
+      </c>
+      <c r="C24" s="59">
+        <f>PCIbatch*DrumLb/(LbWk/7)</f>
+        <v/>
+      </c>
+      <c r="D24" s="52" t="inlineStr">
+        <is>
+          <t>Slides 3, 7</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="11" t="inlineStr">
+        <is>
+          <t>Cycle at one-third (weeks)</t>
+        </is>
+      </c>
+      <c r="C25" s="59">
+        <f>PCIbatch*DrumLb/(LbWk/3)</f>
+        <v/>
+      </c>
+      <c r="D25" s="52" t="inlineStr">
+        <is>
+          <t>Slide 7</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="B26" s="31" t="inlineStr">
-        <is>
-          <t>PCI MANUFACTURING — REAL QUOTE (2026-09-28)</t>
+      <c r="B26" s="11" t="inlineStr">
+        <is>
+          <t>Premium if PCI were $1.50/lb (trigger)</t>
+        </is>
+      </c>
+      <c r="C26" s="54">
+        <f>EffShare*LbWk*Weeks*(1.5-SNPlb)</f>
+        <v/>
+      </c>
+      <c r="D26" s="52" t="inlineStr">
+        <is>
+          <t>Slide 11</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="B27" s="4" t="inlineStr">
-        <is>
-          <t>PCI quoted price — one batch of 5 drums ($/lb)</t>
-        </is>
-      </c>
-      <c r="C27" s="6" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>Real quote. CONFIRM: delivered? materials, drum, freight included? validity period?</t>
+      <c r="B27" s="11" t="inlineStr">
+        <is>
+          <t>Option 3 — one batch/yr: gross / premium</t>
+        </is>
+      </c>
+      <c r="C27" s="52">
+        <f>PCIbatch*DrumLb*PCIq&amp;" / "&amp;PCIbatch*DrumLb*(PCIq-SNPlb)</f>
+        <v/>
+      </c>
+      <c r="D27" s="52" t="inlineStr">
+        <is>
+          <t>Slides 6, 8, 9, 11</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="B28" s="4" t="inlineStr">
-        <is>
-          <t>PCI price — orders below one batch ($/lb)</t>
-        </is>
-      </c>
-      <c r="C28" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>Real quote. Makes any sub-batch (e.g. 1 drum/week) uneconomic.</t>
+      <c r="B28" s="11" t="inlineStr">
+        <is>
+          <t>Option 3 — two batches/yr: gross / premium</t>
+        </is>
+      </c>
+      <c r="C28" s="52">
+        <f>2*PCIbatch*DrumLb*PCIq&amp;" / "&amp;2*PCIbatch*DrumLb*(PCIq-SNPlb)</f>
+        <v/>
+      </c>
+      <c r="D28" s="52" t="inlineStr">
+        <is>
+          <t>Slides 8, 9</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="B29" s="4" t="inlineStr">
-        <is>
-          <t>PCI batch size (drums)</t>
-        </is>
-      </c>
-      <c r="C29" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>One batch = 5 drums = 2,250 lb = ~12 days of full demand</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>The $2.50 / $3.75 / $5.00 rows above were the pre-quote forecast; keep for history. The quote ($3.50) sits at the forecast mid.</t>
+      <c r="B29" s="11" t="inlineStr">
+        <is>
+          <t>Option 3 — share of volume at 1 / 2 batches</t>
+        </is>
+      </c>
+      <c r="C29" s="52">
+        <f>TEXT(PCIbatch*DrumLb/(LbWk*Weeks),"0.0%")&amp;" / "&amp;TEXT(2*PCIbatch*DrumLb/(LbWk*Weeks),"0.0%")</f>
+        <v/>
+      </c>
+      <c r="D29" s="52" t="inlineStr">
+        <is>
+          <t>Slide 8</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B2:G13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="2">
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>Is the insurance worth it? Premium vs (probability x avoided loss)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Option A is justified only if: annual premium &lt;= P(SNP disruption in a year) x loss the second source would AVOID. Full avoidance counts only with PCI's written ramp commitment; with ~1/3 coverage, the outage must be ~3x larger.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1">
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Option A price case</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Annual premium</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>p = 2%</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>p = 5%</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>p = 10%</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>p = 20%</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="11" t="inlineStr">
+        <is>
+          <t>Sensitivity $2.50</t>
+        </is>
+      </c>
+      <c r="C6" s="15">
+        <f>LbWk*Weeks*EffShare*(PCIlo-SNPlb)</f>
+        <v/>
+      </c>
+      <c r="D6" s="15">
+        <f>C6/0.02</f>
+        <v/>
+      </c>
+      <c r="E6" s="15">
+        <f>C6/0.05</f>
+        <v/>
+      </c>
+      <c r="F6" s="15">
+        <f>C6/0.1</f>
+        <v/>
+      </c>
+      <c r="G6" s="15">
+        <f>C6/0.2</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="11" t="inlineStr">
+        <is>
+          <t>PCI quote $3.50</t>
+        </is>
+      </c>
+      <c r="C7" s="15">
+        <f>LbWk*Weeks*EffShare*(PCImid-SNPlb)</f>
+        <v/>
+      </c>
+      <c r="D7" s="15">
+        <f>C7/0.02</f>
+        <v/>
+      </c>
+      <c r="E7" s="15">
+        <f>C7/0.05</f>
+        <v/>
+      </c>
+      <c r="F7" s="15">
+        <f>C7/0.1</f>
+        <v/>
+      </c>
+      <c r="G7" s="15">
+        <f>C7/0.2</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="11" t="inlineStr">
+        <is>
+          <t>Sensitivity $5.00</t>
+        </is>
+      </c>
+      <c r="C8" s="15">
+        <f>LbWk*Weeks*EffShare*(PCIhi-SNPlb)</f>
+        <v/>
+      </c>
+      <c r="D8" s="15">
+        <f>C8/0.02</f>
+        <v/>
+      </c>
+      <c r="E8" s="15">
+        <f>C8/0.05</f>
+        <v/>
+      </c>
+      <c r="F8" s="15">
+        <f>C8/0.1</f>
+        <v/>
+      </c>
+      <c r="G8" s="15">
+        <f>C8/0.2</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Read: each cell = the avoided loss an SNP outage would have to cause for the premium to pay off. Compare to Inputs 'Cost of a 6-month SNP Inc. outage'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="17" t="inlineStr">
+        <is>
+          <t>Expected annual loss with NO second source = Pdis x Dcost:</t>
+        </is>
+      </c>
+      <c r="D12" s="20">
+        <f>Pdis*Dcost</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="17" t="inlineStr">
+        <is>
+          <t>Verdict @ PCI MID:</t>
+        </is>
+      </c>
+      <c r="D13">
+        <f>IF(D12&gt;=C7,"Option A is justified","Premium exceeds expected loss — Option B")</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B2:D13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="42" customWidth="1" min="3" max="3"/>
+    <col width="42" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="2">
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>The options, side by side (Year 1, PCI quote $3.50; second source = 10 whole 5-drum batches = 50 drums)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Legacy A/B layout = Option 1 / Option 2. Option 3 (keep-alive: 1–2 batches of 5 drums a year at $3.50, no volume term so far) is on the PCI Quote Scenarios and Summary tabs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1">
+      <c r="B5" s="3" t="inlineStr"/>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>A — Second source (PCI Manufacturing) at ~1/3</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>B — Single source (SNP Inc.) + strengthen</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="17" t="inlineStr">
+        <is>
+          <t>Annual purchase cost</t>
+        </is>
+      </c>
+      <c r="C6" s="29">
+        <f>LbWk*Weeks*(1-EffShare)*SNPlb+LbWk*Weeks*EffShare*PCImid</f>
+        <v/>
+      </c>
+      <c r="D6" s="29">
+        <f>LbWk*Weeks*SNPlb</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="17" t="inlineStr">
+        <is>
+          <t>Premium vs today</t>
+        </is>
+      </c>
+      <c r="C7" s="29">
+        <f>B6-LbWk*Weeks*SNPlb</f>
+        <v/>
+      </c>
+      <c r="D7" s="30" t="inlineStr">
+        <is>
+          <t>0 (+ small continuity spend)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="17" t="inlineStr">
+        <is>
+          <t>One-time qualification</t>
+        </is>
+      </c>
+      <c r="C8" s="29">
+        <f>QualCost</f>
+        <v/>
+      </c>
+      <c r="D8" s="30" t="inlineStr">
+        <is>
+          <t>0 (plan/document only)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="17" t="inlineStr">
+        <is>
+          <t>5-yr premium (10% growth)</t>
+        </is>
+      </c>
+      <c r="C9" s="29">
+        <f>'5-Year'!L11</f>
+        <v/>
+      </c>
+      <c r="D9" s="30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="17" t="inlineStr">
+        <is>
+          <t>Volume still exposed if SNP fails</t>
+        </is>
+      </c>
+      <c r="C10" s="30" t="inlineStr">
+        <is>
+          <t>~2/3 (until PCI ramps — unconfirmed)</t>
+        </is>
+      </c>
+      <c r="D10" s="30" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="17" t="inlineStr">
+        <is>
+          <t>Time to recover if SNP fails</t>
+        </is>
+      </c>
+      <c r="C11" s="30" t="inlineStr">
+        <is>
+          <t>weeks (PCI ramp)</t>
+        </is>
+      </c>
+      <c r="D11" s="30" t="inlineStr">
+        <is>
+          <t>~3-6 months cold start (decays after ~12 months idle); ~2-3 with a yearly re-check batch</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="17" t="inlineStr">
+        <is>
+          <t>Signal to SNP Inc.</t>
+        </is>
+      </c>
+      <c r="C12" s="30" t="inlineStr">
+        <is>
+          <t>Lost a third of its volume; cadence level only if we carry a small rolling stock</t>
+        </is>
+      </c>
+      <c r="D12" s="30" t="inlineStr">
+        <is>
+          <t>Deeper partnership</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="17" t="inlineStr">
+        <is>
+          <t>Compliance posture</t>
+        </is>
+      </c>
+      <c r="C13" s="30" t="inlineStr">
+        <is>
+          <t>Strong</t>
+        </is>
+      </c>
+      <c r="D13" s="30" t="inlineStr">
+        <is>
+          <t>Defensible if risk + plan documented</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1450,399 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:G15"/>
+  <dimension ref="B2:D30"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="52" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="78" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="2">
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>Second-Supplier Decision — Inputs</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Yellow = editable. PVA = polyvinyl alcohol. SNP Inc. = incumbent. PCI Manufacturing = candidate second source. The second source gets the LARGER of 1/3 of demand and its 1-drum/week minimum — or nothing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1">
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Input</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>Source / note</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>Drum net weight (lb)</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>450</v>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Confirmed (SNP Inc.: 1/450-lb drum)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>SNP Inc. price ($/lb delivered, all-in)</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Real quote — SNP Estimate 012726-1</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>Demand today (lb/week)</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>1300</v>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Confirmed 2026-06-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>Weeks / year</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>52</v>
+      </c>
+      <c r="D9" s="2" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>Volume growth per year</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Leadership assumption</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>Legacy: pre-quote supplier minimum (drums/week) — superseded by batch pricing (rows 27–29)</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Kept for history. The real constraint is whole 5-drum batches at $3.50; anything smaller is $6.00/lb.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  = share of today's demand</t>
+        </is>
+      </c>
+      <c r="C12" s="8">
+        <f>MinDrumsWk*DrumLb/LbWk</f>
+        <v/>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Legacy (34.6%). Not used by any headline figure.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>Target share of demand (Option A)</t>
+        </is>
+      </c>
+      <c r="C13" s="9" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>One-third of demand is the target share for Option A.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  = effective share, Year 1</t>
+        </is>
+      </c>
+      <c r="C14" s="8">
+        <f>ROUNDDOWN(Share*LbWk*Weeks/(DrumLb*PCIbatch),0)*DrumLb*PCIbatch/(LbWk*Weeks)</f>
+        <v/>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>One-third rounded DOWN to whole 5-drum batches: Year 1 = 10 batches = 50 drums = 22,500 lb = 33.3% — the figure on the slides.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>PCI price — LOW ($/lb)</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Sensitivity band below the quote</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>PCI price — MID ($/lb)</t>
+        </is>
+      </c>
+      <c r="C16" s="6">
+        <f>PCIq</f>
+        <v/>
+      </c>
+      <c r="D16" s="2">
+        <f> the real quote (row 27). Every 'MID' figure in the legacy tabs now uses $3.50.</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>PCI price — HIGH ($/lb)</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>Sensitivity band above the quote</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>Market — HIGH quantity, bulk/tote ($/lb)</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>Verified market study 2026-09-28 — comparable pre-mixed PVA solutions; range 0.28-1.04, n=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>Market — COMPETITIVE quantity, drum scale ($/lb)</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>Verified market study 2026-09-28 — comparable pre-mixed PVA solutions; range 2.20-5.03, n=7</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>Market — LOW quantity, small packs ($/lb)</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>Verified market study 2026-09-28 — comparable pre-mixed PVA solutions; range 3.19-5.87, n=32</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>CJB Applied Technologies quote, landed ($/lb) — reference</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="n">
+        <v>8.42</v>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>$8-8.50 toll excl. materials + $75/drum resin; ~11x SNP</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>One-time qualification cost ($)</t>
+        </is>
+      </c>
+      <c r="C22" s="10" t="n">
+        <v>15000</v>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>PLACEHOLDER — engineering hrs, samples, hydrogel tests, quality agreement. Confirm.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>Disruption probability per year (for break-even)</t>
+        </is>
+      </c>
+      <c r="C23" s="7" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>PLACEHOLDER — leadership judgement</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>Cost of a 6-month SNP Inc. outage ($)</t>
+        </is>
+      </c>
+      <c r="C24" s="10" t="n">
+        <v>500000</v>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>PLACEHOLDER — revenue at risk + expedite + line-down. NEEDED FROM FINANCE/OPS.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="31" t="inlineStr">
+        <is>
+          <t>PCI MANUFACTURING — REAL QUOTE (2026-09-28)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>PCI quoted price — one batch of 5 drums ($/lb)</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>Real quote. CONFIRM: delivered? materials, drum, freight included? validity period?</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>PCI price — orders below one batch ($/lb)</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>Real quote. Makes any sub-batch (e.g. 1 drum/week) uneconomic.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>PCI batch size (drums)</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>One batch = 5 drums = 2,250 lb = ~12 days of full demand</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>The $2.50 / $5.00 rows are kept as a sensitivity band; MID points at the real quote ($3.50), within 7% of the pre-quote mid-case ($3.75).</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B2:G18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="2" max="2"/>
@@ -1180,7 +2000,7 @@
       </c>
       <c r="D9" s="34" t="inlineStr">
         <is>
-          <t>$8.00–8.50/lb toll EXCLUDING materials + ~$75/drum resin = ~$8.42 landed. Qual fee $4,900.</t>
+          <t>$8.00–8.50/lb toll EXCLUDING materials + ~$75/drum resin = ~$8.42 landed. Their trial would have cost $6,400 (per Oscar, 28 Sep; the email thread recorded a $4,900 qualification fee + $700 x 7 batch credit) — we declined, so their capability was never corroborated.</t>
         </is>
       </c>
       <c r="E9" s="34" t="inlineStr">
@@ -1190,7 +2010,7 @@
       </c>
       <c r="F9" s="34" t="inlineStr">
         <is>
-          <t>Eliminated on price (~11x SNP)</t>
+          <t>Eliminated on price 2026-08-04 (~11x SNP); trial declined</t>
         </is>
       </c>
       <c r="G9" s="34" t="inlineStr">
@@ -1202,170 +2022,252 @@
     <row r="10">
       <c r="B10" s="35" t="inlineStr">
         <is>
-          <t>Market reference — LOW</t>
-        </is>
-      </c>
-      <c r="C10" s="36" t="n">
-        <v>0.85</v>
+          <t>Brenntag (distributor) — trial blends, Nov 2025 onward</t>
+        </is>
+      </c>
+      <c r="C10" s="36" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
       </c>
       <c r="D10" s="37" t="inlineStr">
         <is>
-          <t>Resin floor + lean labor ($40/hr, 25% margin) + regional 1-drum freight</t>
+          <t>Tried our formula (125 grade and the requested grade): viscosity above range, unreadable on their viscometer. They stalled; no quote was ever received. Mar 2026: sent us a 125-grade resin sample instead.</t>
         </is>
       </c>
       <c r="E10" s="37" t="inlineStr">
         <is>
+          <t>NO QUOTE</t>
+        </is>
+      </c>
+      <c r="F10" s="37" t="inlineStr">
+        <is>
+          <t>Never met viscosity; no quote</t>
+        </is>
+      </c>
+      <c r="G10" s="37" t="inlineStr">
+        <is>
+          <t>Sam (Brenntag) emails</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="60" t="inlineStr">
+        <is>
+          <t>Market — COMPETITIVE quantity (drum scale, 30–55 gal)</t>
+        </is>
+      </c>
+      <c r="C11" s="61" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="D11" s="62" t="inlineStr">
+        <is>
+          <t>Inferred from comparable pre-mixed PVA solutions sold today; range 2.20-5.03; n=7</t>
+        </is>
+      </c>
+      <c r="E11" s="62" t="inlineStr">
+        <is>
+          <t>MARKET STUDY</t>
+        </is>
+      </c>
+      <c r="F11" s="62" t="inlineStr">
+        <is>
+          <t>Reference — see Market Study tab</t>
+        </is>
+      </c>
+      <c r="G11" s="62" t="inlineStr">
+        <is>
+          <t>Verified market study 2026-09-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="60" t="inlineStr">
+        <is>
+          <t>Market — LOW quantity (pints to 5-gal pails)</t>
+        </is>
+      </c>
+      <c r="C12" s="61" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="D12" s="62" t="inlineStr">
+        <is>
+          <t>Retail/lab packs; range 3.19-5.87; n=32</t>
+        </is>
+      </c>
+      <c r="E12" s="62" t="inlineStr">
+        <is>
+          <t>MARKET STUDY</t>
+        </is>
+      </c>
+      <c r="F12" s="62" t="inlineStr">
+        <is>
+          <t>Reference — see Market Study tab</t>
+        </is>
+      </c>
+      <c r="G12" s="62" t="inlineStr">
+        <is>
+          <t>Verified market study 2026-09-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="60" t="inlineStr">
+        <is>
+          <t>Market — HIGH quantity (totes / bulk / tonnage)</t>
+        </is>
+      </c>
+      <c r="C13" s="61" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="D13" s="62" t="inlineStr">
+        <is>
+          <t>Bulk and contract pricing; range 0.28-1.04; n=5. Quality/regulatory context differs.</t>
+        </is>
+      </c>
+      <c r="E13" s="62" t="inlineStr">
+        <is>
+          <t>MARKET STUDY</t>
+        </is>
+      </c>
+      <c r="F13" s="62" t="inlineStr">
+        <is>
+          <t>Reference — see Market Study tab</t>
+        </is>
+      </c>
+      <c r="G13" s="62" t="inlineStr">
+        <is>
+          <t>Verified market study 2026-09-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="35" t="inlineStr">
+        <is>
+          <t>— Superseded / historical references (kept for the record) —</t>
+        </is>
+      </c>
+      <c r="C14" s="36" t="inlineStr"/>
+      <c r="D14" s="37" t="inlineStr"/>
+      <c r="E14" s="37" t="inlineStr"/>
+      <c r="F14" s="37" t="inlineStr"/>
+      <c r="G14" s="37" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="B15" s="35" t="inlineStr">
+        <is>
+          <t>Triangulated market LOW / BASE / HIGH (Sept)</t>
+        </is>
+      </c>
+      <c r="C15" s="36" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="D15" s="37" t="inlineStr">
+        <is>
+          <t>$0.85 / $1.40 / $2.55 — resin floor + labor build-up + retail ceiling</t>
+        </is>
+      </c>
+      <c r="E15" s="37" t="inlineStr">
+        <is>
           <t>TRIANGULATED</t>
         </is>
       </c>
-      <c r="F10" s="37" t="inlineStr">
-        <is>
-          <t>Reference</t>
-        </is>
-      </c>
-      <c r="G10" s="37" t="inlineStr">
+      <c r="F15" s="37" t="inlineStr">
+        <is>
+          <t>SUPERSEDED by market study</t>
+        </is>
+      </c>
+      <c r="G15" s="37" t="inlineStr">
         <is>
           <t>Market Research tab (cost-scenarios workbook)</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="B11" s="35" t="inlineStr">
-        <is>
-          <t>Market reference — BASE</t>
-        </is>
-      </c>
-      <c r="C11" s="36" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="D11" s="37" t="inlineStr">
-        <is>
-          <t>Same build-up at typical conversion</t>
-        </is>
-      </c>
-      <c r="E11" s="37" t="inlineStr">
-        <is>
-          <t>TRIANGULATED</t>
-        </is>
-      </c>
-      <c r="F11" s="37" t="inlineStr">
-        <is>
-          <t>Reference</t>
-        </is>
-      </c>
-      <c r="G11" s="37" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="B12" s="35" t="inlineStr">
-        <is>
-          <t>Market reference — HIGH</t>
-        </is>
-      </c>
-      <c r="C12" s="36" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="D12" s="37" t="inlineStr">
-        <is>
-          <t>Anchored by retail comp ~$2.03/lb bulk PVA solution + freight</t>
-        </is>
-      </c>
-      <c r="E12" s="37" t="inlineStr">
-        <is>
-          <t>TRIANGULATED</t>
-        </is>
-      </c>
-      <c r="F12" s="37" t="inlineStr">
-        <is>
-          <t>Reference</t>
-        </is>
-      </c>
-      <c r="G12" s="37" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="B13" s="35" t="inlineStr">
+    <row r="16">
+      <c r="B16" s="35" t="inlineStr">
         <is>
           <t>Material floor</t>
         </is>
       </c>
-      <c r="C13" s="36" t="n">
+      <c r="C16" s="36" t="n">
         <v>0.18</v>
       </c>
-      <c r="D13" s="37" t="inlineStr">
-        <is>
-          <t>PVA resin $1.26–1.60/lb x 11% solids = $0.16–0.20</t>
-        </is>
-      </c>
-      <c r="E13" s="37" t="inlineStr">
+      <c r="D16" s="37" t="inlineStr">
+        <is>
+          <t>PVA resin $1.26–1.60/lb x 11% solids = $0.14–0.18 (upper bound plotted)</t>
+        </is>
+      </c>
+      <c r="E16" s="37" t="inlineStr">
         <is>
           <t>DERIVED</t>
         </is>
       </c>
-      <c r="F13" s="37" t="inlineStr">
-        <is>
-          <t>Reference</t>
-        </is>
-      </c>
-      <c r="G13" s="37" t="inlineStr">
+      <c r="F16" s="37" t="inlineStr">
+        <is>
+          <t>Reference only</t>
+        </is>
+      </c>
+      <c r="G16" s="37" t="inlineStr">
         <is>
           <t>ChemAnalyst / IMARC 2026</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="B14" s="38" t="inlineStr">
-        <is>
-          <t>July 2026 assumption (KPI deck)</t>
-        </is>
-      </c>
-      <c r="C14" s="39" t="n">
+    <row r="17">
+      <c r="B17" s="38" t="inlineStr">
+        <is>
+          <t>July 2026 assumption (key performance indicator (KPI) review deck)</t>
+        </is>
+      </c>
+      <c r="C17" s="39" t="n">
         <v>1.125</v>
       </c>
-      <c r="D14" s="40" t="inlineStr">
+      <c r="D17" s="40" t="inlineStr">
         <is>
           <t>'$1.00–1.25/lb, ~35% share, ~$6–12k/yr insurance'</t>
         </is>
       </c>
-      <c r="E14" s="40" t="inlineStr">
+      <c r="E17" s="40" t="inlineStr">
         <is>
           <t>ASSUMPTION</t>
         </is>
       </c>
-      <c r="F14" s="40" t="inlineStr">
+      <c r="F17" s="40" t="inlineStr">
         <is>
           <t>SUPERSEDED by PCI quote</t>
         </is>
       </c>
-      <c r="G14" s="40" t="inlineStr">
+      <c r="G17" s="40" t="inlineStr">
         <is>
           <t>KPI review deck 2026-07-09</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="B15" s="38" t="inlineStr">
+    <row r="18">
+      <c r="B18" s="38" t="inlineStr">
         <is>
           <t>Pre-quote forecast (this deck, Sept)</t>
         </is>
       </c>
-      <c r="C15" s="39" t="n">
+      <c r="C18" s="39" t="n">
         <v>3.75</v>
       </c>
-      <c r="D15" s="40" t="inlineStr">
+      <c r="D18" s="40" t="inlineStr">
         <is>
           <t>$2.50 low / $3.75 mid / $5.00 high</t>
         </is>
       </c>
-      <c r="E15" s="40" t="inlineStr">
+      <c r="E18" s="40" t="inlineStr">
         <is>
           <t>ASSUMPTION</t>
         </is>
       </c>
-      <c r="F15" s="40" t="inlineStr">
+      <c r="F18" s="40" t="inlineStr">
         <is>
           <t>SUPERSEDED by PCI quote (quote = mid)</t>
         </is>
       </c>
-      <c r="G15" s="40" t="inlineStr">
+      <c r="G18" s="40" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -1376,13 +2278,3835 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:I31"/>
+  <dimension ref="B2:L83"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="9" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="60" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="2">
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>Market study — comparable pre-mixed PVA solutions, by quantity tier</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Every data point verified against its URL; $/lb of SOLUTION (8.5 lb/gal unless weight given). Polyvinyl ALCOHOL only — acetate glues, resin powder and films excluded.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1">
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Tier</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Recommended $/lb for chart</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>Range</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>Basis</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="64" t="inlineStr">
+        <is>
+          <t>COMPETITIVE quantity — drum scale (30–55 gal)</t>
+        </is>
+      </c>
+      <c r="C6" s="65" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="D6" s="66" t="inlineStr">
+        <is>
+          <t>2.20-5.03</t>
+        </is>
+      </c>
+      <c r="E6" s="66" t="n">
+        <v>7</v>
+      </c>
+      <c r="F6" s="66" t="inlineStr">
+        <is>
+          <t>Largest openly priced US trade lot of pre-mixed PVA solution (20 gal, US Composites); 4–20 gal US trade lots n=7, min–max $2.20–5.03; a 55-gal drum can only sit at or below this</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="64" t="inlineStr">
+        <is>
+          <t>LOW quantity — pints to 5-gal pails</t>
+        </is>
+      </c>
+      <c r="C7" s="65" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="D7" s="66" t="inlineStr">
+        <is>
+          <t>3.19-5.87</t>
+        </is>
+      </c>
+      <c r="E7" s="66" t="n">
+        <v>32</v>
+      </c>
+      <c r="F7" s="66" t="inlineStr">
+        <is>
+          <t>Median of 32 US unit-pack prices (1 gal and smaller) of 7–13% PVA composites-release solutions; whisker = interquartile range; shipping excluded</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="64" t="inlineStr">
+        <is>
+          <t>HIGH quantity — totes / bulk / tonnage</t>
+        </is>
+      </c>
+      <c r="C8" s="65" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="D8" s="66" t="inlineStr">
+        <is>
+          <t>0.28-1.04</t>
+        </is>
+      </c>
+      <c r="E8" s="66" t="n">
+        <v>5</v>
+      </c>
+      <c r="F8" s="66" t="inlineStr">
+        <is>
+          <t>Median of 5 ton-scale offers (FOB China / ex-works India, 1,000-kg MOQ) before ocean freight, duty and packaging; no US/EU vendor publishes tote pricing</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="30" customHeight="1">
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>Vendor</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>Chemistry</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>Solids %</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>Pack</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>Pack lb</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>Price $</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>$ / lb</t>
+        </is>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>Tier</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t>Verdict</t>
+        </is>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t>URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="52" t="inlineStr">
+        <is>
+          <t>Partall PVA Parting Film #10 (PVA-104)</t>
+        </is>
+      </c>
+      <c r="C12" s="52" t="inlineStr">
+        <is>
+          <t>Merritt Supply</t>
+        </is>
+      </c>
+      <c r="D12" s="52" t="inlineStr">
+        <is>
+          <t>PVA solution</t>
+        </is>
+      </c>
+      <c r="E12" s="52" t="inlineStr">
+        <is>
+          <t>7-8%</t>
+        </is>
+      </c>
+      <c r="F12" s="52" t="inlineStr">
+        <is>
+          <t>1 gal</t>
+        </is>
+      </c>
+      <c r="G12" s="51" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="H12" s="67" t="n">
+        <v>17.89</v>
+      </c>
+      <c r="I12" s="67" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="J12" s="52" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K12" s="52" t="inlineStr">
+        <is>
+          <t>PLAUSIBLE (captcha-blocked)</t>
+        </is>
+      </c>
+      <c r="L12" s="52" t="inlineStr">
+        <is>
+          <t>https://merrittsupply.com/product/partall-pva-parting-film-gallon-pn-pva-104/</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="52" t="inlineStr">
+        <is>
+          <t>Partall Coverall Film (REXC-CF128)</t>
+        </is>
+      </c>
+      <c r="C13" s="52" t="inlineStr">
+        <is>
+          <t>US Composites</t>
+        </is>
+      </c>
+      <c r="D13" s="52" t="inlineStr">
+        <is>
+          <t>PVA solution</t>
+        </is>
+      </c>
+      <c r="E13" s="52" t="inlineStr">
+        <is>
+          <t>11-13%</t>
+        </is>
+      </c>
+      <c r="F13" s="52" t="inlineStr">
+        <is>
+          <t>1 gal</t>
+        </is>
+      </c>
+      <c r="G13" s="51" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="H13" s="67" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="I13" s="67" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="J13" s="52" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K13" s="52" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="L13" s="52" t="inlineStr">
+        <is>
+          <t>https://www.uscomposites.com/moldrelease.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="52" t="inlineStr">
+        <is>
+          <t>Partall Coverall Film Purple</t>
+        </is>
+      </c>
+      <c r="C14" s="52" t="inlineStr">
+        <is>
+          <t>Fiberglass Supply Depot</t>
+        </is>
+      </c>
+      <c r="D14" s="52" t="inlineStr">
+        <is>
+          <t>PVA solution</t>
+        </is>
+      </c>
+      <c r="E14" s="52" t="inlineStr">
+        <is>
+          <t>11-13%</t>
+        </is>
+      </c>
+      <c r="F14" s="52" t="inlineStr">
+        <is>
+          <t>1 gal</t>
+        </is>
+      </c>
+      <c r="G14" s="51" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="H14" s="67" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="I14" s="67" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="J14" s="52" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K14" s="52" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="L14" s="52" t="inlineStr">
+        <is>
+          <t>https://fiberglasssupplydepot.com/Partall-Coverall-Film-Purple.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="52" t="inlineStr">
+        <is>
+          <t>Partall Coverall Film</t>
+        </is>
+      </c>
+      <c r="C15" s="52" t="inlineStr">
+        <is>
+          <t>The Engineer Guy</t>
+        </is>
+      </c>
+      <c r="D15" s="52" t="inlineStr">
+        <is>
+          <t>PVA solution</t>
+        </is>
+      </c>
+      <c r="E15" s="52" t="inlineStr">
+        <is>
+          <t>11-13%</t>
+        </is>
+      </c>
+      <c r="F15" s="52" t="inlineStr">
+        <is>
+          <t>1 gal</t>
+        </is>
+      </c>
+      <c r="G15" s="51" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="H15" s="67" t="n">
+        <v>22.25</v>
+      </c>
+      <c r="I15" s="67" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="J15" s="52" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K15" s="52" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="L15" s="52" t="inlineStr">
+        <is>
+          <t>https://theengineerguy.com/partall-coverall-gallon/</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="52" t="inlineStr">
+        <is>
+          <t>Partall Film #10 PVA Green</t>
+        </is>
+      </c>
+      <c r="C16" s="52" t="inlineStr">
+        <is>
+          <t>The Engineer Guy</t>
+        </is>
+      </c>
+      <c r="D16" s="52" t="inlineStr">
+        <is>
+          <t>PVA solution</t>
+        </is>
+      </c>
+      <c r="E16" s="52" t="inlineStr">
+        <is>
+          <t>7-8%</t>
+        </is>
+      </c>
+      <c r="F16" s="52" t="inlineStr">
+        <is>
+          <t>1 gal</t>
+        </is>
+      </c>
+      <c r="G16" s="51" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="H16" s="67" t="n">
+        <v>22.25</v>
+      </c>
+      <c r="I16" s="67" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="J16" s="52" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K16" s="52" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="L16" s="52" t="inlineStr">
+        <is>
+          <t>https://theengineerguy.com/partall-film-10-pva-green-gallon/</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="52" t="inlineStr">
+        <is>
+          <t>Partall Film #10 (REX-PVA105)</t>
+        </is>
+      </c>
+      <c r="C17" s="52" t="inlineStr">
+        <is>
+          <t>US Composites</t>
+        </is>
+      </c>
+      <c r="D17" s="52" t="inlineStr">
+        <is>
+          <t>PVA solution</t>
+        </is>
+      </c>
+      <c r="E17" s="52" t="inlineStr">
+        <is>
+          <t>7-8%</t>
+        </is>
+      </c>
+      <c r="F17" s="52" t="inlineStr">
+        <is>
+          <t>1 gal</t>
+        </is>
+      </c>
+      <c r="G17" s="51" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="H17" s="67" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="I17" s="67" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="J17" s="52" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K17" s="52" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="L17" s="52" t="inlineStr">
+        <is>
+          <t>https://www.uscomposites.com/moldrelease.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="52" t="inlineStr">
+        <is>
+          <t>Partall Coverall Film (REX-PCF-1G)</t>
+        </is>
+      </c>
+      <c r="C18" s="52" t="inlineStr">
+        <is>
+          <t>Infinity FRP Supply</t>
+        </is>
+      </c>
+      <c r="D18" s="52" t="inlineStr">
+        <is>
+          <t>PVA solution</t>
+        </is>
+      </c>
+      <c r="E18" s="52" t="inlineStr">
+        <is>
+          <t>11-13%</t>
+        </is>
+      </c>
+      <c r="F18" s="52" t="inlineStr">
+        <is>
+          <t>1 gal</t>
+        </is>
+      </c>
+      <c r="G18" s="51" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="H18" s="67" t="n">
+        <v>25</v>
+      </c>
+      <c r="I18" s="67" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="J18" s="52" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K18" s="52" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="L18" s="52" t="inlineStr">
+        <is>
+          <t>https://www.infinityfrp.com/partall-coverall-film-1-gallon/</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="52" t="inlineStr">
+        <is>
+          <t>Rexco Partall Coverall Film Purple</t>
+        </is>
+      </c>
+      <c r="C19" s="52" t="inlineStr">
+        <is>
+          <t>Composite Envisions</t>
+        </is>
+      </c>
+      <c r="D19" s="52" t="inlineStr">
+        <is>
+          <t>PVA solution</t>
+        </is>
+      </c>
+      <c r="E19" s="52" t="inlineStr">
+        <is>
+          <t>11-13%</t>
+        </is>
+      </c>
+      <c r="F19" s="52" t="inlineStr">
+        <is>
+          <t>1 gal</t>
+        </is>
+      </c>
+      <c r="G19" s="51" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="H19" s="67" t="n">
+        <v>25.95</v>
+      </c>
+      <c r="I19" s="67" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="J19" s="52" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K19" s="52" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="L19" s="52" t="inlineStr">
+        <is>
+          <t>https://www.compositeenvisions.com/Rexco-Partall-Coverall-Film-Purple-1-Gal</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="52" t="inlineStr">
+        <is>
+          <t>Rexco Partall PVA #10</t>
+        </is>
+      </c>
+      <c r="C20" s="52" t="inlineStr">
+        <is>
+          <t>Composite Envisions</t>
+        </is>
+      </c>
+      <c r="D20" s="52" t="inlineStr">
+        <is>
+          <t>PVA solution</t>
+        </is>
+      </c>
+      <c r="E20" s="52" t="inlineStr">
+        <is>
+          <t>7-8%</t>
+        </is>
+      </c>
+      <c r="F20" s="52" t="inlineStr">
+        <is>
+          <t>1 gal</t>
+        </is>
+      </c>
+      <c r="G20" s="51" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="H20" s="67" t="n">
+        <v>25.67</v>
+      </c>
+      <c r="I20" s="67" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="J20" s="52" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K20" s="52" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="L20" s="52" t="inlineStr">
+        <is>
+          <t>https://www.compositeenvisions.com/Rexco-Partall-PVA-10-Spray-On-Mold-Release</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="52" t="inlineStr">
+        <is>
+          <t>Partall One-Coat PVA (high-solids, water-based)</t>
+        </is>
+      </c>
+      <c r="C21" s="52" t="inlineStr">
+        <is>
+          <t>Fiberglass Supply Depot</t>
+        </is>
+      </c>
+      <c r="D21" s="52" t="inlineStr">
+        <is>
+          <t>PVA solution</t>
+        </is>
+      </c>
+      <c r="E21" s="52" t="inlineStr">
+        <is>
+          <t>not stated (2-3x std)</t>
+        </is>
+      </c>
+      <c r="F21" s="52" t="inlineStr">
+        <is>
+          <t>1 gal</t>
+        </is>
+      </c>
+      <c r="G21" s="51" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="H21" s="67" t="n">
+        <v>28.99</v>
+      </c>
+      <c r="I21" s="67" t="n">
+        <v>3.41</v>
+      </c>
+      <c r="J21" s="52" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K21" s="52" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="L21" s="52" t="inlineStr">
+        <is>
+          <t>https://fiberglasssupplydepot.com/product/partall-r-one-coat-gallon.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="52" t="inlineStr">
+        <is>
+          <t>Partall Film #10</t>
+        </is>
+      </c>
+      <c r="C22" s="52" t="inlineStr">
+        <is>
+          <t>Fiberglass Supply Depot</t>
+        </is>
+      </c>
+      <c r="D22" s="52" t="inlineStr">
+        <is>
+          <t>PVA solution</t>
+        </is>
+      </c>
+      <c r="E22" s="52" t="inlineStr">
+        <is>
+          <t>7-8%</t>
+        </is>
+      </c>
+      <c r="F22" s="52" t="inlineStr">
+        <is>
+          <t>1 gal</t>
+        </is>
+      </c>
+      <c r="G22" s="51" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="H22" s="67" t="n">
+        <v>28.95</v>
+      </c>
+      <c r="I22" s="67" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="J22" s="52" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K22" s="52" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="L22" s="52" t="inlineStr">
+        <is>
+          <t>https://fiberglasssupplydepot.com/product/Partall-Film-10.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="52" t="inlineStr">
+        <is>
+          <t>Partall Film #10 PVA</t>
+        </is>
+      </c>
+      <c r="C23" s="52" t="inlineStr">
+        <is>
+          <t>Brick In The Yard</t>
+        </is>
+      </c>
+      <c r="D23" s="52" t="inlineStr">
+        <is>
+          <t>PVA solution</t>
+        </is>
+      </c>
+      <c r="E23" s="52" t="inlineStr">
+        <is>
+          <t>7-8%</t>
+        </is>
+      </c>
+      <c r="F23" s="52" t="inlineStr">
+        <is>
+          <t>1 gal</t>
+        </is>
+      </c>
+      <c r="G23" s="51" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="H23" s="67" t="n">
+        <v>29</v>
+      </c>
+      <c r="I23" s="67" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="J23" s="52" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K23" s="52" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="L23" s="52" t="inlineStr">
+        <is>
+          <t>https://www.brickintheyard.com/products/partall-film-10-pva-gallon</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="52" t="inlineStr">
+        <is>
+          <t>PVA Mold Release (Partall #10)</t>
+        </is>
+      </c>
+      <c r="C24" s="52" t="inlineStr">
+        <is>
+          <t>FGCI</t>
+        </is>
+      </c>
+      <c r="D24" s="52" t="inlineStr">
+        <is>
+          <t>PVA solution</t>
+        </is>
+      </c>
+      <c r="E24" s="52" t="inlineStr">
+        <is>
+          <t>7-8%</t>
+        </is>
+      </c>
+      <c r="F24" s="52" t="inlineStr">
+        <is>
+          <t>1 gal</t>
+        </is>
+      </c>
+      <c r="G24" s="51" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="H24" s="67" t="n">
+        <v>29.99</v>
+      </c>
+      <c r="I24" s="67" t="n">
+        <v>3.79</v>
+      </c>
+      <c r="J24" s="52" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K24" s="52" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="L24" s="52" t="inlineStr">
+        <is>
+          <t>https://fgci.com/product/pva-partall-mold-release/</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="52" t="inlineStr">
+        <is>
+          <t>Partall Coverall Film (REXC-CF032)</t>
+        </is>
+      </c>
+      <c r="C25" s="52" t="inlineStr">
+        <is>
+          <t>US Composites</t>
+        </is>
+      </c>
+      <c r="D25" s="52" t="inlineStr">
+        <is>
+          <t>PVA solution</t>
+        </is>
+      </c>
+      <c r="E25" s="52" t="inlineStr">
+        <is>
+          <t>11-13%</t>
+        </is>
+      </c>
+      <c r="F25" s="52" t="inlineStr">
+        <is>
+          <t>1 qt</t>
+        </is>
+      </c>
+      <c r="G25" s="51" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="H25" s="67" t="n">
+        <v>8.75</v>
+      </c>
+      <c r="I25" s="67" t="n">
+        <v>4.11</v>
+      </c>
+      <c r="J25" s="52" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K25" s="52" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="L25" s="52" t="inlineStr">
+        <is>
+          <t>https://www.uscomposites.com/moldrelease.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="52" t="inlineStr">
+        <is>
+          <t>Partall Film #10 (PVA10-G)</t>
+        </is>
+      </c>
+      <c r="C26" s="52" t="inlineStr">
+        <is>
+          <t>Express Composites</t>
+        </is>
+      </c>
+      <c r="D26" s="52" t="inlineStr">
+        <is>
+          <t>PVA solution</t>
+        </is>
+      </c>
+      <c r="E26" s="52" t="inlineStr">
+        <is>
+          <t>7-8%</t>
+        </is>
+      </c>
+      <c r="F26" s="52" t="inlineStr">
+        <is>
+          <t>1 gal</t>
+        </is>
+      </c>
+      <c r="G26" s="51" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="H26" s="67" t="n">
+        <v>32.99</v>
+      </c>
+      <c r="I26" s="67" t="n">
+        <v>4.17</v>
+      </c>
+      <c r="J26" s="52" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K26" s="52" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="L26" s="52" t="inlineStr">
+        <is>
+          <t>https://www.expresscomposites.com/partall-coverall-pva-release-film-1</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="52" t="inlineStr">
+        <is>
+          <t>PVA Partall Film #10 (RA-202-G)</t>
+        </is>
+      </c>
+      <c r="C27" s="52" t="inlineStr">
+        <is>
+          <t>CST The Composites Store</t>
+        </is>
+      </c>
+      <c r="D27" s="52" t="inlineStr">
+        <is>
+          <t>PVA solution</t>
+        </is>
+      </c>
+      <c r="E27" s="52" t="inlineStr">
+        <is>
+          <t>7-8%</t>
+        </is>
+      </c>
+      <c r="F27" s="52" t="inlineStr">
+        <is>
+          <t>1 gal</t>
+        </is>
+      </c>
+      <c r="G27" s="51" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="H27" s="67" t="n">
+        <v>36</v>
+      </c>
+      <c r="I27" s="67" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="J27" s="52" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K27" s="52" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="L27" s="52" t="inlineStr">
+        <is>
+          <t>https://www.cstsales.com/a-vacuum-supplies-mold-release.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" s="52" t="inlineStr">
+        <is>
+          <t>Partall Film #10 (REX-PVA103)</t>
+        </is>
+      </c>
+      <c r="C28" s="52" t="inlineStr">
+        <is>
+          <t>US Composites</t>
+        </is>
+      </c>
+      <c r="D28" s="52" t="inlineStr">
+        <is>
+          <t>PVA solution</t>
+        </is>
+      </c>
+      <c r="E28" s="52" t="inlineStr">
+        <is>
+          <t>7-8%</t>
+        </is>
+      </c>
+      <c r="F28" s="52" t="inlineStr">
+        <is>
+          <t>1 qt</t>
+        </is>
+      </c>
+      <c r="G28" s="51" t="n">
+        <v>2</v>
+      </c>
+      <c r="H28" s="67" t="n">
+        <v>9</v>
+      </c>
+      <c r="I28" s="67" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="J28" s="52" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K28" s="52" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="L28" s="52" t="inlineStr">
+        <is>
+          <t>https://www.uscomposites.com/moldrelease.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="52" t="inlineStr">
+        <is>
+          <t>#13 PVA Release Film (13-B)</t>
+        </is>
+      </c>
+      <c r="C29" s="52" t="inlineStr">
+        <is>
+          <t>Fibre Glast</t>
+        </is>
+      </c>
+      <c r="D29" s="52" t="inlineStr">
+        <is>
+          <t>PVA solution</t>
+        </is>
+      </c>
+      <c r="E29" s="52" t="inlineStr">
+        <is>
+          <t>not stated (~7-8%)</t>
+        </is>
+      </c>
+      <c r="F29" s="52" t="inlineStr">
+        <is>
+          <t>1 gal</t>
+        </is>
+      </c>
+      <c r="G29" s="51" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="H29" s="67" t="n">
+        <v>36.01</v>
+      </c>
+      <c r="I29" s="67" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="J29" s="52" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K29" s="52" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="L29" s="52" t="inlineStr">
+        <is>
+          <t>https://www.fibreglast.com/product/PVA_Release_Film_13</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="52" t="inlineStr">
+        <is>
+          <t>Partall Coverall (V208-G)</t>
+        </is>
+      </c>
+      <c r="C30" s="52" t="inlineStr">
+        <is>
+          <t>CST The Composites Store</t>
+        </is>
+      </c>
+      <c r="D30" s="52" t="inlineStr">
+        <is>
+          <t>PVA solution</t>
+        </is>
+      </c>
+      <c r="E30" s="52" t="inlineStr">
+        <is>
+          <t>11-13%</t>
+        </is>
+      </c>
+      <c r="F30" s="52" t="inlineStr">
+        <is>
+          <t>1 gal</t>
+        </is>
+      </c>
+      <c r="G30" s="51" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="H30" s="67" t="n">
+        <v>41.1</v>
+      </c>
+      <c r="I30" s="67" t="n">
+        <v>4.83</v>
+      </c>
+      <c r="J30" s="52" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K30" s="52" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="L30" s="52" t="inlineStr">
+        <is>
+          <t>https://www.cstsales.com/a-vacuum-supplies-mold-release.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" s="52" t="inlineStr">
+        <is>
+          <t>PVA Release (Partall #10 class)</t>
+        </is>
+      </c>
+      <c r="C31" s="52" t="inlineStr">
+        <is>
+          <t>Coast Fiber Tek (Canada)</t>
+        </is>
+      </c>
+      <c r="D31" s="52" t="inlineStr">
+        <is>
+          <t>PVA solution</t>
+        </is>
+      </c>
+      <c r="E31" s="52" t="inlineStr">
+        <is>
+          <t>~7-8%</t>
+        </is>
+      </c>
+      <c r="F31" s="52" t="inlineStr">
+        <is>
+          <t>4 L</t>
+        </is>
+      </c>
+      <c r="G31" s="51" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="H31" s="67" t="n">
+        <v>43.65</v>
+      </c>
+      <c r="I31" s="67" t="n">
+        <v>5.22</v>
+      </c>
+      <c r="J31" s="52" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K31" s="52" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="L31" s="52" t="inlineStr">
+        <is>
+          <t>https://fibertek.ca/products/pva-poly-vinyl-alcohol-release</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="52" t="inlineStr">
+        <is>
+          <t>PVA Release Film</t>
+        </is>
+      </c>
+      <c r="C32" s="52" t="inlineStr">
+        <is>
+          <t>Douglas and Sturgess</t>
+        </is>
+      </c>
+      <c r="D32" s="52" t="inlineStr">
+        <is>
+          <t>PVA solution</t>
+        </is>
+      </c>
+      <c r="E32" s="52" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="F32" s="52" t="inlineStr">
+        <is>
+          <t>1 gal</t>
+        </is>
+      </c>
+      <c r="G32" s="51" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="H32" s="67" t="n">
+        <v>47.5</v>
+      </c>
+      <c r="I32" s="67" t="n">
+        <v>5.59</v>
+      </c>
+      <c r="J32" s="52" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K32" s="52" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="L32" s="52" t="inlineStr">
+        <is>
+          <t>https://douglasandsturgess.com/products/p-v-a-5-gallon</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" s="52" t="inlineStr">
+        <is>
+          <t>Partall Parting Film #10</t>
+        </is>
+      </c>
+      <c r="C33" s="52" t="inlineStr">
+        <is>
+          <t>Fiberglass Site</t>
+        </is>
+      </c>
+      <c r="D33" s="52" t="inlineStr">
+        <is>
+          <t>PVA solution</t>
+        </is>
+      </c>
+      <c r="E33" s="52" t="inlineStr">
+        <is>
+          <t>7-8%</t>
+        </is>
+      </c>
+      <c r="F33" s="52" t="inlineStr">
+        <is>
+          <t>1 gal</t>
+        </is>
+      </c>
+      <c r="G33" s="51" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="H33" s="67" t="n">
+        <v>45.95</v>
+      </c>
+      <c r="I33" s="67" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="J33" s="52" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K33" s="52" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="L33" s="52" t="inlineStr">
+        <is>
+          <t>https://fiberglasssite.com/partall-parting-film-10-1-gallon-45-95/</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" s="52" t="inlineStr">
+        <is>
+          <t>Partall Film #10</t>
+        </is>
+      </c>
+      <c r="C34" s="52" t="inlineStr">
+        <is>
+          <t>True Composites</t>
+        </is>
+      </c>
+      <c r="D34" s="52" t="inlineStr">
+        <is>
+          <t>PVA solution</t>
+        </is>
+      </c>
+      <c r="E34" s="52" t="inlineStr">
+        <is>
+          <t>7-8%</t>
+        </is>
+      </c>
+      <c r="F34" s="52" t="inlineStr">
+        <is>
+          <t>1 gal</t>
+        </is>
+      </c>
+      <c r="G34" s="51" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="H34" s="67" t="n">
+        <v>45.95</v>
+      </c>
+      <c r="I34" s="67" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="J34" s="52" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K34" s="52" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="L34" s="52" t="inlineStr">
+        <is>
+          <t>https://www.truecomposites.com/products/partall-film-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="52" t="inlineStr">
+        <is>
+          <t>PVA Parting Film (Partall #10)</t>
+        </is>
+      </c>
+      <c r="C35" s="52" t="inlineStr">
+        <is>
+          <t>Blackburn Marine</t>
+        </is>
+      </c>
+      <c r="D35" s="52" t="inlineStr">
+        <is>
+          <t>PVA solution</t>
+        </is>
+      </c>
+      <c r="E35" s="52" t="inlineStr">
+        <is>
+          <t>7-8%</t>
+        </is>
+      </c>
+      <c r="F35" s="52" t="inlineStr">
+        <is>
+          <t>1 gal inferred</t>
+        </is>
+      </c>
+      <c r="G35" s="51" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="H35" s="67" t="n">
+        <v>46</v>
+      </c>
+      <c r="I35" s="67" t="n">
+        <v>5.81</v>
+      </c>
+      <c r="J35" s="52" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K35" s="52" t="inlineStr">
+        <is>
+          <t>PLAUSIBLE (size not stated)</t>
+        </is>
+      </c>
+      <c r="L35" s="52" t="inlineStr">
+        <is>
+          <t>https://www.blackburnmarine.com/product/1669/pva-parting-film</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" s="52" t="inlineStr">
+        <is>
+          <t>Partall #10 PVA (N12-2140)</t>
+        </is>
+      </c>
+      <c r="C36" s="52" t="inlineStr">
+        <is>
+          <t>Fiberglass Supply</t>
+        </is>
+      </c>
+      <c r="D36" s="52" t="inlineStr">
+        <is>
+          <t>PVA solution</t>
+        </is>
+      </c>
+      <c r="E36" s="52" t="inlineStr">
+        <is>
+          <t>7-8%</t>
+        </is>
+      </c>
+      <c r="F36" s="52" t="inlineStr">
+        <is>
+          <t>1 gal</t>
+        </is>
+      </c>
+      <c r="G36" s="51" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="H36" s="67" t="n">
+        <v>48.06</v>
+      </c>
+      <c r="I36" s="67" t="n">
+        <v>6.07</v>
+      </c>
+      <c r="J36" s="52" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K36" s="52" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="L36" s="52" t="inlineStr">
+        <is>
+          <t>https://fiberglasssupply.com/one-gallon-bottle-partall-10-pva/</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" s="52" t="inlineStr">
+        <is>
+          <t>Rexco Poly Vinyl Alcohol (RPA-PVA-GL)</t>
+        </is>
+      </c>
+      <c r="C37" s="52" t="inlineStr">
+        <is>
+          <t>Hamilton Marine</t>
+        </is>
+      </c>
+      <c r="D37" s="52" t="inlineStr">
+        <is>
+          <t>PVA solution</t>
+        </is>
+      </c>
+      <c r="E37" s="52" t="inlineStr">
+        <is>
+          <t>7-8%</t>
+        </is>
+      </c>
+      <c r="F37" s="52" t="inlineStr">
+        <is>
+          <t>1 gal</t>
+        </is>
+      </c>
+      <c r="G37" s="51" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="H37" s="67" t="n">
+        <v>48.29</v>
+      </c>
+      <c r="I37" s="67" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="J37" s="52" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K37" s="52" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="L37" s="52" t="inlineStr">
+        <is>
+          <t>https://shop.hamiltonmarine.com/products/poly-vinyl-alcohol-pva-gallon-28338.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" s="52" t="inlineStr">
+        <is>
+          <t>Partall Film #10</t>
+        </is>
+      </c>
+      <c r="C38" s="52" t="inlineStr">
+        <is>
+          <t>Fiberglass Warehouse</t>
+        </is>
+      </c>
+      <c r="D38" s="52" t="inlineStr">
+        <is>
+          <t>PVA solution</t>
+        </is>
+      </c>
+      <c r="E38" s="52" t="inlineStr">
+        <is>
+          <t>7-8%</t>
+        </is>
+      </c>
+      <c r="F38" s="52" t="inlineStr">
+        <is>
+          <t>1 gal</t>
+        </is>
+      </c>
+      <c r="G38" s="51" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="H38" s="67" t="n">
+        <v>49.95</v>
+      </c>
+      <c r="I38" s="67" t="n">
+        <v>6.31</v>
+      </c>
+      <c r="J38" s="52" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K38" s="52" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="L38" s="52" t="inlineStr">
+        <is>
+          <t>https://www.fiberglasswarehouse.com/products/partall-film-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" s="52" t="inlineStr">
+        <is>
+          <t>360 PVA Mold Release (LBI-360-G)</t>
+        </is>
+      </c>
+      <c r="C39" s="52" t="inlineStr">
+        <is>
+          <t>LBI Fiberglass</t>
+        </is>
+      </c>
+      <c r="D39" s="52" t="inlineStr">
+        <is>
+          <t>PVA solution</t>
+        </is>
+      </c>
+      <c r="E39" s="52" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="F39" s="52" t="inlineStr">
+        <is>
+          <t>1 gal</t>
+        </is>
+      </c>
+      <c r="G39" s="51" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="H39" s="67" t="n">
+        <v>60.71</v>
+      </c>
+      <c r="I39" s="67" t="n">
+        <v>7.14</v>
+      </c>
+      <c r="J39" s="52" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K39" s="52" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="L39" s="52" t="inlineStr">
+        <is>
+          <t>https://www.lbifiberglass.com/product/360-pva-mold-release-air-barrier/</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" s="52" t="inlineStr">
+        <is>
+          <t>PVA Mold Release (Partall #10)</t>
+        </is>
+      </c>
+      <c r="C40" s="52" t="inlineStr">
+        <is>
+          <t>Boat Crafters Company</t>
+        </is>
+      </c>
+      <c r="D40" s="52" t="inlineStr">
+        <is>
+          <t>PVA solution</t>
+        </is>
+      </c>
+      <c r="E40" s="52" t="inlineStr">
+        <is>
+          <t>7-8%</t>
+        </is>
+      </c>
+      <c r="F40" s="52" t="inlineStr">
+        <is>
+          <t>1 qt</t>
+        </is>
+      </c>
+      <c r="G40" s="51" t="n">
+        <v>2</v>
+      </c>
+      <c r="H40" s="67" t="n">
+        <v>15.89</v>
+      </c>
+      <c r="I40" s="67" t="n">
+        <v>8.029999999999999</v>
+      </c>
+      <c r="J40" s="52" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K40" s="52" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="L40" s="52" t="inlineStr">
+        <is>
+          <t>https://boatcrafterscompany.com/products/pva-polyvinyl-alcohol-mold-release-agent</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" s="52" t="inlineStr">
+        <is>
+          <t>PVA 1000 Mold Release (Ark)</t>
+        </is>
+      </c>
+      <c r="C41" s="52" t="inlineStr">
+        <is>
+          <t>Noah's Marine</t>
+        </is>
+      </c>
+      <c r="D41" s="52" t="inlineStr">
+        <is>
+          <t>PVA solution</t>
+        </is>
+      </c>
+      <c r="E41" s="52" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="F41" s="52" t="inlineStr">
+        <is>
+          <t>1 gal</t>
+        </is>
+      </c>
+      <c r="G41" s="51" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="H41" s="67" t="n">
+        <v>79</v>
+      </c>
+      <c r="I41" s="67" t="n">
+        <v>9.289999999999999</v>
+      </c>
+      <c r="J41" s="52" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K41" s="52" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="L41" s="52" t="inlineStr">
+        <is>
+          <t>https://noahsmarine.com/en-us/products/pva-1000-mold-release</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" s="52" t="inlineStr">
+        <is>
+          <t>#13 PVA Release Film qt (01-14813A)</t>
+        </is>
+      </c>
+      <c r="C42" s="52" t="inlineStr">
+        <is>
+          <t>Aircraft Spruce</t>
+        </is>
+      </c>
+      <c r="D42" s="52" t="inlineStr">
+        <is>
+          <t>PVA solution</t>
+        </is>
+      </c>
+      <c r="E42" s="52" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="F42" s="52" t="inlineStr">
+        <is>
+          <t>1 qt</t>
+        </is>
+      </c>
+      <c r="G42" s="51" t="n">
+        <v>2</v>
+      </c>
+      <c r="H42" s="67" t="n">
+        <v>27.85</v>
+      </c>
+      <c r="I42" s="67" t="n">
+        <v>14.07</v>
+      </c>
+      <c r="J42" s="52" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K42" s="52" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="L42" s="52" t="inlineStr">
+        <is>
+          <t>https://www.aircraftspruce.com/catalog/cmpages/moldpva.php</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="B43" s="52" t="inlineStr">
+        <is>
+          <t>TAP PVA Mold Release (Partall #10 MSDS)</t>
+        </is>
+      </c>
+      <c r="C43" s="52" t="inlineStr">
+        <is>
+          <t>TAP Plastics</t>
+        </is>
+      </c>
+      <c r="D43" s="52" t="inlineStr">
+        <is>
+          <t>PVA solution</t>
+        </is>
+      </c>
+      <c r="E43" s="52" t="inlineStr">
+        <is>
+          <t>7-8%</t>
+        </is>
+      </c>
+      <c r="F43" s="52" t="inlineStr">
+        <is>
+          <t>8 oz</t>
+        </is>
+      </c>
+      <c r="G43" s="51" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H43" s="67" t="n">
+        <v>14.35</v>
+      </c>
+      <c r="I43" s="67" t="n">
+        <v>28.99</v>
+      </c>
+      <c r="J43" s="52" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K43" s="52" t="inlineStr">
+        <is>
+          <t>PLAUSIBLE (403; snippet)</t>
+        </is>
+      </c>
+      <c r="L43" s="52" t="inlineStr">
+        <is>
+          <t>https://www.tapplastics.com/product/fiberglass/mold_releases/tap_pva_mold_release_liquid/67</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" s="52" t="inlineStr">
+        <is>
+          <t>Partall Coverall Film case (REXC-CF400)</t>
+        </is>
+      </c>
+      <c r="C44" s="52" t="inlineStr">
+        <is>
+          <t>US Composites</t>
+        </is>
+      </c>
+      <c r="D44" s="52" t="inlineStr">
+        <is>
+          <t>PVA solution</t>
+        </is>
+      </c>
+      <c r="E44" s="52" t="inlineStr">
+        <is>
+          <t>11-13%</t>
+        </is>
+      </c>
+      <c r="F44" s="52" t="inlineStr">
+        <is>
+          <t>4 x 1 gal</t>
+        </is>
+      </c>
+      <c r="G44" s="51" t="n">
+        <v>34.1</v>
+      </c>
+      <c r="H44" s="67" t="n">
+        <v>75</v>
+      </c>
+      <c r="I44" s="67" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="J44" s="52" t="inlineStr">
+        <is>
+          <t>COMPETITIVE (trade case)</t>
+        </is>
+      </c>
+      <c r="K44" s="52" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="L44" s="52" t="inlineStr">
+        <is>
+          <t>https://www.uscomposites.com/moldrelease.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" s="52" t="inlineStr">
+        <is>
+          <t>Partall Film #10, 5 cases (REX-PVA107)</t>
+        </is>
+      </c>
+      <c r="C45" s="52" t="inlineStr">
+        <is>
+          <t>US Composites</t>
+        </is>
+      </c>
+      <c r="D45" s="52" t="inlineStr">
+        <is>
+          <t>PVA solution</t>
+        </is>
+      </c>
+      <c r="E45" s="52" t="inlineStr">
+        <is>
+          <t>7-8%</t>
+        </is>
+      </c>
+      <c r="F45" s="52" t="inlineStr">
+        <is>
+          <t>20 gal</t>
+        </is>
+      </c>
+      <c r="G45" s="51" t="n">
+        <v>158.6</v>
+      </c>
+      <c r="H45" s="67" t="n">
+        <v>368</v>
+      </c>
+      <c r="I45" s="67" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="J45" s="52" t="inlineStr">
+        <is>
+          <t>COMPETITIVE</t>
+        </is>
+      </c>
+      <c r="K45" s="52" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="L45" s="52" t="inlineStr">
+        <is>
+          <t>https://www.uscomposites.com/moldrelease.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="B46" s="52" t="inlineStr">
+        <is>
+          <t>Partall Film #10 case (REX-PVA106)</t>
+        </is>
+      </c>
+      <c r="C46" s="52" t="inlineStr">
+        <is>
+          <t>US Composites</t>
+        </is>
+      </c>
+      <c r="D46" s="52" t="inlineStr">
+        <is>
+          <t>PVA solution</t>
+        </is>
+      </c>
+      <c r="E46" s="52" t="inlineStr">
+        <is>
+          <t>7-8%</t>
+        </is>
+      </c>
+      <c r="F46" s="52" t="inlineStr">
+        <is>
+          <t>4 x 1 gal</t>
+        </is>
+      </c>
+      <c r="G46" s="51" t="n">
+        <v>31.7</v>
+      </c>
+      <c r="H46" s="67" t="n">
+        <v>79</v>
+      </c>
+      <c r="I46" s="67" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="J46" s="52" t="inlineStr">
+        <is>
+          <t>COMPETITIVE (trade case)</t>
+        </is>
+      </c>
+      <c r="K46" s="52" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="L46" s="52" t="inlineStr">
+        <is>
+          <t>https://www.uscomposites.com/moldrelease.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" s="52" t="inlineStr">
+        <is>
+          <t>Partall Film #10 Green pail</t>
+        </is>
+      </c>
+      <c r="C47" s="52" t="inlineStr">
+        <is>
+          <t>The Engineer Guy</t>
+        </is>
+      </c>
+      <c r="D47" s="52" t="inlineStr">
+        <is>
+          <t>PVA solution</t>
+        </is>
+      </c>
+      <c r="E47" s="52" t="inlineStr">
+        <is>
+          <t>7-8%</t>
+        </is>
+      </c>
+      <c r="F47" s="52" t="inlineStr">
+        <is>
+          <t>5 gal</t>
+        </is>
+      </c>
+      <c r="G47" s="51" t="n">
+        <v>39.6</v>
+      </c>
+      <c r="H47" s="67" t="n">
+        <v>108</v>
+      </c>
+      <c r="I47" s="67" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="J47" s="52" t="inlineStr">
+        <is>
+          <t>COMPETITIVE (pail)</t>
+        </is>
+      </c>
+      <c r="K47" s="52" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="L47" s="52" t="inlineStr">
+        <is>
+          <t>https://theengineerguy.com/partall-film-10-green-5-gallon/</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" s="52" t="inlineStr">
+        <is>
+          <t>#13 PVA Release Film case (13-C)</t>
+        </is>
+      </c>
+      <c r="C48" s="52" t="inlineStr">
+        <is>
+          <t>Fibre Glast</t>
+        </is>
+      </c>
+      <c r="D48" s="52" t="inlineStr">
+        <is>
+          <t>PVA solution</t>
+        </is>
+      </c>
+      <c r="E48" s="52" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="F48" s="52" t="inlineStr">
+        <is>
+          <t>4 x 1 gal</t>
+        </is>
+      </c>
+      <c r="G48" s="51" t="n">
+        <v>31.7</v>
+      </c>
+      <c r="H48" s="67" t="n">
+        <v>115.78</v>
+      </c>
+      <c r="I48" s="67" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="J48" s="52" t="inlineStr">
+        <is>
+          <t>COMPETITIVE (trade case)</t>
+        </is>
+      </c>
+      <c r="K48" s="52" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="L48" s="52" t="inlineStr">
+        <is>
+          <t>https://www.fibreglast.com/product/PVA_Release_Film_13</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="B49" s="52" t="inlineStr">
+        <is>
+          <t>Partall Coverall case (V208-GC)</t>
+        </is>
+      </c>
+      <c r="C49" s="52" t="inlineStr">
+        <is>
+          <t>CST The Composites Store</t>
+        </is>
+      </c>
+      <c r="D49" s="52" t="inlineStr">
+        <is>
+          <t>PVA solution</t>
+        </is>
+      </c>
+      <c r="E49" s="52" t="inlineStr">
+        <is>
+          <t>11-13%</t>
+        </is>
+      </c>
+      <c r="F49" s="52" t="inlineStr">
+        <is>
+          <t>4 x 1 gal</t>
+        </is>
+      </c>
+      <c r="G49" s="51" t="n">
+        <v>34.1</v>
+      </c>
+      <c r="H49" s="67" t="n">
+        <v>133.9</v>
+      </c>
+      <c r="I49" s="67" t="n">
+        <v>3.93</v>
+      </c>
+      <c r="J49" s="52" t="inlineStr">
+        <is>
+          <t>COMPETITIVE (trade case)</t>
+        </is>
+      </c>
+      <c r="K49" s="52" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="L49" s="52" t="inlineStr">
+        <is>
+          <t>https://www.cstsales.com/a-vacuum-supplies-mold-release.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" s="52" t="inlineStr">
+        <is>
+          <t>PVA Release Film pail</t>
+        </is>
+      </c>
+      <c r="C50" s="52" t="inlineStr">
+        <is>
+          <t>Douglas and Sturgess</t>
+        </is>
+      </c>
+      <c r="D50" s="52" t="inlineStr">
+        <is>
+          <t>PVA solution</t>
+        </is>
+      </c>
+      <c r="E50" s="52" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="F50" s="52" t="inlineStr">
+        <is>
+          <t>5 gal</t>
+        </is>
+      </c>
+      <c r="G50" s="51" t="n">
+        <v>42.5</v>
+      </c>
+      <c r="H50" s="67" t="n">
+        <v>213.75</v>
+      </c>
+      <c r="I50" s="67" t="n">
+        <v>5.03</v>
+      </c>
+      <c r="J50" s="52" t="inlineStr">
+        <is>
+          <t>COMPETITIVE (pail)</t>
+        </is>
+      </c>
+      <c r="K50" s="52" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="L50" s="52" t="inlineStr">
+        <is>
+          <t>https://douglasandsturgess.com/products/p-v-a-5-gallon</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" s="52" t="inlineStr">
+        <is>
+          <t>PVA Solution, paper/textile, liquid</t>
+        </is>
+      </c>
+      <c r="C51" s="52" t="inlineStr">
+        <is>
+          <t>Rci Specialities (Erode, India)</t>
+        </is>
+      </c>
+      <c r="D51" s="52" t="inlineStr">
+        <is>
+          <t>PVA solution</t>
+        </is>
+      </c>
+      <c r="E51" s="52" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="F51" s="52" t="inlineStr">
+        <is>
+          <t>30/50/200 L barrels</t>
+        </is>
+      </c>
+      <c r="G51" s="51" t="n"/>
+      <c r="H51" s="67" t="n"/>
+      <c r="I51" s="67" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="J51" s="52" t="inlineStr">
+        <is>
+          <t>COMPETITIVE (offshore, ex-works)</t>
+        </is>
+      </c>
+      <c r="K51" s="52" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="L51" s="52" t="inlineStr">
+        <is>
+          <t>https://www.indiamart.com/proddetail/polyvinyl-alcohol-solution-22413495597.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="B52" s="52" t="inlineStr">
+        <is>
+          <t>PVA Solution Chemical, technical grade</t>
+        </is>
+      </c>
+      <c r="C52" s="52" t="inlineStr">
+        <is>
+          <t>Pexi Chem (Gujarat, India)</t>
+        </is>
+      </c>
+      <c r="D52" s="52" t="inlineStr">
+        <is>
+          <t>PVA solution</t>
+        </is>
+      </c>
+      <c r="E52" s="52" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="F52" s="52" t="inlineStr">
+        <is>
+          <t>50 kg drum, MOQ 100 kg</t>
+        </is>
+      </c>
+      <c r="G52" s="51" t="n"/>
+      <c r="H52" s="67" t="n"/>
+      <c r="I52" s="67" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="J52" s="52" t="inlineStr">
+        <is>
+          <t>COMPETITIVE (offshore)</t>
+        </is>
+      </c>
+      <c r="K52" s="52" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="L52" s="52" t="inlineStr">
+        <is>
+          <t>https://www.pexichem.in/pva-solution-chemical.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53" s="52" t="inlineStr">
+        <is>
+          <t>PVA Liquid, industrial grade 99%</t>
+        </is>
+      </c>
+      <c r="C53" s="52" t="inlineStr">
+        <is>
+          <t>Colour Plus Organics (Surat, India)</t>
+        </is>
+      </c>
+      <c r="D53" s="52" t="inlineStr">
+        <is>
+          <t>PVA solution</t>
+        </is>
+      </c>
+      <c r="E53" s="52" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="F53" s="52" t="inlineStr">
+        <is>
+          <t>50 kg drum</t>
+        </is>
+      </c>
+      <c r="G53" s="51" t="n"/>
+      <c r="H53" s="67" t="n"/>
+      <c r="I53" s="67" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="J53" s="52" t="inlineStr">
+        <is>
+          <t>COMPETITIVE (offshore)</t>
+        </is>
+      </c>
+      <c r="K53" s="52" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="L53" s="52" t="inlineStr">
+        <is>
+          <t>https://dir.indiamart.com/impcat/polyvinyl-alcohol/physical-state-liquid-q15654957/</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="B54" s="52" t="inlineStr">
+        <is>
+          <t>PVA Solution</t>
+        </is>
+      </c>
+      <c r="C54" s="52" t="inlineStr">
+        <is>
+          <t>Hari Om Polymers (Mumbai)</t>
+        </is>
+      </c>
+      <c r="D54" s="52" t="inlineStr">
+        <is>
+          <t>PVA solution</t>
+        </is>
+      </c>
+      <c r="E54" s="52" t="inlineStr">
+        <is>
+          <t>not stated; no spec sheet</t>
+        </is>
+      </c>
+      <c r="F54" s="52" t="inlineStr">
+        <is>
+          <t>pack not stated</t>
+        </is>
+      </c>
+      <c r="G54" s="51" t="n"/>
+      <c r="H54" s="67" t="n"/>
+      <c r="I54" s="67" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="J54" s="52" t="inlineStr">
+        <is>
+          <t>COMPETITIVE (offshore, weak)</t>
+        </is>
+      </c>
+      <c r="K54" s="52" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="L54" s="52" t="inlineStr">
+        <is>
+          <t>https://www.indiamart.com/proddetail/pva-solution-13129791312.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" s="52" t="inlineStr">
+        <is>
+          <t>Liquid Polyvinyl Alcohol 99.9%</t>
+        </is>
+      </c>
+      <c r="C55" s="52" t="inlineStr">
+        <is>
+          <t>Signature Solve Chem (Mumbai)</t>
+        </is>
+      </c>
+      <c r="D55" s="52" t="inlineStr">
+        <is>
+          <t>PVA solution</t>
+        </is>
+      </c>
+      <c r="E55" s="52" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="F55" s="52" t="inlineStr">
+        <is>
+          <t>200 L drum</t>
+        </is>
+      </c>
+      <c r="G55" s="51" t="n"/>
+      <c r="H55" s="67" t="n"/>
+      <c r="I55" s="67" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="J55" s="52" t="inlineStr">
+        <is>
+          <t>COMPETITIVE (offshore)</t>
+        </is>
+      </c>
+      <c r="K55" s="52" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="L55" s="52" t="inlineStr">
+        <is>
+          <t>https://www.indiamart.com/proddetail/liquid-polyvinyl-alcohol-6833971891.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="B56" s="52" t="inlineStr">
+        <is>
+          <t>PVA Liquid, textile, 87-89% hydrolyzed</t>
+        </is>
+      </c>
+      <c r="C56" s="52" t="inlineStr">
+        <is>
+          <t>Bhavna Plast (Ahmedabad)</t>
+        </is>
+      </c>
+      <c r="D56" s="52" t="inlineStr">
+        <is>
+          <t>PVA solution</t>
+        </is>
+      </c>
+      <c r="E56" s="52" t="inlineStr">
+        <is>
+          <t>not stated; partially hydrolyzed</t>
+        </is>
+      </c>
+      <c r="F56" s="52" t="inlineStr">
+        <is>
+          <t>pack not stated</t>
+        </is>
+      </c>
+      <c r="G56" s="51" t="n"/>
+      <c r="H56" s="67" t="n"/>
+      <c r="I56" s="67" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="J56" s="52" t="inlineStr">
+        <is>
+          <t>COMPETITIVE (offshore)</t>
+        </is>
+      </c>
+      <c r="K56" s="52" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="L56" s="52" t="inlineStr">
+        <is>
+          <t>https://dir.indiamart.com/impcat/polyvinyl-alcohol/physical-state-liquid-q15654957/</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="B57" s="52" t="inlineStr">
+        <is>
+          <t>Industrial PVA Solution for textile</t>
+        </is>
+      </c>
+      <c r="C57" s="52" t="inlineStr">
+        <is>
+          <t>Padma Traders (Coimbatore)</t>
+        </is>
+      </c>
+      <c r="D57" s="52" t="inlineStr">
+        <is>
+          <t>PVA solution</t>
+        </is>
+      </c>
+      <c r="E57" s="52" t="inlineStr">
+        <is>
+          <t>10% or 20% (stated)</t>
+        </is>
+      </c>
+      <c r="F57" s="52" t="inlineStr">
+        <is>
+          <t>20/30/50 kg carboys</t>
+        </is>
+      </c>
+      <c r="G57" s="51" t="n"/>
+      <c r="H57" s="67" t="n"/>
+      <c r="I57" s="67" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="J57" s="52" t="inlineStr">
+        <is>
+          <t>COMPETITIVE (offshore)</t>
+        </is>
+      </c>
+      <c r="K57" s="52" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="L57" s="52" t="inlineStr">
+        <is>
+          <t>https://www.indiamart.com/proddetail/pva-solution-17107003597.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="B58" s="52" t="inlineStr">
+        <is>
+          <t>PVA Liquid grade 2688, fully hydrolyzed</t>
+        </is>
+      </c>
+      <c r="C58" s="52" t="inlineStr">
+        <is>
+          <t>Astrra Chemicals (Chennai)</t>
+        </is>
+      </c>
+      <c r="D58" s="52" t="inlineStr">
+        <is>
+          <t>PVA solution</t>
+        </is>
+      </c>
+      <c r="E58" s="52" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="F58" s="52" t="inlineStr">
+        <is>
+          <t>50 L container</t>
+        </is>
+      </c>
+      <c r="G58" s="51" t="n"/>
+      <c r="H58" s="67" t="n"/>
+      <c r="I58" s="67" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="J58" s="52" t="inlineStr">
+        <is>
+          <t>COMPETITIVE (offshore)</t>
+        </is>
+      </c>
+      <c r="K58" s="52" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="L58" s="52" t="inlineStr">
+        <is>
+          <t>https://www.indiamart.com/proddetail/polyvinyl-alcohol-pva-liquid-for-textile-use-5052116512.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="B59" s="52" t="inlineStr">
+        <is>
+          <t>Liquid PVA Solution, industrial, fully hydrolyzed</t>
+        </is>
+      </c>
+      <c r="C59" s="52" t="inlineStr">
+        <is>
+          <t>Pexi Chem (India)</t>
+        </is>
+      </c>
+      <c r="D59" s="52" t="inlineStr">
+        <is>
+          <t>PVA solution</t>
+        </is>
+      </c>
+      <c r="E59" s="52" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="F59" s="52" t="inlineStr">
+        <is>
+          <t>50 kg drums, MOQ 1,000 kg</t>
+        </is>
+      </c>
+      <c r="G59" s="51" t="n"/>
+      <c r="H59" s="67" t="n"/>
+      <c r="I59" s="67" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="J59" s="52" t="inlineStr">
+        <is>
+          <t>HIGH (offshore, ex-works)</t>
+        </is>
+      </c>
+      <c r="K59" s="52" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="L59" s="52" t="inlineStr">
+        <is>
+          <t>https://www.pexichem.in/pva-solution-chemical.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="B60" s="52" t="inlineStr">
+        <is>
+          <t>Liquid PVA (yellow liquid)</t>
+        </is>
+      </c>
+      <c r="C60" s="52" t="inlineStr">
+        <is>
+          <t>Qingdao Easthony via Alibaba</t>
+        </is>
+      </c>
+      <c r="D60" s="52" t="inlineStr">
+        <is>
+          <t>PVA solution</t>
+        </is>
+      </c>
+      <c r="E60" s="52" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="F60" s="52" t="inlineStr">
+        <is>
+          <t>per MT, MOQ 1 MT</t>
+        </is>
+      </c>
+      <c r="G60" s="51" t="n"/>
+      <c r="H60" s="67" t="n">
+        <v>1500</v>
+      </c>
+      <c r="I60" s="67" t="n"/>
+      <c r="J60" s="52" t="inlineStr">
+        <is>
+          <t>HIGH (FOB China)</t>
+        </is>
+      </c>
+      <c r="K60" s="52" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="L60" s="52" t="inlineStr">
+        <is>
+          <t>https://www.alibaba.com/countrysearch/CN/liquid-pva.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="B61" s="52" t="inlineStr">
+        <is>
+          <t>SINOPEC SVW FS-200 liquid PVA</t>
+        </is>
+      </c>
+      <c r="C61" s="52" t="inlineStr">
+        <is>
+          <t>Chongqing SVW via Alibaba</t>
+        </is>
+      </c>
+      <c r="D61" s="52" t="inlineStr">
+        <is>
+          <t>PVA solution</t>
+        </is>
+      </c>
+      <c r="E61" s="52" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="F61" s="52" t="inlineStr">
+        <is>
+          <t>per MT, MOQ 10 MT</t>
+        </is>
+      </c>
+      <c r="G61" s="51" t="n">
+        <v>2178.2</v>
+      </c>
+      <c r="H61" s="67" t="n">
+        <v>2200</v>
+      </c>
+      <c r="I61" s="67" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="J61" s="52" t="inlineStr">
+        <is>
+          <t>HIGH (FOB China)</t>
+        </is>
+      </c>
+      <c r="K61" s="52" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="L61" s="52" t="inlineStr">
+        <is>
+          <t>https://www.alibaba.com/countrysearch/CN/liquid-pva.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="B62" s="52" t="inlineStr">
+        <is>
+          <t>Liquid Polyvinyl Alcohol</t>
+        </is>
+      </c>
+      <c r="C62" s="52" t="inlineStr">
+        <is>
+          <t>Shandong Qibo via Made-in-China</t>
+        </is>
+      </c>
+      <c r="D62" s="52" t="inlineStr">
+        <is>
+          <t>PVA solution</t>
+        </is>
+      </c>
+      <c r="E62" s="52" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="F62" s="52" t="inlineStr">
+        <is>
+          <t>per kg, export lot</t>
+        </is>
+      </c>
+      <c r="G62" s="51" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H62" s="67" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I62" s="67" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="J62" s="52" t="inlineStr">
+        <is>
+          <t>HIGH (FOB China)</t>
+        </is>
+      </c>
+      <c r="K62" s="52" t="inlineStr">
+        <is>
+          <t>PLAUSIBLE (listing not re-found)</t>
+        </is>
+      </c>
+      <c r="L62" s="52" t="inlineStr">
+        <is>
+          <t>https://www.made-in-china.com/price/polyvinyl-alcohol-price.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="B63" s="52" t="inlineStr">
+        <is>
+          <t>PVA Solution Chemical, industrial 99%</t>
+        </is>
+      </c>
+      <c r="C63" s="52" t="inlineStr">
+        <is>
+          <t>Pexi Chem (India)</t>
+        </is>
+      </c>
+      <c r="D63" s="52" t="inlineStr">
+        <is>
+          <t>PVA solution</t>
+        </is>
+      </c>
+      <c r="E63" s="52" t="inlineStr">
+        <is>
+          <t>not stated</t>
+        </is>
+      </c>
+      <c r="F63" s="52" t="inlineStr">
+        <is>
+          <t>100 kg pack, MOQ 1,000 kg</t>
+        </is>
+      </c>
+      <c r="G63" s="51" t="n"/>
+      <c r="H63" s="67" t="n"/>
+      <c r="I63" s="67" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="J63" s="52" t="inlineStr">
+        <is>
+          <t>HIGH (offshore, ex-works)</t>
+        </is>
+      </c>
+      <c r="K63" s="52" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="L63" s="52" t="inlineStr">
+        <is>
+          <t>https://www.pexichem.in/pva-solution-chemical.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="B64" s="52" t="inlineStr">
+        <is>
+          <t>PVA Solution 4% (P0211)</t>
+        </is>
+      </c>
+      <c r="C64" s="52" t="inlineStr">
+        <is>
+          <t>Flinn Scientific</t>
+        </is>
+      </c>
+      <c r="D64" s="52" t="inlineStr">
+        <is>
+          <t>PVA solution</t>
+        </is>
+      </c>
+      <c r="E64" s="52" t="inlineStr">
+        <is>
+          <t>4%</t>
+        </is>
+      </c>
+      <c r="F64" s="52" t="inlineStr">
+        <is>
+          <t>4 L</t>
+        </is>
+      </c>
+      <c r="G64" s="51" t="n">
+        <v>9</v>
+      </c>
+      <c r="H64" s="67" t="n">
+        <v>20.99</v>
+      </c>
+      <c r="I64" s="67" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="J64" s="52" t="inlineStr">
+        <is>
+          <t>LOW (lab)</t>
+        </is>
+      </c>
+      <c r="K64" s="52" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="L64" s="52" t="inlineStr">
+        <is>
+          <t>https://www.flinnsci.com/polyvinyl-alcohol-solution-4-aqueous-4-l/p0211/</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="B65" s="52" t="inlineStr">
+        <is>
+          <t>PVA Solution 4% (P0209)</t>
+        </is>
+      </c>
+      <c r="C65" s="52" t="inlineStr">
+        <is>
+          <t>Flinn Scientific</t>
+        </is>
+      </c>
+      <c r="D65" s="52" t="inlineStr">
+        <is>
+          <t>PVA solution</t>
+        </is>
+      </c>
+      <c r="E65" s="52" t="inlineStr">
+        <is>
+          <t>4%</t>
+        </is>
+      </c>
+      <c r="F65" s="52" t="inlineStr">
+        <is>
+          <t>500 mL</t>
+        </is>
+      </c>
+      <c r="G65" s="51" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="H65" s="67" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="I65" s="67" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="J65" s="52" t="inlineStr">
+        <is>
+          <t>LOW (lab)</t>
+        </is>
+      </c>
+      <c r="K65" s="52" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="L65" s="52" t="inlineStr">
+        <is>
+          <t>https://www.flinnsci.com/polyvinyl-alcohol-solution-4-aqueous-500-ml/p0209/</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="B66" s="52" t="inlineStr">
+        <is>
+          <t>Aldon 4% PVA Solution</t>
+        </is>
+      </c>
+      <c r="C66" s="52" t="inlineStr">
+        <is>
+          <t>Geyer Instructional</t>
+        </is>
+      </c>
+      <c r="D66" s="52" t="inlineStr">
+        <is>
+          <t>PVA solution</t>
+        </is>
+      </c>
+      <c r="E66" s="52" t="inlineStr">
+        <is>
+          <t>4%</t>
+        </is>
+      </c>
+      <c r="F66" s="52" t="inlineStr">
+        <is>
+          <t>1 L</t>
+        </is>
+      </c>
+      <c r="G66" s="51" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="H66" s="67" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="I66" s="67" t="n">
+        <v>4.19</v>
+      </c>
+      <c r="J66" s="52" t="inlineStr">
+        <is>
+          <t>LOW (lab)</t>
+        </is>
+      </c>
+      <c r="K66" s="52" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="L66" s="52" t="inlineStr">
+        <is>
+          <t>https://www.geyerinstructional.com/aldon-chemicals-4-polyvinyl-alcohol-solution-1l/</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="B67" s="52" t="inlineStr">
+        <is>
+          <t>PVA Solution 4% (P0210)</t>
+        </is>
+      </c>
+      <c r="C67" s="52" t="inlineStr">
+        <is>
+          <t>Flinn Scientific</t>
+        </is>
+      </c>
+      <c r="D67" s="52" t="inlineStr">
+        <is>
+          <t>PVA solution</t>
+        </is>
+      </c>
+      <c r="E67" s="52" t="inlineStr">
+        <is>
+          <t>4%</t>
+        </is>
+      </c>
+      <c r="F67" s="52" t="inlineStr">
+        <is>
+          <t>1 L</t>
+        </is>
+      </c>
+      <c r="G67" s="51" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="H67" s="67" t="n">
+        <v>10.49</v>
+      </c>
+      <c r="I67" s="67" t="n">
+        <v>4.67</v>
+      </c>
+      <c r="J67" s="52" t="inlineStr">
+        <is>
+          <t>LOW (lab)</t>
+        </is>
+      </c>
+      <c r="K67" s="52" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="L67" s="52" t="inlineStr">
+        <is>
+          <t>https://www.flinnsci.com/polyvinyl-alcohol-solution-4-aqueous-1-l/p0210/</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="B68" s="52" t="inlineStr">
+        <is>
+          <t>PVA Solution 5% (IS25024-AL)</t>
+        </is>
+      </c>
+      <c r="C68" s="52" t="inlineStr">
+        <is>
+          <t>Dawn Scientific</t>
+        </is>
+      </c>
+      <c r="D68" s="52" t="inlineStr">
+        <is>
+          <t>PVA solution</t>
+        </is>
+      </c>
+      <c r="E68" s="52" t="inlineStr">
+        <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="F68" s="52" t="inlineStr">
+        <is>
+          <t>3.8 L</t>
+        </is>
+      </c>
+      <c r="G68" s="51" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="H68" s="67" t="n">
+        <v>61.95</v>
+      </c>
+      <c r="I68" s="67" t="n">
+        <v>7.26</v>
+      </c>
+      <c r="J68" s="52" t="inlineStr">
+        <is>
+          <t>LOW (lab)</t>
+        </is>
+      </c>
+      <c r="K68" s="52" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="L68" s="52" t="inlineStr">
+        <is>
+          <t>https://dawnscientific.com/product/polyvinyl-alcohol-solution-5-3-8l/</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="B69" s="52" t="inlineStr">
+        <is>
+          <t>PVA Solution 5% (IS25024)</t>
+        </is>
+      </c>
+      <c r="C69" s="52" t="inlineStr">
+        <is>
+          <t>The Lab Stockroom</t>
+        </is>
+      </c>
+      <c r="D69" s="52" t="inlineStr">
+        <is>
+          <t>PVA solution</t>
+        </is>
+      </c>
+      <c r="E69" s="52" t="inlineStr">
+        <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="F69" s="52" t="inlineStr">
+        <is>
+          <t>3.8 L</t>
+        </is>
+      </c>
+      <c r="G69" s="51" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="H69" s="67" t="n">
+        <v>62.99</v>
+      </c>
+      <c r="I69" s="67" t="n">
+        <v>7.38</v>
+      </c>
+      <c r="J69" s="52" t="inlineStr">
+        <is>
+          <t>LOW (lab)</t>
+        </is>
+      </c>
+      <c r="K69" s="52" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="L69" s="52" t="inlineStr">
+        <is>
+          <t>https://www.thelabstockroom.com/products/is25024</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="B70" s="52" t="inlineStr">
+        <is>
+          <t>PVA 4% Lab Grade (882373)</t>
+        </is>
+      </c>
+      <c r="C70" s="52" t="inlineStr">
+        <is>
+          <t>Carolina Biological</t>
+        </is>
+      </c>
+      <c r="D70" s="52" t="inlineStr">
+        <is>
+          <t>PVA solution</t>
+        </is>
+      </c>
+      <c r="E70" s="52" t="inlineStr">
+        <is>
+          <t>4%</t>
+        </is>
+      </c>
+      <c r="F70" s="52" t="inlineStr">
+        <is>
+          <t>3.8 L</t>
+        </is>
+      </c>
+      <c r="G70" s="51" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="H70" s="67" t="n">
+        <v>65.95</v>
+      </c>
+      <c r="I70" s="67" t="n">
+        <v>7.73</v>
+      </c>
+      <c r="J70" s="52" t="inlineStr">
+        <is>
+          <t>LOW (lab)</t>
+        </is>
+      </c>
+      <c r="K70" s="52" t="inlineStr">
+        <is>
+          <t>PLAUSIBLE (403)</t>
+        </is>
+      </c>
+      <c r="L70" s="52" t="inlineStr">
+        <is>
+          <t>https://www.carolina.com/specialty-chemicals-p-r/polyvinyl-alcohol-4-laboratory-grade-38-l/882373.pr</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="B71" s="52" t="inlineStr">
+        <is>
+          <t>PVA 4% Lab Grade (882372)</t>
+        </is>
+      </c>
+      <c r="C71" s="52" t="inlineStr">
+        <is>
+          <t>Carolina Biological</t>
+        </is>
+      </c>
+      <c r="D71" s="52" t="inlineStr">
+        <is>
+          <t>PVA solution</t>
+        </is>
+      </c>
+      <c r="E71" s="52" t="inlineStr">
+        <is>
+          <t>4%</t>
+        </is>
+      </c>
+      <c r="F71" s="52" t="inlineStr">
+        <is>
+          <t>1 L</t>
+        </is>
+      </c>
+      <c r="G71" s="51" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="H71" s="67" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="I71" s="67" t="n">
+        <v>9.57</v>
+      </c>
+      <c r="J71" s="52" t="inlineStr">
+        <is>
+          <t>LOW (lab)</t>
+        </is>
+      </c>
+      <c r="K71" s="52" t="inlineStr">
+        <is>
+          <t>PLAUSIBLE (403)</t>
+        </is>
+      </c>
+      <c r="L71" s="52" t="inlineStr">
+        <is>
+          <t>https://www.carolina.com/specialty-chemicals-p-r/polyvinyl-alcohol-4-laboratory-grade-1-l/882372.pr</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="B72" s="52" t="inlineStr">
+        <is>
+          <t>PVA Solution 5% (AD-PP0119-3.8L)</t>
+        </is>
+      </c>
+      <c r="C72" s="52" t="inlineStr">
+        <is>
+          <t>CP Lab Safety</t>
+        </is>
+      </c>
+      <c r="D72" s="52" t="inlineStr">
+        <is>
+          <t>PVA solution</t>
+        </is>
+      </c>
+      <c r="E72" s="52" t="inlineStr">
+        <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="F72" s="52" t="inlineStr">
+        <is>
+          <t>3.8 L</t>
+        </is>
+      </c>
+      <c r="G72" s="51" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="H72" s="67" t="n">
+        <v>90.31999999999999</v>
+      </c>
+      <c r="I72" s="67" t="n">
+        <v>10.59</v>
+      </c>
+      <c r="J72" s="52" t="inlineStr">
+        <is>
+          <t>LOW (lab)</t>
+        </is>
+      </c>
+      <c r="K72" s="52" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="L72" s="52" t="inlineStr">
+        <is>
+          <t>https://www.cplabsafety.com/polyvinyl-alcohol-solution-5-percent-3-8-liters-innovating-science/ad-pp0119-3-8l</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="B73" s="52" t="inlineStr">
+        <is>
+          <t>PVA 4% Preserved (C6191-4L)</t>
+        </is>
+      </c>
+      <c r="C73" s="52" t="inlineStr">
+        <is>
+          <t>Lab Alley</t>
+        </is>
+      </c>
+      <c r="D73" s="52" t="inlineStr">
+        <is>
+          <t>PVA solution</t>
+        </is>
+      </c>
+      <c r="E73" s="52" t="inlineStr">
+        <is>
+          <t>4%</t>
+        </is>
+      </c>
+      <c r="F73" s="52" t="inlineStr">
+        <is>
+          <t>4 L</t>
+        </is>
+      </c>
+      <c r="G73" s="51" t="n">
+        <v>9</v>
+      </c>
+      <c r="H73" s="67" t="n">
+        <v>101.32</v>
+      </c>
+      <c r="I73" s="67" t="n">
+        <v>11.28</v>
+      </c>
+      <c r="J73" s="52" t="inlineStr">
+        <is>
+          <t>LOW (lab)</t>
+        </is>
+      </c>
+      <c r="K73" s="52" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="L73" s="52" t="inlineStr">
+        <is>
+          <t>https://www.laballey.com/products/pva-4-preserved-solution</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="B74" s="52" t="inlineStr">
+        <is>
+          <t>PVA 3% Solution (CH-PVASOLN)</t>
+        </is>
+      </c>
+      <c r="C74" s="52" t="inlineStr">
+        <is>
+          <t>Home Science Tools</t>
+        </is>
+      </c>
+      <c r="D74" s="52" t="inlineStr">
+        <is>
+          <t>PVA solution</t>
+        </is>
+      </c>
+      <c r="E74" s="52" t="inlineStr">
+        <is>
+          <t>3%</t>
+        </is>
+      </c>
+      <c r="F74" s="52" t="inlineStr">
+        <is>
+          <t>500 mL</t>
+        </is>
+      </c>
+      <c r="G74" s="51" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="H74" s="67" t="n">
+        <v>12.95</v>
+      </c>
+      <c r="I74" s="67" t="n">
+        <v>11.53</v>
+      </c>
+      <c r="J74" s="52" t="inlineStr">
+        <is>
+          <t>LOW (lab)</t>
+        </is>
+      </c>
+      <c r="K74" s="52" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="L74" s="52" t="inlineStr">
+        <is>
+          <t>https://www.homesciencetools.com/product/polyvinyl-alcohol-3-solution-500-ml/</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="B75" s="52" t="inlineStr">
+        <is>
+          <t>PVA 4% Lab Grade (882371)</t>
+        </is>
+      </c>
+      <c r="C75" s="52" t="inlineStr">
+        <is>
+          <t>Carolina Biological</t>
+        </is>
+      </c>
+      <c r="D75" s="52" t="inlineStr">
+        <is>
+          <t>PVA solution</t>
+        </is>
+      </c>
+      <c r="E75" s="52" t="inlineStr">
+        <is>
+          <t>4%</t>
+        </is>
+      </c>
+      <c r="F75" s="52" t="inlineStr">
+        <is>
+          <t>500 mL</t>
+        </is>
+      </c>
+      <c r="G75" s="51" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="H75" s="67" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="I75" s="67" t="n">
+        <v>11.67</v>
+      </c>
+      <c r="J75" s="52" t="inlineStr">
+        <is>
+          <t>LOW (lab)</t>
+        </is>
+      </c>
+      <c r="K75" s="52" t="inlineStr">
+        <is>
+          <t>PLAUSIBLE (403)</t>
+        </is>
+      </c>
+      <c r="L75" s="52" t="inlineStr">
+        <is>
+          <t>https://www.carolina.com/specialty-chemicals-p-r/polyvinyl-alcohol-4-laboratory-grade-500-ml/882371.pr</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="B76" s="52" t="inlineStr">
+        <is>
+          <t>PVA Solution 4% (IS25020)</t>
+        </is>
+      </c>
+      <c r="C76" s="52" t="inlineStr">
+        <is>
+          <t>The Lab Stockroom</t>
+        </is>
+      </c>
+      <c r="D76" s="52" t="inlineStr">
+        <is>
+          <t>PVA solution</t>
+        </is>
+      </c>
+      <c r="E76" s="52" t="inlineStr">
+        <is>
+          <t>4%</t>
+        </is>
+      </c>
+      <c r="F76" s="52" t="inlineStr">
+        <is>
+          <t>1 L</t>
+        </is>
+      </c>
+      <c r="G76" s="51" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="H76" s="67" t="n">
+        <v>30.49</v>
+      </c>
+      <c r="I76" s="67" t="n">
+        <v>13.58</v>
+      </c>
+      <c r="J76" s="52" t="inlineStr">
+        <is>
+          <t>LOW (lab)</t>
+        </is>
+      </c>
+      <c r="K76" s="52" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="L76" s="52" t="inlineStr">
+        <is>
+          <t>https://www.thelabstockroom.com/products/is25020</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="B77" s="52" t="inlineStr">
+        <is>
+          <t>Aqua Solutions PVA 4% w/v (NC9222312)</t>
+        </is>
+      </c>
+      <c r="C77" s="52" t="inlineStr">
+        <is>
+          <t>Fisher Scientific</t>
+        </is>
+      </c>
+      <c r="D77" s="52" t="inlineStr">
+        <is>
+          <t>PVA solution</t>
+        </is>
+      </c>
+      <c r="E77" s="52" t="inlineStr">
+        <is>
+          <t>4%</t>
+        </is>
+      </c>
+      <c r="F77" s="52" t="inlineStr">
+        <is>
+          <t>4 L</t>
+        </is>
+      </c>
+      <c r="G77" s="51" t="n">
+        <v>9</v>
+      </c>
+      <c r="H77" s="67" t="n">
+        <v>132.7</v>
+      </c>
+      <c r="I77" s="67" t="n">
+        <v>14.78</v>
+      </c>
+      <c r="J77" s="52" t="inlineStr">
+        <is>
+          <t>LOW (lab)</t>
+        </is>
+      </c>
+      <c r="K77" s="52" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="L77" s="52" t="inlineStr">
+        <is>
+          <t>https://www.fishersci.com/shop/products/poly-vinyl-alcohol-4ltr/NC9222312</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="B78" s="52" t="inlineStr">
+        <is>
+          <t>Aqua Solutions PVA 4% w/v (NC9880556)</t>
+        </is>
+      </c>
+      <c r="C78" s="52" t="inlineStr">
+        <is>
+          <t>Fisher Scientific</t>
+        </is>
+      </c>
+      <c r="D78" s="52" t="inlineStr">
+        <is>
+          <t>PVA solution</t>
+        </is>
+      </c>
+      <c r="E78" s="52" t="inlineStr">
+        <is>
+          <t>4%</t>
+        </is>
+      </c>
+      <c r="F78" s="52" t="inlineStr">
+        <is>
+          <t>1 L</t>
+        </is>
+      </c>
+      <c r="G78" s="51" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="H78" s="67" t="n">
+        <v>38.81</v>
+      </c>
+      <c r="I78" s="67" t="n">
+        <v>17.28</v>
+      </c>
+      <c r="J78" s="52" t="inlineStr">
+        <is>
+          <t>LOW (lab)</t>
+        </is>
+      </c>
+      <c r="K78" s="52" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="L78" s="52" t="inlineStr">
+        <is>
+          <t>https://www.fishersci.com/shop/products/poly-vinyl-alcohol-1l/NC9880556</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="B79" s="52" t="inlineStr">
+        <is>
+          <t>PVA Solution 4% bulk refill (PL-1-5-B)</t>
+        </is>
+      </c>
+      <c r="C79" s="52" t="inlineStr">
+        <is>
+          <t>Lab-Aids</t>
+        </is>
+      </c>
+      <c r="D79" s="52" t="inlineStr">
+        <is>
+          <t>PVA solution</t>
+        </is>
+      </c>
+      <c r="E79" s="52" t="inlineStr">
+        <is>
+          <t>4%</t>
+        </is>
+      </c>
+      <c r="F79" s="52" t="inlineStr">
+        <is>
+          <t>960 mL</t>
+        </is>
+      </c>
+      <c r="G79" s="51" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="H79" s="67" t="n">
+        <v>39.3</v>
+      </c>
+      <c r="I79" s="67" t="n">
+        <v>18.23</v>
+      </c>
+      <c r="J79" s="52" t="inlineStr">
+        <is>
+          <t>LOW (lab)</t>
+        </is>
+      </c>
+      <c r="K79" s="52" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="L79" s="52" t="inlineStr">
+        <is>
+          <t>https://store.lab-aids.com/products/polyvinyl-alcohol-solution-4-960-ml-bulk-refill</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="B80" s="52" t="inlineStr">
+        <is>
+          <t>PVA Solution 4% (AD-PP0117-1L)</t>
+        </is>
+      </c>
+      <c r="C80" s="52" t="inlineStr">
+        <is>
+          <t>CP Lab Safety</t>
+        </is>
+      </c>
+      <c r="D80" s="52" t="inlineStr">
+        <is>
+          <t>PVA solution</t>
+        </is>
+      </c>
+      <c r="E80" s="52" t="inlineStr">
+        <is>
+          <t>4%</t>
+        </is>
+      </c>
+      <c r="F80" s="52" t="inlineStr">
+        <is>
+          <t>1 L</t>
+        </is>
+      </c>
+      <c r="G80" s="51" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="H80" s="67" t="n">
+        <v>41.34</v>
+      </c>
+      <c r="I80" s="67" t="n">
+        <v>18.41</v>
+      </c>
+      <c r="J80" s="52" t="inlineStr">
+        <is>
+          <t>LOW (lab)</t>
+        </is>
+      </c>
+      <c r="K80" s="52" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="L80" s="52" t="inlineStr">
+        <is>
+          <t>https://www.cplabsafety.com/polyvinyl-alcohol-solution-4-percent-1-liter-innovating-science/ad-pp0117-1l</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="B81" s="52" t="inlineStr">
+        <is>
+          <t>PVA 4% Solution</t>
+        </is>
+      </c>
+      <c r="C81" s="52" t="inlineStr">
+        <is>
+          <t>Loose in the Lab Science</t>
+        </is>
+      </c>
+      <c r="D81" s="52" t="inlineStr">
+        <is>
+          <t>PVA solution</t>
+        </is>
+      </c>
+      <c r="E81" s="52" t="inlineStr">
+        <is>
+          <t>4%</t>
+        </is>
+      </c>
+      <c r="F81" s="52" t="inlineStr">
+        <is>
+          <t>1 fl oz</t>
+        </is>
+      </c>
+      <c r="G81" s="51" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H81" s="67" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="I81" s="67" t="n">
+        <v>26.95</v>
+      </c>
+      <c r="J81" s="52" t="inlineStr">
+        <is>
+          <t>LOW (lab)</t>
+        </is>
+      </c>
+      <c r="K81" s="52" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="L81" s="52" t="inlineStr">
+        <is>
+          <t>https://looseinthelabscience.com/polyvinyl-alcohol-4-solution/</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="B82" s="52" t="inlineStr">
+        <is>
+          <t>PVA Solution 4% (PL-1-5EA)</t>
+        </is>
+      </c>
+      <c r="C82" s="52" t="inlineStr">
+        <is>
+          <t>Lab-Aids</t>
+        </is>
+      </c>
+      <c r="D82" s="52" t="inlineStr">
+        <is>
+          <t>PVA solution</t>
+        </is>
+      </c>
+      <c r="E82" s="52" t="inlineStr">
+        <is>
+          <t>4%</t>
+        </is>
+      </c>
+      <c r="F82" s="52" t="inlineStr">
+        <is>
+          <t>180 mL</t>
+        </is>
+      </c>
+      <c r="G82" s="51" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H82" s="67" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="I82" s="67" t="n">
+        <v>35.87</v>
+      </c>
+      <c r="J82" s="52" t="inlineStr">
+        <is>
+          <t>LOW (lab)</t>
+        </is>
+      </c>
+      <c r="K82" s="52" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="L82" s="52" t="inlineStr">
+        <is>
+          <t>https://store.lab-aids.com/products/polyvinyl-alcohol-solution-4-180-ml</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="B83" s="52" t="inlineStr">
+        <is>
+          <t>PVA 4% Preserved (C6191-500ml)</t>
+        </is>
+      </c>
+      <c r="C83" s="52" t="inlineStr">
+        <is>
+          <t>Lab Alley</t>
+        </is>
+      </c>
+      <c r="D83" s="52" t="inlineStr">
+        <is>
+          <t>PVA solution</t>
+        </is>
+      </c>
+      <c r="E83" s="52" t="inlineStr">
+        <is>
+          <t>4%</t>
+        </is>
+      </c>
+      <c r="F83" s="52" t="inlineStr">
+        <is>
+          <t>500 mL</t>
+        </is>
+      </c>
+      <c r="G83" s="51" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="H83" s="67" t="n">
+        <v>49.48</v>
+      </c>
+      <c r="I83" s="67" t="n">
+        <v>44.07</v>
+      </c>
+      <c r="J83" s="52" t="inlineStr">
+        <is>
+          <t>LOW (lab)</t>
+        </is>
+      </c>
+      <c r="K83" s="52" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="L83" s="52" t="inlineStr">
+        <is>
+          <t>https://www.laballey.com/products/pva-4-preserved-solution</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B2:I38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="2" max="2"/>
@@ -1454,7 +6178,7 @@
     <row r="6">
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>All-SNP (today)</t>
+          <t>All-SNP (today) = Option 2 purchase cost</t>
         </is>
       </c>
       <c r="C6" s="12" t="n">
@@ -1488,7 +6212,7 @@
     <row r="7">
       <c r="B7" s="42" t="inlineStr">
         <is>
-          <t>A — PCI at 1/3, 5-drum batches (10/yr)</t>
+          <t>Option 1 — PCI at 1/3 (50 drums = 10 batches of 5) at $3.50 — chart bar</t>
         </is>
       </c>
       <c r="C7" s="43" t="n">
@@ -1522,11 +6246,11 @@
     <row r="8">
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>A — PCI 1 drum/week, below-batch price</t>
+          <t>Option 1 — same 1/3 but ordered below batch size ($6.00) — chart bar</t>
         </is>
       </c>
       <c r="C8" s="12" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D8" s="21">
         <f>PCIsub</f>
@@ -1556,14 +6280,14 @@
     <row r="9">
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>A — PCI at 1/3 but below-batch price (for reference)</t>
+          <t>CJB at the same 1/3 (for scale) — chart bar</t>
         </is>
       </c>
       <c r="C9" s="12" t="n">
         <v>50</v>
       </c>
       <c r="D9" s="21">
-        <f>PCIsub</f>
+        <f>CJBlb</f>
         <v/>
       </c>
       <c r="E9" s="15">
@@ -1590,14 +6314,14 @@
     <row r="10">
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>CJB at 1/3 (for scale)</t>
+          <t>Option 3 — keep-alive: 1 batch of 5 drums / yr at $3.50</t>
         </is>
       </c>
       <c r="C10" s="12" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="D10" s="21">
-        <f>CJBlb</f>
+        <f>PCIq</f>
         <v/>
       </c>
       <c r="E10" s="15">
@@ -1621,101 +6345,119 @@
         <v/>
       </c>
     </row>
+    <row r="11">
+      <c r="B11" s="11" t="inlineStr">
+        <is>
+          <t>Option 3 — keep-alive: 2 batches (10 drums) / yr at $3.50</t>
+        </is>
+      </c>
+      <c r="C11" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="D11" s="21">
+        <f>PCIq</f>
+        <v/>
+      </c>
+      <c r="E11" s="15">
+        <f>C11*DrumLb*D11</f>
+        <v/>
+      </c>
+      <c r="F11" s="15">
+        <f>(LbWk*Weeks-C11*DrumLb)*SNPlb</f>
+        <v/>
+      </c>
+      <c r="G11" s="15">
+        <f>E11+F11</f>
+        <v/>
+      </c>
+      <c r="H11" s="15">
+        <f>G11-LbWk*Weeks*SNPlb</f>
+        <v/>
+      </c>
+      <c r="I11" s="41">
+        <f>H11/(LbWk*Weeks*SNPlb)</f>
+        <v/>
+      </c>
+    </row>
     <row r="12">
-      <c r="B12" s="47" t="inlineStr">
-        <is>
-          <t>Five years at 1/3 share, PCI $3.50, volume +10%/yr</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="30" customHeight="1">
-      <c r="B13" s="3" t="inlineStr">
+      <c r="B12" s="11" t="inlineStr">
+        <is>
+          <t>Reference: 1 drum/week (52 drums) at the below-batch price</t>
+        </is>
+      </c>
+      <c r="C12" s="12" t="n">
+        <v>52</v>
+      </c>
+      <c r="D12" s="21">
+        <f>PCIsub</f>
+        <v/>
+      </c>
+      <c r="E12" s="15">
+        <f>C12*DrumLb*D12</f>
+        <v/>
+      </c>
+      <c r="F12" s="15">
+        <f>(LbWk*Weeks-C12*DrumLb)*SNPlb</f>
+        <v/>
+      </c>
+      <c r="G12" s="15">
+        <f>E12+F12</f>
+        <v/>
+      </c>
+      <c r="H12" s="15">
+        <f>G12-LbWk*Weeks*SNPlb</f>
+        <v/>
+      </c>
+      <c r="I12" s="41">
+        <f>H12/(LbWk*Weeks*SNPlb)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="47" t="inlineStr">
+        <is>
+          <t>Five years at 1/3 share (Option 1), PCI $3.50, volume +10%/yr</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="30" customHeight="1">
+      <c r="B15" s="3" t="inlineStr">
         <is>
           <t>Year</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
+      <c r="C15" s="3" t="inlineStr">
         <is>
           <t>Volume (lb)</t>
         </is>
       </c>
-      <c r="D13" s="3" t="inlineStr">
+      <c r="D15" s="3" t="inlineStr">
         <is>
           <t>Lb to PCI (1/3)</t>
         </is>
       </c>
-      <c r="E13" s="3" t="inlineStr">
+      <c r="E15" s="3" t="inlineStr">
         <is>
           <t>Batches of 5 (rounded)</t>
         </is>
       </c>
-      <c r="F13" s="3" t="inlineStr">
+      <c r="F15" s="3" t="inlineStr">
         <is>
           <t>Premium ($2.75/lb x lb to PCI)</t>
         </is>
       </c>
-      <c r="G13" s="3" t="inlineStr">
+      <c r="G15" s="3" t="inlineStr">
         <is>
           <t>Cumulative</t>
         </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="B14" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="C14" s="12">
-        <f>LbWk*Weeks*(1+Growth)^(1-1)</f>
-        <v/>
-      </c>
-      <c r="D14" s="12">
-        <f>C14/3</f>
-        <v/>
-      </c>
-      <c r="E14" s="12">
-        <f>ROUND(D14/DrumLb/PCIbatch,0)</f>
-        <v/>
-      </c>
-      <c r="F14" s="15">
-        <f>D14*(PCIq-SNPlb)</f>
-        <v/>
-      </c>
-      <c r="G14" s="15">
-        <f>F14</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15">
-      <c r="B15" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="C15" s="12">
-        <f>LbWk*Weeks*(1+Growth)^(2-1)</f>
-        <v/>
-      </c>
-      <c r="D15" s="12">
-        <f>C15/3</f>
-        <v/>
-      </c>
-      <c r="E15" s="12">
-        <f>ROUND(D15/DrumLb/PCIbatch,0)</f>
-        <v/>
-      </c>
-      <c r="F15" s="15">
-        <f>D15*(PCIq-SNPlb)</f>
-        <v/>
-      </c>
-      <c r="G15" s="15">
-        <f>G14+F15</f>
-        <v/>
       </c>
     </row>
     <row r="16">
       <c r="B16" s="11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C16" s="12">
-        <f>LbWk*Weeks*(1+Growth)^(3-1)</f>
+        <f>LbWk*Weeks*(1+Growth)^(1-1)</f>
         <v/>
       </c>
       <c r="D16" s="12">
@@ -1731,16 +6473,16 @@
         <v/>
       </c>
       <c r="G16" s="15">
-        <f>G15+F16</f>
+        <f>F16</f>
         <v/>
       </c>
     </row>
     <row r="17">
       <c r="B17" s="11" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C17" s="12">
-        <f>LbWk*Weeks*(1+Growth)^(4-1)</f>
+        <f>LbWk*Weeks*(1+Growth)^(2-1)</f>
         <v/>
       </c>
       <c r="D17" s="12">
@@ -1762,10 +6504,10 @@
     </row>
     <row r="18">
       <c r="B18" s="11" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C18" s="12">
-        <f>LbWk*Weeks*(1+Growth)^(5-1)</f>
+        <f>LbWk*Weeks*(1+Growth)^(3-1)</f>
         <v/>
       </c>
       <c r="D18" s="12">
@@ -1785,174 +6527,299 @@
         <v/>
       </c>
     </row>
+    <row r="19">
+      <c r="B19" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="C19" s="12">
+        <f>LbWk*Weeks*(1+Growth)^(4-1)</f>
+        <v/>
+      </c>
+      <c r="D19" s="12">
+        <f>C19/3</f>
+        <v/>
+      </c>
+      <c r="E19" s="12">
+        <f>ROUND(D19/DrumLb/PCIbatch,0)</f>
+        <v/>
+      </c>
+      <c r="F19" s="15">
+        <f>D19*(PCIq-SNPlb)</f>
+        <v/>
+      </c>
+      <c r="G19" s="15">
+        <f>G18+F19</f>
+        <v/>
+      </c>
+    </row>
     <row r="20">
-      <c r="B20" s="47" t="inlineStr">
+      <c r="B20" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="C20" s="12">
+        <f>LbWk*Weeks*(1+Growth)^(5-1)</f>
+        <v/>
+      </c>
+      <c r="D20" s="12">
+        <f>C20/3</f>
+        <v/>
+      </c>
+      <c r="E20" s="12">
+        <f>ROUND(D20/DrumLb/PCIbatch,0)</f>
+        <v/>
+      </c>
+      <c r="F20" s="15">
+        <f>D20*(PCIq-SNPlb)</f>
+        <v/>
+      </c>
+      <c r="G20" s="15">
+        <f>G19+F20</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="47" t="inlineStr">
         <is>
           <t>Break-even — outage cost that justifies the premium</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="30" customHeight="1">
-      <c r="B21" s="3" t="inlineStr">
+    <row r="23" ht="30" customHeight="1">
+      <c r="B23" s="3" t="inlineStr">
         <is>
           <t>Premium (Y1)</t>
         </is>
       </c>
-      <c r="C21" s="3" t="inlineStr">
+      <c r="C23" s="3" t="inlineStr">
         <is>
           <t>p = 2%</t>
         </is>
       </c>
-      <c r="D21" s="3" t="inlineStr">
+      <c r="D23" s="3" t="inlineStr">
         <is>
           <t>p = 5%</t>
         </is>
       </c>
-      <c r="E21" s="3" t="inlineStr">
+      <c r="E23" s="3" t="inlineStr">
         <is>
           <t>p = 10%</t>
         </is>
       </c>
-      <c r="F21" s="3" t="inlineStr">
+      <c r="F23" s="3" t="inlineStr">
         <is>
           <t>p = 20%</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="B22" s="15">
+    <row r="24">
+      <c r="B24" s="15">
         <f>H7</f>
         <v/>
       </c>
-      <c r="C22" s="15">
-        <f>B22/0.02</f>
-        <v/>
-      </c>
-      <c r="D22" s="15">
-        <f>B22/0.05</f>
-        <v/>
-      </c>
-      <c r="E22" s="15">
-        <f>B22/0.1</f>
-        <v/>
-      </c>
-      <c r="F22" s="15">
-        <f>B22/0.2</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24">
-      <c r="B24" s="47" t="inlineStr">
+      <c r="C24" s="15">
+        <f>B24/0.02</f>
+        <v/>
+      </c>
+      <c r="D24" s="15">
+        <f>B24/0.05</f>
+        <v/>
+      </c>
+      <c r="E24" s="15">
+        <f>B24/0.1</f>
+        <v/>
+      </c>
+      <c r="F24" s="15">
+        <f>B24/0.2</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="47" t="inlineStr">
         <is>
           <t>Block-rotation logistics of a 5-drum batch (shelf life 18 days)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="B25" s="17" t="inlineStr">
-        <is>
-          <t>Batch size (lb)</t>
-        </is>
-      </c>
-      <c r="C25" s="12">
-        <f>PCIbatch*DrumLb</f>
-        <v/>
-      </c>
-      <c r="D25" s="2" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="B26" s="17" t="inlineStr">
-        <is>
-          <t>Days of FULL demand in one batch</t>
-        </is>
-      </c>
-      <c r="C26" s="48">
-        <f>B25/(LbWk/7)</f>
-        <v/>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>Must be consumed within the 18-day shelf life -&gt; use at full rate on receipt</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="B27" s="17" t="inlineStr">
         <is>
-          <t>Cycle length at 1/3 share (weeks)</t>
-        </is>
-      </c>
-      <c r="C27" s="48">
-        <f>B25/(LbWk/3)</f>
-        <v/>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>One PCI batch every ~5 weeks</t>
-        </is>
-      </c>
+          <t>Batch size (lb)</t>
+        </is>
+      </c>
+      <c r="C27" s="12">
+        <f>PCIbatch*DrumLb</f>
+        <v/>
+      </c>
+      <c r="D27" s="2" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="B28" s="17" t="inlineStr">
         <is>
-          <t>Weeks on SNP material per cycle</t>
+          <t>Days of FULL demand in one batch</t>
         </is>
       </c>
       <c r="C28" s="48">
-        <f>B27-B25/LbWk</f>
+        <f>B27/(LbWk/7)</f>
         <v/>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>SNP sees a ~12-day gap every cycle: LUMPY demand</t>
+          <t>12.1 days — must be consumed within the shelf life -&gt; use at full rate on receipt</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="B29" s="17" t="inlineStr">
         <is>
-          <t>Days to consume a batch at 2/3 rate (needs 30-day shelf life)</t>
+          <t>Cycle length at 1/3 share (weeks)</t>
         </is>
       </c>
       <c r="C29" s="48">
-        <f>B25/(LbWk*2/3/7)</f>
+        <f>B27/(LbWk/3)</f>
         <v/>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>With a validated 30-day life, SNP can keep supplying at 1/3 rate during a PCI batch -&gt; smoother</t>
+          <t>One PCI batch every ~5 weeks (Year 1: 10 batches; ~15 by Year 5)</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="B30" s="17" t="inlineStr">
         <is>
-          <t>One qualification batch — cost</t>
-        </is>
-      </c>
-      <c r="C30" s="15">
-        <f>B25*PCIq</f>
+          <t>Weeks on SNP material per cycle</t>
+        </is>
+      </c>
+      <c r="C30" s="48">
+        <f>B29-B27/LbWk</f>
         <v/>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>A single production-scale batch (Option B-plus)</t>
+          <t>Cadence is a choice: (i) block rotation = a ~12-day pause in SNP orders per cycle; (ii) SNP keeps ~2 drums/wk and we hold ~3 drums of rolling stock (peak ~8 drums, strict first-in-first-out) — the shelf-life study decides</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="B31" s="17" t="inlineStr">
         <is>
+          <t>Age of PCI drums on receipt (days: cook, release, transit) — INPUT</t>
+        </is>
+      </c>
+      <c r="C31" s="63" t="n">
+        <v>4</v>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>Assumption: the 18-day clock starts at manufacture. Confirm PCI lead time and transit St. Louis -&gt; site</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="17" t="inlineStr">
+        <is>
+          <t>Usable days on receipt (18-day life)</t>
+        </is>
+      </c>
+      <c r="C32" s="48">
+        <f>18-B31</f>
+        <v/>
+      </c>
+      <c r="D32" s="2" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="B33" s="17" t="inlineStr">
+        <is>
+          <t>Slack in block rotation (days)</t>
+        </is>
+      </c>
+      <c r="C33" s="48">
+        <f>B32-B28</f>
+        <v/>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>~1–2 days: block rotation has almost no margin at 18 days; a validated 21-day life gives real margin</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" s="17" t="inlineStr">
+        <is>
+          <t>Days to consume a batch at 2/3 rate</t>
+        </is>
+      </c>
+      <c r="C34" s="48">
+        <f>B27/(LbWk*2/3/7)</f>
+        <v/>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>18.2 days — needs a validated life longer than 18.2 days plus the age on receipt</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="17" t="inlineStr">
+        <is>
+          <t>Days to consume a batch at an exact 1/3 rate</t>
+        </is>
+      </c>
+      <c r="C35" s="48">
+        <f>B27/(LbWk/3/7)</f>
+        <v/>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>36.3 days — a true one-third blend needs a ~40-day validated life</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" s="17" t="inlineStr">
+        <is>
+          <t>Minimum PCI share of rate under a 30-day life</t>
+        </is>
+      </c>
+      <c r="C36" s="24">
+        <f>B27/((30-B31)*LbWk/7)</f>
+        <v/>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>~47% at 4 days' age: even a 30-day life does not allow a one-third blend</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" s="17" t="inlineStr">
+        <is>
+          <t>One qualification batch — cost</t>
+        </is>
+      </c>
+      <c r="C37" s="15">
+        <f>B27*PCIq</f>
+        <v/>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>A single production-scale batch (Option B-plus); $7.9k gross</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" s="17" t="inlineStr">
+        <is>
           <t>One qualification batch — premium over SNP</t>
         </is>
       </c>
-      <c r="C31" s="15">
-        <f>B25*(PCIq-SNPlb)</f>
-        <v/>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>~4% of annual volume; invisible to SNP's year</t>
+      <c r="C38" s="15">
+        <f>B27*(PCIq-SNPlb)</f>
+        <v/>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>3.3% of annual volume (2,250 of 67,600 lb); one ~12-day pause in SNP orders</t>
         </is>
       </c>
     </row>
@@ -1961,7 +6828,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2198,7 +7065,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2231,7 +7098,7 @@
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Each year the second source gets max(1/3 of demand, 1 drum/week). Premium = share x (PCI price - SNP price) x annual lb; it grows with volume.</t>
+          <t>Second source at an exact one-third of each year's demand (batches round differently each year). The Year-1 headline elsewhere uses 10 whole batches (50 drums, $61,875) — $92 apart. Premium = share x (PCI price - SNP price) x volume; MID = the real quote.</t>
         </is>
       </c>
     </row>
@@ -2310,7 +7177,7 @@
         <v/>
       </c>
       <c r="E6" s="13">
-        <f>MAX(Share,MinDrumsWk*Weeks*DrumLb/C6)</f>
+        <f>Share</f>
         <v/>
       </c>
       <c r="F6" s="14">
@@ -2359,7 +7226,7 @@
         <v/>
       </c>
       <c r="E7" s="13">
-        <f>MAX(Share,MinDrumsWk*Weeks*DrumLb/C7)</f>
+        <f>Share</f>
         <v/>
       </c>
       <c r="F7" s="14">
@@ -2408,7 +7275,7 @@
         <v/>
       </c>
       <c r="E8" s="13">
-        <f>MAX(Share,MinDrumsWk*Weeks*DrumLb/C8)</f>
+        <f>Share</f>
         <v/>
       </c>
       <c r="F8" s="14">
@@ -2457,7 +7324,7 @@
         <v/>
       </c>
       <c r="E9" s="13">
-        <f>MAX(Share,MinDrumsWk*Weeks*DrumLb/C9)</f>
+        <f>Share</f>
         <v/>
       </c>
       <c r="F9" s="14">
@@ -2506,7 +7373,7 @@
         <v/>
       </c>
       <c r="E10" s="13">
-        <f>MAX(Share,MinDrumsWk*Weeks*DrumLb/C10)</f>
+        <f>Share</f>
         <v/>
       </c>
       <c r="F10" s="14">
@@ -2601,7 +7468,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2619,14 +7486,14 @@
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>What drives the premium (Year 1, at the supplier minimum ≈ 1/3)</t>
+          <t>What drives the premium (Year 1, second source = 10 whole 5-drum batches = 50 drums)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Price is what the market gives us. Share is NOT a free lever: anything below the supplier minimum is not available.</t>
+          <t>Price is what the market gives us. Below one 5-drum batch PCI charges $6.00/lb, so there is no cheap small-order version.</t>
         </is>
       </c>
     </row>
@@ -2659,7 +7526,7 @@
       </c>
       <c r="C6" s="22" t="inlineStr">
         <is>
-          <t>Market LOW</t>
+          <t>Market — high quantity (bulk/tote)</t>
         </is>
       </c>
       <c r="D6" s="15">
@@ -2677,7 +7544,7 @@
       </c>
       <c r="C7" s="22" t="inlineStr">
         <is>
-          <t>Upside case / assumed in July (low)</t>
+          <t>July 2026 assumption, low (superseded)</t>
         </is>
       </c>
       <c r="D7" s="15">
@@ -2695,7 +7562,7 @@
       </c>
       <c r="C8" s="22" t="inlineStr">
         <is>
-          <t>Upside case / assumed in July (high)</t>
+          <t>July 2026 assumption, high (superseded)</t>
         </is>
       </c>
       <c r="D8" s="15">
@@ -2714,7 +7581,7 @@
       </c>
       <c r="C9" s="22" t="inlineStr">
         <is>
-          <t>Market BASE</t>
+          <t>Market — competitive quantity (drum scale)</t>
         </is>
       </c>
       <c r="D9" s="15">
@@ -2769,7 +7636,7 @@
       </c>
       <c r="C12" s="22" t="inlineStr">
         <is>
-          <t>Market HIGH</t>
+          <t>Market — low quantity (small packs)</t>
         </is>
       </c>
       <c r="D12" s="15">
@@ -2788,7 +7655,7 @@
       </c>
       <c r="C13" s="22" t="inlineStr">
         <is>
-          <t>PCI LOW</t>
+          <t>Sensitivity — below the quote</t>
         </is>
       </c>
       <c r="D13" s="15">
@@ -2807,7 +7674,7 @@
       </c>
       <c r="C14" s="22" t="inlineStr">
         <is>
-          <t>PCI MID</t>
+          <t>PCI real quote ($3.50, one 5-drum batch)</t>
         </is>
       </c>
       <c r="D14" s="15">
@@ -2826,7 +7693,7 @@
       </c>
       <c r="C15" s="22" t="inlineStr">
         <is>
-          <t>PCI HIGH</t>
+          <t>Sensitivity — above the quote</t>
         </is>
       </c>
       <c r="D15" s="15">
@@ -2865,17 +7732,17 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Drums/week</t>
+          <t>Batches of 5 drums / yr</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>Available?</t>
+          <t>Available at $3.50?</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>Premium @ PCI MID</t>
+          <t>Premium @ PCI quote</t>
         </is>
       </c>
     </row>
@@ -2883,16 +7750,16 @@
       <c r="B18" s="24" t="n">
         <v>0.05</v>
       </c>
-      <c r="C18" s="14">
-        <f>LbWk*B18/DrumLb</f>
+      <c r="C18" s="48">
+        <f>B18*LbWk*Weeks/(DrumLb*PCIbatch)</f>
         <v/>
       </c>
       <c r="D18" s="25">
-        <f>IF(C18&gt;=MinDrumsWk,"Yes",IF(B18&gt;=0.3,"Rounds up to the 1-drum minimum","NO — below supplier minimum"))</f>
+        <f>IF(C18&lt;1,"Below one batch — $6.00/lb","Yes at $3.50 — no volume term attached to the batch price so far (confirm in writing)")</f>
         <v/>
       </c>
       <c r="E18" s="26">
-        <f>IF(B18&gt;=0.3,LbWk*Weeks*MAX(B18,MinShare)*(PCImid-SNPlb),"n/a")</f>
+        <f>B18*LbWk*Weeks*(PCIq-SNPlb)</f>
         <v/>
       </c>
     </row>
@@ -2900,16 +7767,16 @@
       <c r="B19" s="24" t="n">
         <v>0.1</v>
       </c>
-      <c r="C19" s="14">
-        <f>LbWk*B19/DrumLb</f>
+      <c r="C19" s="48">
+        <f>B19*LbWk*Weeks/(DrumLb*PCIbatch)</f>
         <v/>
       </c>
       <c r="D19" s="25">
-        <f>IF(C19&gt;=MinDrumsWk,"Yes",IF(B19&gt;=0.3,"Rounds up to the 1-drum minimum","NO — below supplier minimum"))</f>
+        <f>IF(C19&lt;1,"Below one batch — $6.00/lb","Yes at $3.50 — no volume term attached to the batch price so far (confirm in writing)")</f>
         <v/>
       </c>
       <c r="E19" s="26">
-        <f>IF(B19&gt;=0.3,LbWk*Weeks*MAX(B19,MinShare)*(PCImid-SNPlb),"n/a")</f>
+        <f>B19*LbWk*Weeks*(PCIq-SNPlb)</f>
         <v/>
       </c>
     </row>
@@ -2917,16 +7784,16 @@
       <c r="B20" s="24" t="n">
         <v>0.2</v>
       </c>
-      <c r="C20" s="14">
-        <f>LbWk*B20/DrumLb</f>
+      <c r="C20" s="48">
+        <f>B20*LbWk*Weeks/(DrumLb*PCIbatch)</f>
         <v/>
       </c>
       <c r="D20" s="25">
-        <f>IF(C20&gt;=MinDrumsWk,"Yes",IF(B20&gt;=0.3,"Rounds up to the 1-drum minimum","NO — below supplier minimum"))</f>
+        <f>IF(C20&lt;1,"Below one batch — $6.00/lb","Yes at $3.50 — no volume term attached to the batch price so far (confirm in writing)")</f>
         <v/>
       </c>
       <c r="E20" s="26">
-        <f>IF(B20&gt;=0.3,LbWk*Weeks*MAX(B20,MinShare)*(PCImid-SNPlb),"n/a")</f>
+        <f>B20*LbWk*Weeks*(PCIq-SNPlb)</f>
         <v/>
       </c>
     </row>
@@ -2934,16 +7801,16 @@
       <c r="B21" s="24" t="n">
         <v>0.3333333333333333</v>
       </c>
-      <c r="C21" s="14">
-        <f>LbWk*B21/DrumLb</f>
+      <c r="C21" s="48">
+        <f>B21*LbWk*Weeks/(DrumLb*PCIbatch)</f>
         <v/>
       </c>
       <c r="D21" s="27">
-        <f>IF(C21&gt;=MinDrumsWk,"Yes",IF(B21&gt;=0.3,"Rounds up to the 1-drum minimum","NO — below supplier minimum"))</f>
+        <f>IF(C21&lt;1,"Below one batch — $6.00/lb","Yes at $3.50 — no volume term attached to the batch price so far (confirm in writing)")</f>
         <v/>
       </c>
       <c r="E21" s="15">
-        <f>IF(B21&gt;=0.3,LbWk*Weeks*MAX(B21,MinShare)*(PCImid-SNPlb),"n/a")</f>
+        <f>B21*LbWk*Weeks*(PCIq-SNPlb)</f>
         <v/>
       </c>
     </row>
@@ -2951,23 +7818,23 @@
       <c r="B22" s="24" t="n">
         <v>0.5</v>
       </c>
-      <c r="C22" s="14">
-        <f>LbWk*B22/DrumLb</f>
+      <c r="C22" s="48">
+        <f>B22*LbWk*Weeks/(DrumLb*PCIbatch)</f>
         <v/>
       </c>
       <c r="D22" s="27">
-        <f>IF(C22&gt;=MinDrumsWk,"Yes",IF(B22&gt;=0.3,"Rounds up to the 1-drum minimum","NO — below supplier minimum"))</f>
+        <f>IF(C22&lt;1,"Below one batch — $6.00/lb","Yes at $3.50 — no volume term attached to the batch price so far (confirm in writing)")</f>
         <v/>
       </c>
       <c r="E22" s="15">
-        <f>IF(B22&gt;=0.3,LbWk*Weeks*MAX(B22,MinShare)*(PCImid-SNPlb),"n/a")</f>
+        <f>B22*LbWk*Weeks*(PCIq-SNPlb)</f>
         <v/>
       </c>
     </row>
     <row r="24">
       <c r="B24" s="28" t="inlineStr">
         <is>
-          <t>This is why there is no 'low-cost insurance' version of Option A: the smallest second source anyone will sell us is one drum a week.</t>
+          <t>No small-order version exists at this price: below a 5-drum batch PCI charges $6.00/lb. Above it, the $3.50 batch price carries no volume term so far — Option 3 (1–2 batches a year) rests on that; confirm it in writing.</t>
         </is>
       </c>
     </row>
@@ -2976,7 +7843,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2996,7 +7863,7 @@
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>If SNP Inc. raises price on the volume it keeps (Year 1, PCI MID)</t>
+          <t>If SNP Inc. raises price on the volume it keeps (Year 1, PCI quote $3.50, 50 drums to PCI)</t>
         </is>
       </c>
     </row>
@@ -3162,361 +8029,6 @@
       <c r="G10" s="15">
         <f>F10-LbWk*Weeks*SNPlb</f>
         <v/>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="B2:G13"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-  </cols>
-  <sheetData>
-    <row r="2">
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t>Is the insurance worth it? Premium vs (probability x avoided loss)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>Option A is justified only if: annual premium &lt;= P(SNP disruption in a year) x loss the second source would AVOID. ~2/3 of volume is still exposed until PCI can ramp.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="30" customHeight="1">
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>Option A price case</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>Annual premium</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>p = 2%</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>p = 5%</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>p = 10%</t>
-        </is>
-      </c>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t>p = 20%</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="B6" s="11" t="inlineStr">
-        <is>
-          <t>PCI LOW $2.50</t>
-        </is>
-      </c>
-      <c r="C6" s="15">
-        <f>LbWk*Weeks*EffShare*(PCIlo-SNPlb)</f>
-        <v/>
-      </c>
-      <c r="D6" s="15">
-        <f>C6/0.02</f>
-        <v/>
-      </c>
-      <c r="E6" s="15">
-        <f>C6/0.05</f>
-        <v/>
-      </c>
-      <c r="F6" s="15">
-        <f>C6/0.1</f>
-        <v/>
-      </c>
-      <c r="G6" s="15">
-        <f>C6/0.2</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7">
-      <c r="B7" s="11" t="inlineStr">
-        <is>
-          <t>PCI MID $3.75</t>
-        </is>
-      </c>
-      <c r="C7" s="15">
-        <f>LbWk*Weeks*EffShare*(PCImid-SNPlb)</f>
-        <v/>
-      </c>
-      <c r="D7" s="15">
-        <f>C7/0.02</f>
-        <v/>
-      </c>
-      <c r="E7" s="15">
-        <f>C7/0.05</f>
-        <v/>
-      </c>
-      <c r="F7" s="15">
-        <f>C7/0.1</f>
-        <v/>
-      </c>
-      <c r="G7" s="15">
-        <f>C7/0.2</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8">
-      <c r="B8" s="11" t="inlineStr">
-        <is>
-          <t>PCI HIGH $5.00</t>
-        </is>
-      </c>
-      <c r="C8" s="15">
-        <f>LbWk*Weeks*EffShare*(PCIhi-SNPlb)</f>
-        <v/>
-      </c>
-      <c r="D8" s="15">
-        <f>C8/0.02</f>
-        <v/>
-      </c>
-      <c r="E8" s="15">
-        <f>C8/0.05</f>
-        <v/>
-      </c>
-      <c r="F8" s="15">
-        <f>C8/0.1</f>
-        <v/>
-      </c>
-      <c r="G8" s="15">
-        <f>C8/0.2</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10">
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>Read: each cell = the avoided loss an SNP outage would have to cause for the premium to pay off. Compare to Inputs 'Cost of a 6-month SNP Inc. outage'.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="B12" s="17" t="inlineStr">
-        <is>
-          <t>Expected annual loss with NO second source = Pdis x Dcost:</t>
-        </is>
-      </c>
-      <c r="D12" s="20">
-        <f>Pdis*Dcost</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13">
-      <c r="B13" s="17" t="inlineStr">
-        <is>
-          <t>Verdict @ PCI MID:</t>
-        </is>
-      </c>
-      <c r="D13">
-        <f>IF(D12&gt;=C7,"Option A is justified","Premium exceeds expected loss — Option B")</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="B2:D13"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="42" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="2">
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t>The two options, side by side (Year 1, PCI MID unless noted)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>There is no smaller version of A: the supplier minimum is one drum a week.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="30" customHeight="1">
-      <c r="B5" s="3" t="inlineStr"/>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>A — Second source (PCI Manufacturing) at ~1/3</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>B — Single source (SNP Inc.) + strengthen</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="B6" s="17" t="inlineStr">
-        <is>
-          <t>Annual purchase cost</t>
-        </is>
-      </c>
-      <c r="C6" s="29">
-        <f>LbWk*Weeks*(1-EffShare)*SNPlb+LbWk*Weeks*EffShare*PCImid</f>
-        <v/>
-      </c>
-      <c r="D6" s="29">
-        <f>LbWk*Weeks*SNPlb</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7">
-      <c r="B7" s="17" t="inlineStr">
-        <is>
-          <t>Premium vs today</t>
-        </is>
-      </c>
-      <c r="C7" s="29">
-        <f>B6-LbWk*Weeks*SNPlb</f>
-        <v/>
-      </c>
-      <c r="D7" s="30" t="inlineStr">
-        <is>
-          <t>0 (+ small continuity spend)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="B8" s="17" t="inlineStr">
-        <is>
-          <t>One-time qualification</t>
-        </is>
-      </c>
-      <c r="C8" s="29">
-        <f>QualCost</f>
-        <v/>
-      </c>
-      <c r="D8" s="30" t="inlineStr">
-        <is>
-          <t>0 (plan/document only)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="B9" s="17" t="inlineStr">
-        <is>
-          <t>5-yr premium (10% growth)</t>
-        </is>
-      </c>
-      <c r="C9" s="29">
-        <f>'5-Year'!L11</f>
-        <v/>
-      </c>
-      <c r="D9" s="30" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="B10" s="17" t="inlineStr">
-        <is>
-          <t>Volume still exposed if SNP fails</t>
-        </is>
-      </c>
-      <c r="C10" s="30" t="inlineStr">
-        <is>
-          <t>~2/3 (until PCI ramps — unconfirmed)</t>
-        </is>
-      </c>
-      <c r="D10" s="30" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="B11" s="17" t="inlineStr">
-        <is>
-          <t>Time to recover if SNP fails</t>
-        </is>
-      </c>
-      <c r="C11" s="30" t="inlineStr">
-        <is>
-          <t>weeks (PCI ramp)</t>
-        </is>
-      </c>
-      <c r="D11" s="30" t="inlineStr">
-        <is>
-          <t>6-12 months cold start; 3-4 with kit current</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="B12" s="17" t="inlineStr">
-        <is>
-          <t>Signal to SNP Inc.</t>
-        </is>
-      </c>
-      <c r="C12" s="30" t="inlineStr">
-        <is>
-          <t>Lost a third of its volume</t>
-        </is>
-      </c>
-      <c r="D12" s="30" t="inlineStr">
-        <is>
-          <t>Deeper partnership</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="B13" s="17" t="inlineStr">
-        <is>
-          <t>Compliance posture</t>
-        </is>
-      </c>
-      <c r="C13" s="30" t="inlineStr">
-        <is>
-          <t>Strong</t>
-        </is>
-      </c>
-      <c r="D13" s="30" t="inlineStr">
-        <is>
-          <t>Defensible if risk + plan documented</t>
-        </is>
       </c>
     </row>
   </sheetData>

--- a/PVA second supplier initiative/PVA_Second_Supplier_Leadership_Model.xlsx
+++ b/PVA second supplier initiative/PVA_Second_Supplier_Leadership_Model.xlsx
@@ -712,7 +712,7 @@
       </c>
       <c r="D6" s="52" t="inlineStr">
         <is>
-          <t>Slide 5 — identical in every bar</t>
+          <t>Slide 4 — identical in every bar</t>
         </is>
       </c>
     </row>
@@ -728,7 +728,7 @@
       </c>
       <c r="D7" s="52" t="inlineStr">
         <is>
-          <t>Slide 5</t>
+          <t>Slide 4</t>
         </is>
       </c>
     </row>
@@ -744,7 +744,7 @@
       </c>
       <c r="D8" s="52" t="inlineStr">
         <is>
-          <t>Slide 5 — every option</t>
+          <t>Slide 4 — every option</t>
         </is>
       </c>
     </row>
@@ -760,7 +760,7 @@
       </c>
       <c r="D9" s="52" t="inlineStr">
         <is>
-          <t>Slides 3, 5, 7, 8</t>
+          <t>Slides 4, 6, 7</t>
         </is>
       </c>
     </row>
@@ -776,7 +776,7 @@
       </c>
       <c r="D10" s="52" t="inlineStr">
         <is>
-          <t>Slide 5</t>
+          <t>Slide 4</t>
         </is>
       </c>
     </row>
@@ -792,7 +792,7 @@
       </c>
       <c r="D11" s="52" t="inlineStr">
         <is>
-          <t>Slide 5</t>
+          <t>Slide 4</t>
         </is>
       </c>
     </row>
@@ -808,7 +808,7 @@
       </c>
       <c r="D12" s="52" t="inlineStr">
         <is>
-          <t>Slides 5, 8</t>
+          <t>Slides 4, 7</t>
         </is>
       </c>
     </row>
@@ -824,7 +824,7 @@
       </c>
       <c r="D13" s="56" t="inlineStr">
         <is>
-          <t>Slides 5, 6, 8, 11</t>
+          <t>Slides 4, 5, 7, 10</t>
         </is>
       </c>
     </row>
@@ -840,7 +840,7 @@
       </c>
       <c r="D14" s="52" t="inlineStr">
         <is>
-          <t>Slide 5</t>
+          <t>Slide 4</t>
         </is>
       </c>
     </row>
@@ -856,7 +856,7 @@
       </c>
       <c r="D15" s="52" t="inlineStr">
         <is>
-          <t>Slide 5</t>
+          <t>Slide 4</t>
         </is>
       </c>
     </row>
@@ -872,7 +872,7 @@
       </c>
       <c r="D16" s="52" t="inlineStr">
         <is>
-          <t>Slide 5</t>
+          <t>Slide 4</t>
         </is>
       </c>
     </row>
@@ -888,7 +888,7 @@
       </c>
       <c r="D17" s="52" t="inlineStr">
         <is>
-          <t>Slides 6, 8</t>
+          <t>Slides 5, 7</t>
         </is>
       </c>
     </row>
@@ -904,7 +904,7 @@
       </c>
       <c r="D18" s="52" t="inlineStr">
         <is>
-          <t>Slide 11</t>
+          <t>Slide 10</t>
         </is>
       </c>
     </row>
@@ -920,7 +920,7 @@
       </c>
       <c r="D19" s="52" t="inlineStr">
         <is>
-          <t>Slide 11</t>
+          <t>Slide 10</t>
         </is>
       </c>
     </row>
@@ -952,7 +952,7 @@
       </c>
       <c r="D21" s="52" t="inlineStr">
         <is>
-          <t>Slides 6, 8, 9, 11</t>
+          <t>Slides 5, 7, 8, 10</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="D22" s="52" t="inlineStr">
         <is>
-          <t>Slides 6, 9</t>
+          <t>Slides 5, 8</t>
         </is>
       </c>
     </row>
@@ -984,7 +984,7 @@
       </c>
       <c r="D23" s="52" t="inlineStr">
         <is>
-          <t>Slides 6, 8</t>
+          <t>Slides 5, 7</t>
         </is>
       </c>
     </row>
@@ -1000,7 +1000,7 @@
       </c>
       <c r="D24" s="52" t="inlineStr">
         <is>
-          <t>Slides 3, 7</t>
+          <t>Slide 6</t>
         </is>
       </c>
     </row>
@@ -1016,7 +1016,7 @@
       </c>
       <c r="D25" s="52" t="inlineStr">
         <is>
-          <t>Slide 7</t>
+          <t>Slide 6</t>
         </is>
       </c>
     </row>
@@ -1032,7 +1032,7 @@
       </c>
       <c r="D26" s="52" t="inlineStr">
         <is>
-          <t>Slide 11</t>
+          <t>Slide 10</t>
         </is>
       </c>
     </row>
@@ -1048,7 +1048,7 @@
       </c>
       <c r="D27" s="52" t="inlineStr">
         <is>
-          <t>Slides 6, 8, 9, 11</t>
+          <t>Slides 5, 7, 8, 10</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="D28" s="52" t="inlineStr">
         <is>
-          <t>Slides 8, 9</t>
+          <t>Slides 7, 8</t>
         </is>
       </c>
     </row>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="D29" s="52" t="inlineStr">
         <is>
-          <t>Slide 8</t>
+          <t>Slide 7</t>
         </is>
       </c>
     </row>

--- a/PVA second supplier initiative/PVA_Second_Supplier_Leadership_Model.xlsx
+++ b/PVA second supplier initiative/PVA_Second_Supplier_Leadership_Model.xlsx
@@ -712,7 +712,7 @@
       </c>
       <c r="D6" s="52" t="inlineStr">
         <is>
-          <t>Slide 4 — identical in every bar</t>
+          <t>Annual-cost slide — identical in every bar</t>
         </is>
       </c>
     </row>
@@ -728,7 +728,7 @@
       </c>
       <c r="D7" s="52" t="inlineStr">
         <is>
-          <t>Slide 4</t>
+          <t>Annual-cost slide</t>
         </is>
       </c>
     </row>
@@ -744,7 +744,7 @@
       </c>
       <c r="D8" s="52" t="inlineStr">
         <is>
-          <t>Slide 4 — every option</t>
+          <t>Annual-cost slide — every option</t>
         </is>
       </c>
     </row>
@@ -760,7 +760,7 @@
       </c>
       <c r="D9" s="52" t="inlineStr">
         <is>
-          <t>Slides 4, 6, 7</t>
+          <t>Annual-cost, logistics, options slides</t>
         </is>
       </c>
     </row>
@@ -776,7 +776,7 @@
       </c>
       <c r="D10" s="52" t="inlineStr">
         <is>
-          <t>Slide 4</t>
+          <t>Annual-cost slide</t>
         </is>
       </c>
     </row>
@@ -792,7 +792,7 @@
       </c>
       <c r="D11" s="52" t="inlineStr">
         <is>
-          <t>Slide 4</t>
+          <t>Annual-cost slide</t>
         </is>
       </c>
     </row>
@@ -808,7 +808,7 @@
       </c>
       <c r="D12" s="52" t="inlineStr">
         <is>
-          <t>Slides 4, 7</t>
+          <t>Annual-cost and options slides</t>
         </is>
       </c>
     </row>
@@ -824,7 +824,7 @@
       </c>
       <c r="D13" s="56" t="inlineStr">
         <is>
-          <t>Slides 4, 5, 7, 10</t>
+          <t>Annual-cost, chronology, options, recommendation slides</t>
         </is>
       </c>
     </row>
@@ -840,7 +840,7 @@
       </c>
       <c r="D14" s="52" t="inlineStr">
         <is>
-          <t>Slide 4</t>
+          <t>Annual-cost slide</t>
         </is>
       </c>
     </row>
@@ -856,7 +856,7 @@
       </c>
       <c r="D15" s="52" t="inlineStr">
         <is>
-          <t>Slide 4</t>
+          <t>Annual-cost slide</t>
         </is>
       </c>
     </row>
@@ -872,7 +872,7 @@
       </c>
       <c r="D16" s="52" t="inlineStr">
         <is>
-          <t>Slide 4</t>
+          <t>Annual-cost slide</t>
         </is>
       </c>
     </row>
@@ -888,7 +888,7 @@
       </c>
       <c r="D17" s="52" t="inlineStr">
         <is>
-          <t>Slides 5, 7</t>
+          <t>Chronology and options slides</t>
         </is>
       </c>
     </row>
@@ -904,7 +904,7 @@
       </c>
       <c r="D18" s="52" t="inlineStr">
         <is>
-          <t>Slide 10</t>
+          <t>Recommendation slide</t>
         </is>
       </c>
     </row>
@@ -920,7 +920,7 @@
       </c>
       <c r="D19" s="52" t="inlineStr">
         <is>
-          <t>Slide 10</t>
+          <t>Recommendation slide</t>
         </is>
       </c>
     </row>
@@ -952,7 +952,7 @@
       </c>
       <c r="D21" s="52" t="inlineStr">
         <is>
-          <t>Slides 5, 7, 8, 10</t>
+          <t>Chronology, options, keep-alive, recommendation slides</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="D22" s="52" t="inlineStr">
         <is>
-          <t>Slides 5, 8</t>
+          <t>Chronology and keep-alive slides</t>
         </is>
       </c>
     </row>
@@ -984,7 +984,7 @@
       </c>
       <c r="D23" s="52" t="inlineStr">
         <is>
-          <t>Slides 5, 7</t>
+          <t>Chronology and options slides</t>
         </is>
       </c>
     </row>
@@ -1000,7 +1000,7 @@
       </c>
       <c r="D24" s="52" t="inlineStr">
         <is>
-          <t>Slide 6</t>
+          <t>Logistics slide</t>
         </is>
       </c>
     </row>
@@ -1016,7 +1016,7 @@
       </c>
       <c r="D25" s="52" t="inlineStr">
         <is>
-          <t>Slide 6</t>
+          <t>Logistics slide</t>
         </is>
       </c>
     </row>
@@ -1032,7 +1032,7 @@
       </c>
       <c r="D26" s="52" t="inlineStr">
         <is>
-          <t>Slide 10</t>
+          <t>Recommendation slide</t>
         </is>
       </c>
     </row>
@@ -1048,7 +1048,7 @@
       </c>
       <c r="D27" s="52" t="inlineStr">
         <is>
-          <t>Slides 5, 7, 8, 10</t>
+          <t>Chronology, options, keep-alive, recommendation slides</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="D28" s="52" t="inlineStr">
         <is>
-          <t>Slides 7, 8</t>
+          <t>Options and keep-alive slides</t>
         </is>
       </c>
     </row>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="D29" s="52" t="inlineStr">
         <is>
-          <t>Slide 7</t>
+          <t>Options slide</t>
         </is>
       </c>
     </row>

--- a/PVA second supplier initiative/PVA_Second_Supplier_Leadership_Model.xlsx
+++ b/PVA second supplier initiative/PVA_Second_Supplier_Leadership_Model.xlsx
@@ -6106,7 +6106,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:I38"/>
+  <dimension ref="B2:I39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="2" max="2"/>
@@ -6246,7 +6246,7 @@
     <row r="8">
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>Option 1 — same 1/3 but ordered below batch size ($6.00) — chart bar</t>
+          <t>Option 1 — same 1/3 but ordered below batch size ($6.00) — reference</t>
         </is>
       </c>
       <c r="C8" s="12" t="n">
@@ -6382,14 +6382,14 @@
     <row r="12">
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>Reference: 1 drum/week (52 drums) at the below-batch price</t>
+          <t>Option 3 — keep-alive: 3 batches (15 drums) / yr at $3.50</t>
         </is>
       </c>
       <c r="C12" s="12" t="n">
-        <v>52</v>
+        <v>15</v>
       </c>
       <c r="D12" s="21">
-        <f>PCIsub</f>
+        <f>PCIq</f>
         <v/>
       </c>
       <c r="E12" s="15">
@@ -6413,76 +6413,85 @@
         <v/>
       </c>
     </row>
-    <row r="14">
-      <c r="B14" s="47" t="inlineStr">
+    <row r="13">
+      <c r="B13" s="11" t="inlineStr">
+        <is>
+          <t>PCI $6.00 at 1 drum/week (52 drums, 23,400 lb ≈ 35% ≈ almost one-third) — chart bar</t>
+        </is>
+      </c>
+      <c r="C13" s="12" t="n">
+        <v>52</v>
+      </c>
+      <c r="D13" s="21">
+        <f>PCIsub</f>
+        <v/>
+      </c>
+      <c r="E13" s="15">
+        <f>C13*DrumLb*D13</f>
+        <v/>
+      </c>
+      <c r="F13" s="15">
+        <f>(LbWk*Weeks-C13*DrumLb)*SNPlb</f>
+        <v/>
+      </c>
+      <c r="G13" s="15">
+        <f>E13+F13</f>
+        <v/>
+      </c>
+      <c r="H13" s="15">
+        <f>G13-LbWk*Weeks*SNPlb</f>
+        <v/>
+      </c>
+      <c r="I13" s="41">
+        <f>H13/(LbWk*Weeks*SNPlb)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="47" t="inlineStr">
         <is>
           <t>Five years at 1/3 share (Option 1), PCI $3.50, volume +10%/yr</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="30" customHeight="1">
-      <c r="B15" s="3" t="inlineStr">
+    <row r="16" ht="30" customHeight="1">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Year</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
+      <c r="C16" s="3" t="inlineStr">
         <is>
           <t>Volume (lb)</t>
         </is>
       </c>
-      <c r="D15" s="3" t="inlineStr">
+      <c r="D16" s="3" t="inlineStr">
         <is>
           <t>Lb to PCI (1/3)</t>
         </is>
       </c>
-      <c r="E15" s="3" t="inlineStr">
+      <c r="E16" s="3" t="inlineStr">
         <is>
           <t>Batches of 5 (rounded)</t>
         </is>
       </c>
-      <c r="F15" s="3" t="inlineStr">
+      <c r="F16" s="3" t="inlineStr">
         <is>
           <t>Premium ($2.75/lb x lb to PCI)</t>
         </is>
       </c>
-      <c r="G15" s="3" t="inlineStr">
+      <c r="G16" s="3" t="inlineStr">
         <is>
           <t>Cumulative</t>
         </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="B16" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="C16" s="12">
-        <f>LbWk*Weeks*(1+Growth)^(1-1)</f>
-        <v/>
-      </c>
-      <c r="D16" s="12">
-        <f>C16/3</f>
-        <v/>
-      </c>
-      <c r="E16" s="12">
-        <f>ROUND(D16/DrumLb/PCIbatch,0)</f>
-        <v/>
-      </c>
-      <c r="F16" s="15">
-        <f>D16*(PCIq-SNPlb)</f>
-        <v/>
-      </c>
-      <c r="G16" s="15">
-        <f>F16</f>
-        <v/>
       </c>
     </row>
     <row r="17">
       <c r="B17" s="11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C17" s="12">
-        <f>LbWk*Weeks*(1+Growth)^(2-1)</f>
+        <f>LbWk*Weeks*(1+Growth)^(1-1)</f>
         <v/>
       </c>
       <c r="D17" s="12">
@@ -6498,16 +6507,16 @@
         <v/>
       </c>
       <c r="G17" s="15">
-        <f>G16+F17</f>
+        <f>F17</f>
         <v/>
       </c>
     </row>
     <row r="18">
       <c r="B18" s="11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C18" s="12">
-        <f>LbWk*Weeks*(1+Growth)^(3-1)</f>
+        <f>LbWk*Weeks*(1+Growth)^(2-1)</f>
         <v/>
       </c>
       <c r="D18" s="12">
@@ -6529,10 +6538,10 @@
     </row>
     <row r="19">
       <c r="B19" s="11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C19" s="12">
-        <f>LbWk*Weeks*(1+Growth)^(4-1)</f>
+        <f>LbWk*Weeks*(1+Growth)^(3-1)</f>
         <v/>
       </c>
       <c r="D19" s="12">
@@ -6554,10 +6563,10 @@
     </row>
     <row r="20">
       <c r="B20" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C20" s="12">
-        <f>LbWk*Weeks*(1+Growth)^(5-1)</f>
+        <f>LbWk*Weeks*(1+Growth)^(4-1)</f>
         <v/>
       </c>
       <c r="D20" s="12">
@@ -6577,247 +6586,272 @@
         <v/>
       </c>
     </row>
-    <row r="22">
-      <c r="B22" s="47" t="inlineStr">
+    <row r="21">
+      <c r="B21" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="C21" s="12">
+        <f>LbWk*Weeks*(1+Growth)^(5-1)</f>
+        <v/>
+      </c>
+      <c r="D21" s="12">
+        <f>C21/3</f>
+        <v/>
+      </c>
+      <c r="E21" s="12">
+        <f>ROUND(D21/DrumLb/PCIbatch,0)</f>
+        <v/>
+      </c>
+      <c r="F21" s="15">
+        <f>D21*(PCIq-SNPlb)</f>
+        <v/>
+      </c>
+      <c r="G21" s="15">
+        <f>G20+F21</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="47" t="inlineStr">
         <is>
           <t>Break-even — outage cost that justifies the premium</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="30" customHeight="1">
-      <c r="B23" s="3" t="inlineStr">
+    <row r="24" ht="30" customHeight="1">
+      <c r="B24" s="3" t="inlineStr">
         <is>
           <t>Premium (Y1)</t>
         </is>
       </c>
-      <c r="C23" s="3" t="inlineStr">
+      <c r="C24" s="3" t="inlineStr">
         <is>
           <t>p = 2%</t>
         </is>
       </c>
-      <c r="D23" s="3" t="inlineStr">
+      <c r="D24" s="3" t="inlineStr">
         <is>
           <t>p = 5%</t>
         </is>
       </c>
-      <c r="E23" s="3" t="inlineStr">
+      <c r="E24" s="3" t="inlineStr">
         <is>
           <t>p = 10%</t>
         </is>
       </c>
-      <c r="F23" s="3" t="inlineStr">
+      <c r="F24" s="3" t="inlineStr">
         <is>
           <t>p = 20%</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="B24" s="15">
+    <row r="25">
+      <c r="B25" s="15">
         <f>H7</f>
         <v/>
       </c>
-      <c r="C24" s="15">
-        <f>B24/0.02</f>
-        <v/>
-      </c>
-      <c r="D24" s="15">
-        <f>B24/0.05</f>
-        <v/>
-      </c>
-      <c r="E24" s="15">
-        <f>B24/0.1</f>
-        <v/>
-      </c>
-      <c r="F24" s="15">
-        <f>B24/0.2</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26">
-      <c r="B26" s="47" t="inlineStr">
+      <c r="C25" s="15">
+        <f>B25/0.02</f>
+        <v/>
+      </c>
+      <c r="D25" s="15">
+        <f>B25/0.05</f>
+        <v/>
+      </c>
+      <c r="E25" s="15">
+        <f>B25/0.1</f>
+        <v/>
+      </c>
+      <c r="F25" s="15">
+        <f>B25/0.2</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="47" t="inlineStr">
         <is>
           <t>Block-rotation logistics of a 5-drum batch (shelf life 18 days)</t>
         </is>
       </c>
-    </row>
-    <row r="27">
-      <c r="B27" s="17" t="inlineStr">
-        <is>
-          <t>Batch size (lb)</t>
-        </is>
-      </c>
-      <c r="C27" s="12">
-        <f>PCIbatch*DrumLb</f>
-        <v/>
-      </c>
-      <c r="D27" s="2" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="B28" s="17" t="inlineStr">
         <is>
-          <t>Days of FULL demand in one batch</t>
-        </is>
-      </c>
-      <c r="C28" s="48">
-        <f>B27/(LbWk/7)</f>
-        <v/>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>12.1 days — must be consumed within the shelf life -&gt; use at full rate on receipt</t>
-        </is>
-      </c>
+          <t>Batch size (lb)</t>
+        </is>
+      </c>
+      <c r="C28" s="12">
+        <f>PCIbatch*DrumLb</f>
+        <v/>
+      </c>
+      <c r="D28" s="2" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="B29" s="17" t="inlineStr">
         <is>
-          <t>Cycle length at 1/3 share (weeks)</t>
+          <t>Days of FULL demand in one batch</t>
         </is>
       </c>
       <c r="C29" s="48">
-        <f>B27/(LbWk/3)</f>
+        <f>B28/(LbWk/7)</f>
         <v/>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>One PCI batch every ~5 weeks (Year 1: 10 batches; ~15 by Year 5)</t>
+          <t>12.1 days — must be consumed within the shelf life -&gt; use at full rate on receipt</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="B30" s="17" t="inlineStr">
         <is>
-          <t>Weeks on SNP material per cycle</t>
+          <t>Cycle length at 1/3 share (weeks)</t>
         </is>
       </c>
       <c r="C30" s="48">
-        <f>B29-B27/LbWk</f>
+        <f>B28/(LbWk/3)</f>
         <v/>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Cadence is a choice: (i) block rotation = a ~12-day pause in SNP orders per cycle; (ii) SNP keeps ~2 drums/wk and we hold ~3 drums of rolling stock (peak ~8 drums, strict first-in-first-out) — the shelf-life study decides</t>
+          <t>One PCI batch every ~5 weeks (Year 1: 10 batches; ~15 by Year 5)</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="B31" s="17" t="inlineStr">
         <is>
-          <t>Age of PCI drums on receipt (days: cook, release, transit) — INPUT</t>
-        </is>
-      </c>
-      <c r="C31" s="63" t="n">
-        <v>4</v>
+          <t>Weeks on SNP material per cycle</t>
+        </is>
+      </c>
+      <c r="C31" s="48">
+        <f>B30-B28/LbWk</f>
+        <v/>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>Assumption: the 18-day clock starts at manufacture. Confirm PCI lead time and transit St. Louis -&gt; site</t>
+          <t>Cadence is a choice: (i) block rotation = a ~12-day pause in SNP orders per cycle; (ii) SNP keeps ~2 drums/wk and we hold ~3 drums of rolling stock (peak ~8 drums, strict first-in-first-out) — the shelf-life study decides</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="B32" s="17" t="inlineStr">
         <is>
-          <t>Usable days on receipt (18-day life)</t>
-        </is>
-      </c>
-      <c r="C32" s="48">
-        <f>18-B31</f>
-        <v/>
-      </c>
-      <c r="D32" s="2" t="inlineStr"/>
+          <t>Age of PCI drums on receipt (days: cook, release, transit) — INPUT</t>
+        </is>
+      </c>
+      <c r="C32" s="63" t="n">
+        <v>4</v>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>Assumption: the 18-day clock starts at manufacture. Confirm PCI lead time and transit St. Louis -&gt; site</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="B33" s="17" t="inlineStr">
         <is>
-          <t>Slack in block rotation (days)</t>
+          <t>Usable days on receipt (18-day life)</t>
         </is>
       </c>
       <c r="C33" s="48">
-        <f>B32-B28</f>
-        <v/>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>~1–2 days: block rotation has almost no margin at 18 days; a validated 21-day life gives real margin</t>
-        </is>
-      </c>
+        <f>18-B32</f>
+        <v/>
+      </c>
+      <c r="D33" s="2" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="B34" s="17" t="inlineStr">
         <is>
-          <t>Days to consume a batch at 2/3 rate</t>
+          <t>Slack in block rotation (days)</t>
         </is>
       </c>
       <c r="C34" s="48">
-        <f>B27/(LbWk*2/3/7)</f>
+        <f>B33-B29</f>
         <v/>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>18.2 days — needs a validated life longer than 18.2 days plus the age on receipt</t>
+          <t>~1–2 days: block rotation has almost no margin at 18 days; a validated 21-day life gives real margin</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="B35" s="17" t="inlineStr">
         <is>
-          <t>Days to consume a batch at an exact 1/3 rate</t>
+          <t>Days to consume a batch at 2/3 rate</t>
         </is>
       </c>
       <c r="C35" s="48">
-        <f>B27/(LbWk/3/7)</f>
+        <f>B28/(LbWk*2/3/7)</f>
         <v/>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>36.3 days — a true one-third blend needs a ~40-day validated life</t>
+          <t>18.2 days — needs a validated life longer than 18.2 days plus the age on receipt</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="B36" s="17" t="inlineStr">
         <is>
-          <t>Minimum PCI share of rate under a 30-day life</t>
-        </is>
-      </c>
-      <c r="C36" s="24">
-        <f>B27/((30-B31)*LbWk/7)</f>
+          <t>Days to consume a batch at an exact 1/3 rate</t>
+        </is>
+      </c>
+      <c r="C36" s="48">
+        <f>B28/(LbWk/3/7)</f>
         <v/>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>~47% at 4 days' age: even a 30-day life does not allow a one-third blend</t>
+          <t>36.3 days — a true one-third blend needs a ~40-day validated life</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="B37" s="17" t="inlineStr">
         <is>
-          <t>One qualification batch — cost</t>
-        </is>
-      </c>
-      <c r="C37" s="15">
-        <f>B27*PCIq</f>
+          <t>Minimum PCI share of rate under a 30-day life</t>
+        </is>
+      </c>
+      <c r="C37" s="24">
+        <f>B28/((30-B32)*LbWk/7)</f>
         <v/>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>A single production-scale batch (Option B-plus); $7.9k gross</t>
+          <t>~47% at 4 days' age: even a 30-day life does not allow a one-third blend</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="B38" s="17" t="inlineStr">
         <is>
+          <t>One qualification batch — cost</t>
+        </is>
+      </c>
+      <c r="C38" s="15">
+        <f>B28*PCIq</f>
+        <v/>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>A single production-scale batch (Option B-plus); $7.9k gross</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" s="17" t="inlineStr">
+        <is>
           <t>One qualification batch — premium over SNP</t>
         </is>
       </c>
-      <c r="C38" s="15">
-        <f>B27*(PCIq-SNPlb)</f>
-        <v/>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="C39" s="15">
+        <f>B28*(PCIq-SNPlb)</f>
+        <v/>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
         <is>
           <t>3.3% of annual volume (2,250 of 67,600 lb); one ~12-day pause in SNP orders</t>
         </is>

--- a/PVA second supplier initiative/PVA_Second_Supplier_Leadership_Model.xlsx
+++ b/PVA second supplier initiative/PVA_Second_Supplier_Leadership_Model.xlsx
@@ -1842,7 +1842,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:G18"/>
+  <dimension ref="B2:G19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="2" max="2"/>
@@ -2022,77 +2022,77 @@
     <row r="10">
       <c r="B10" s="35" t="inlineStr">
         <is>
+          <t>APV Engineered Coatings (Akron, OH) — no quote</t>
+        </is>
+      </c>
+      <c r="C10" s="36" t="n">
+        <v>3</v>
+      </c>
+      <c r="D10" s="37" t="inlineStr">
+        <is>
+          <t>On our call they considered $1.50/lb too cheap for our volume; we estimate at least $3.00/lb — NEVER CONFIRMED. Heat capability confirmed.</t>
+        </is>
+      </c>
+      <c r="E10" s="37" t="inlineStr">
+        <is>
+          <t>ESTIMATE</t>
+        </is>
+      </c>
+      <c r="F10" s="37" t="inlineStr">
+        <is>
+          <t>No quote received; reserve</t>
+        </is>
+      </c>
+      <c r="G10" s="37" t="inlineStr">
+        <is>
+          <t>APV call (2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="35" t="inlineStr">
+        <is>
           <t>Brenntag (distributor) — trial blends, Nov 2025 onward</t>
         </is>
       </c>
-      <c r="C10" s="36" t="inlineStr">
+      <c r="C11" s="36" t="inlineStr">
         <is>
           <t>pending</t>
         </is>
       </c>
-      <c r="D10" s="37" t="inlineStr">
+      <c r="D11" s="37" t="inlineStr">
         <is>
           <t>Tried our formula (125 grade and the requested grade): viscosity above range, unreadable on their viscometer. They stalled; no quote was ever received. Mar 2026: sent us a 125-grade resin sample instead.</t>
         </is>
       </c>
-      <c r="E10" s="37" t="inlineStr">
+      <c r="E11" s="37" t="inlineStr">
         <is>
           <t>NO QUOTE</t>
         </is>
       </c>
-      <c r="F10" s="37" t="inlineStr">
+      <c r="F11" s="37" t="inlineStr">
         <is>
           <t>Never met viscosity; no quote</t>
         </is>
       </c>
-      <c r="G10" s="37" t="inlineStr">
+      <c r="G11" s="37" t="inlineStr">
         <is>
           <t>Sam (Brenntag) emails</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="B11" s="60" t="inlineStr">
-        <is>
-          <t>Market — COMPETITIVE quantity (drum scale, 30–55 gal)</t>
-        </is>
-      </c>
-      <c r="C11" s="61" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="D11" s="62" t="inlineStr">
-        <is>
-          <t>Inferred from comparable pre-mixed PVA solutions sold today; range 2.20-5.03; n=7</t>
-        </is>
-      </c>
-      <c r="E11" s="62" t="inlineStr">
-        <is>
-          <t>MARKET STUDY</t>
-        </is>
-      </c>
-      <c r="F11" s="62" t="inlineStr">
-        <is>
-          <t>Reference — see Market Study tab</t>
-        </is>
-      </c>
-      <c r="G11" s="62" t="inlineStr">
-        <is>
-          <t>Verified market study 2026-09-28</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="B12" s="60" t="inlineStr">
         <is>
-          <t>Market — LOW quantity (pints to 5-gal pails)</t>
+          <t>Market — COMPETITIVE quantity (drum scale, 30–55 gal)</t>
         </is>
       </c>
       <c r="C12" s="61" t="n">
-        <v>4.55</v>
+        <v>2.32</v>
       </c>
       <c r="D12" s="62" t="inlineStr">
         <is>
-          <t>Retail/lab packs; range 3.19-5.87; n=32</t>
+          <t>Inferred from comparable pre-mixed PVA solutions sold today; range 2.20-5.03; n=7</t>
         </is>
       </c>
       <c r="E12" s="62" t="inlineStr">
@@ -2114,160 +2114,190 @@
     <row r="13">
       <c r="B13" s="60" t="inlineStr">
         <is>
+          <t>Market — LOW quantity (pints to 5-gal pails)</t>
+        </is>
+      </c>
+      <c r="C13" s="61" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="D13" s="62" t="inlineStr">
+        <is>
+          <t>Retail/lab packs; range 3.19-5.87; n=32</t>
+        </is>
+      </c>
+      <c r="E13" s="62" t="inlineStr">
+        <is>
+          <t>MARKET STUDY</t>
+        </is>
+      </c>
+      <c r="F13" s="62" t="inlineStr">
+        <is>
+          <t>Reference — see Market Study tab</t>
+        </is>
+      </c>
+      <c r="G13" s="62" t="inlineStr">
+        <is>
+          <t>Verified market study 2026-09-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="60" t="inlineStr">
+        <is>
           <t>Market — HIGH quantity (totes / bulk / tonnage)</t>
         </is>
       </c>
-      <c r="C13" s="61" t="n">
+      <c r="C14" s="61" t="n">
         <v>1.01</v>
       </c>
-      <c r="D13" s="62" t="inlineStr">
+      <c r="D14" s="62" t="inlineStr">
         <is>
           <t>Bulk and contract pricing; range 0.28-1.04; n=5. Quality/regulatory context differs.</t>
         </is>
       </c>
-      <c r="E13" s="62" t="inlineStr">
+      <c r="E14" s="62" t="inlineStr">
         <is>
           <t>MARKET STUDY</t>
         </is>
       </c>
-      <c r="F13" s="62" t="inlineStr">
+      <c r="F14" s="62" t="inlineStr">
         <is>
           <t>Reference — see Market Study tab</t>
         </is>
       </c>
-      <c r="G13" s="62" t="inlineStr">
+      <c r="G14" s="62" t="inlineStr">
         <is>
           <t>Verified market study 2026-09-28</t>
         </is>
       </c>
-    </row>
-    <row r="14">
-      <c r="B14" s="35" t="inlineStr">
-        <is>
-          <t>— Superseded / historical references (kept for the record) —</t>
-        </is>
-      </c>
-      <c r="C14" s="36" t="inlineStr"/>
-      <c r="D14" s="37" t="inlineStr"/>
-      <c r="E14" s="37" t="inlineStr"/>
-      <c r="F14" s="37" t="inlineStr"/>
-      <c r="G14" s="37" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="B15" s="35" t="inlineStr">
         <is>
-          <t>Triangulated market LOW / BASE / HIGH (Sept)</t>
-        </is>
-      </c>
-      <c r="C15" s="36" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="D15" s="37" t="inlineStr">
-        <is>
-          <t>$0.85 / $1.40 / $2.55 — resin floor + labor build-up + retail ceiling</t>
-        </is>
-      </c>
-      <c r="E15" s="37" t="inlineStr">
-        <is>
-          <t>TRIANGULATED</t>
-        </is>
-      </c>
-      <c r="F15" s="37" t="inlineStr">
-        <is>
-          <t>SUPERSEDED by market study</t>
-        </is>
-      </c>
-      <c r="G15" s="37" t="inlineStr">
-        <is>
-          <t>Market Research tab (cost-scenarios workbook)</t>
-        </is>
-      </c>
+          <t>— Superseded / historical references (kept for the record) —</t>
+        </is>
+      </c>
+      <c r="C15" s="36" t="inlineStr"/>
+      <c r="D15" s="37" t="inlineStr"/>
+      <c r="E15" s="37" t="inlineStr"/>
+      <c r="F15" s="37" t="inlineStr"/>
+      <c r="G15" s="37" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="B16" s="35" t="inlineStr">
         <is>
+          <t>Triangulated market LOW / BASE / HIGH (Sept)</t>
+        </is>
+      </c>
+      <c r="C16" s="36" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="D16" s="37" t="inlineStr">
+        <is>
+          <t>$0.85 / $1.40 / $2.55 — resin floor + labor build-up + retail ceiling</t>
+        </is>
+      </c>
+      <c r="E16" s="37" t="inlineStr">
+        <is>
+          <t>TRIANGULATED</t>
+        </is>
+      </c>
+      <c r="F16" s="37" t="inlineStr">
+        <is>
+          <t>SUPERSEDED by market study</t>
+        </is>
+      </c>
+      <c r="G16" s="37" t="inlineStr">
+        <is>
+          <t>Market Research tab (cost-scenarios workbook)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="35" t="inlineStr">
+        <is>
           <t>Material floor</t>
         </is>
       </c>
-      <c r="C16" s="36" t="n">
+      <c r="C17" s="36" t="n">
         <v>0.18</v>
       </c>
-      <c r="D16" s="37" t="inlineStr">
+      <c r="D17" s="37" t="inlineStr">
         <is>
           <t>PVA resin $1.26–1.60/lb x 11% solids = $0.14–0.18 (upper bound plotted)</t>
         </is>
       </c>
-      <c r="E16" s="37" t="inlineStr">
+      <c r="E17" s="37" t="inlineStr">
         <is>
           <t>DERIVED</t>
         </is>
       </c>
-      <c r="F16" s="37" t="inlineStr">
+      <c r="F17" s="37" t="inlineStr">
         <is>
           <t>Reference only</t>
         </is>
       </c>
-      <c r="G16" s="37" t="inlineStr">
+      <c r="G17" s="37" t="inlineStr">
         <is>
           <t>ChemAnalyst / IMARC 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="B17" s="38" t="inlineStr">
-        <is>
-          <t>July 2026 assumption (key performance indicator (KPI) review deck)</t>
-        </is>
-      </c>
-      <c r="C17" s="39" t="n">
-        <v>1.125</v>
-      </c>
-      <c r="D17" s="40" t="inlineStr">
-        <is>
-          <t>'$1.00–1.25/lb, ~35% share, ~$6–12k/yr insurance'</t>
-        </is>
-      </c>
-      <c r="E17" s="40" t="inlineStr">
-        <is>
-          <t>ASSUMPTION</t>
-        </is>
-      </c>
-      <c r="F17" s="40" t="inlineStr">
-        <is>
-          <t>SUPERSEDED by PCI quote</t>
-        </is>
-      </c>
-      <c r="G17" s="40" t="inlineStr">
-        <is>
-          <t>KPI review deck 2026-07-09</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="B18" s="38" t="inlineStr">
         <is>
+          <t>July 2026 assumption (key performance indicator (KPI) review deck)</t>
+        </is>
+      </c>
+      <c r="C18" s="39" t="n">
+        <v>1.125</v>
+      </c>
+      <c r="D18" s="40" t="inlineStr">
+        <is>
+          <t>'$1.00–1.25/lb, ~35% share, ~$6–12k/yr insurance'</t>
+        </is>
+      </c>
+      <c r="E18" s="40" t="inlineStr">
+        <is>
+          <t>ASSUMPTION</t>
+        </is>
+      </c>
+      <c r="F18" s="40" t="inlineStr">
+        <is>
+          <t>SUPERSEDED by PCI quote</t>
+        </is>
+      </c>
+      <c r="G18" s="40" t="inlineStr">
+        <is>
+          <t>KPI review deck 2026-07-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="38" t="inlineStr">
+        <is>
           <t>Pre-quote forecast (this deck, Sept)</t>
         </is>
       </c>
-      <c r="C18" s="39" t="n">
+      <c r="C19" s="39" t="n">
         <v>3.75</v>
       </c>
-      <c r="D18" s="40" t="inlineStr">
+      <c r="D19" s="40" t="inlineStr">
         <is>
           <t>$2.50 low / $3.75 mid / $5.00 high</t>
         </is>
       </c>
-      <c r="E18" s="40" t="inlineStr">
+      <c r="E19" s="40" t="inlineStr">
         <is>
           <t>ASSUMPTION</t>
         </is>
       </c>
-      <c r="F18" s="40" t="inlineStr">
+      <c r="F19" s="40" t="inlineStr">
         <is>
           <t>SUPERSEDED by PCI quote (quote = mid)</t>
         </is>
       </c>
-      <c r="G18" s="40" t="inlineStr">
+      <c r="G19" s="40" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -6932,12 +6962,12 @@
       </c>
       <c r="C7" s="34" t="inlineStr">
         <is>
-          <t>ROOT CAUSE FOUND</t>
+          <t>ADJUSTED IN TEST</t>
         </is>
       </c>
       <c r="D7" s="34" t="inlineStr">
         <is>
-          <t>First sample 2,420 cP vs ~1,000 target; dilution to 10.8% solids -&gt; 1,590 cP; cause = elevated solids from water loss during processing; fix = water adjustment at end of mix</t>
+          <t>First sample 2,420 cP vs ~1,000 target; dilution to 10.8% solids -&gt; 1,590 cP; brought on target within the test by adjusting solids/water at end of mix (part of the test, not a separate root-cause finding)</t>
         </is>
       </c>
     </row>

--- a/PVA second supplier initiative/PVA_Second_Supplier_Leadership_Model.xlsx
+++ b/PVA second supplier initiative/PVA_Second_Supplier_Leadership_Model.xlsx
@@ -11,13 +11,14 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Inputs" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Supplier Quotes" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Market Study" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PCI Quote Scenarios" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PCI Experiment" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5-Year" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sensitivity" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SNP Re-price" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Break-even" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Options" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Price Curve" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PCI Quote Scenarios" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PCI Experiment" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5-Year" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sensitivity" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SNP Re-price" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Break-even" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Options" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames>
     <definedName name="DrumLb">Inputs!$C$6</definedName>
@@ -49,13 +50,14 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="6">
+  <numFmts count="7">
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
     <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0"/>
     <numFmt numFmtId="167" formatCode="0.0&quot;x&quot;"/>
     <numFmt numFmtId="168" formatCode="0.00&quot;x&quot;"/>
     <numFmt numFmtId="169" formatCode="0.0"/>
+    <numFmt numFmtId="170" formatCode="0.000"/>
   </numFmts>
   <fonts count="10">
     <font>
@@ -187,7 +189,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="68">
+  <cellXfs count="71">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -296,6 +298,11 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1095,6 +1102,199 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="B2:G10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="2">
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>If SNP Inc. raises price on the volume it keeps (Year 1, PCI quote $3.50, 50 drums to PCI)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Losing a third of our volume may cost SNP its batch efficiency. A surcharge on the retained ~2/3 compounds the premium.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1">
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>SNP surcharge</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>SNP $/lb</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>SNP annual (retained)</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>PCI annual</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>Premium vs today</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="21">
+        <f>SNPlb*(1+B6)</f>
+        <v/>
+      </c>
+      <c r="D6" s="15">
+        <f>LbWk*Weeks*(1-EffShare)*C6</f>
+        <v/>
+      </c>
+      <c r="E6" s="15">
+        <f>LbWk*Weeks*EffShare*PCImid</f>
+        <v/>
+      </c>
+      <c r="F6" s="15">
+        <f>D6+E6</f>
+        <v/>
+      </c>
+      <c r="G6" s="15">
+        <f>F6-LbWk*Weeks*SNPlb</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="24" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="C7" s="21">
+        <f>SNPlb*(1+B7)</f>
+        <v/>
+      </c>
+      <c r="D7" s="15">
+        <f>LbWk*Weeks*(1-EffShare)*C7</f>
+        <v/>
+      </c>
+      <c r="E7" s="15">
+        <f>LbWk*Weeks*EffShare*PCImid</f>
+        <v/>
+      </c>
+      <c r="F7" s="15">
+        <f>D7+E7</f>
+        <v/>
+      </c>
+      <c r="G7" s="15">
+        <f>F7-LbWk*Weeks*SNPlb</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="24" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C8" s="21">
+        <f>SNPlb*(1+B8)</f>
+        <v/>
+      </c>
+      <c r="D8" s="15">
+        <f>LbWk*Weeks*(1-EffShare)*C8</f>
+        <v/>
+      </c>
+      <c r="E8" s="15">
+        <f>LbWk*Weeks*EffShare*PCImid</f>
+        <v/>
+      </c>
+      <c r="F8" s="15">
+        <f>D8+E8</f>
+        <v/>
+      </c>
+      <c r="G8" s="15">
+        <f>F8-LbWk*Weeks*SNPlb</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="24" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="C9" s="21">
+        <f>SNPlb*(1+B9)</f>
+        <v/>
+      </c>
+      <c r="D9" s="15">
+        <f>LbWk*Weeks*(1-EffShare)*C9</f>
+        <v/>
+      </c>
+      <c r="E9" s="15">
+        <f>LbWk*Weeks*EffShare*PCImid</f>
+        <v/>
+      </c>
+      <c r="F9" s="15">
+        <f>D9+E9</f>
+        <v/>
+      </c>
+      <c r="G9" s="15">
+        <f>F9-LbWk*Weeks*SNPlb</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="24" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="C10" s="21">
+        <f>SNPlb*(1+B10)</f>
+        <v/>
+      </c>
+      <c r="D10" s="15">
+        <f>LbWk*Weeks*(1-EffShare)*C10</f>
+        <v/>
+      </c>
+      <c r="E10" s="15">
+        <f>LbWk*Weeks*EffShare*PCImid</f>
+        <v/>
+      </c>
+      <c r="F10" s="15">
+        <f>D10+E10</f>
+        <v/>
+      </c>
+      <c r="G10" s="15">
+        <f>F10-LbWk*Weeks*SNPlb</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="B2:G13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -1267,7 +1467,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6136,6 +6336,310 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="B2:G20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="2">
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>Price per lb vs. quantity per order — market trend, band and where each supplier sits</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Fit: log-log regression of verified market points (US packs 2 lb–20 gal, ≤$12/lb, plus ton-scale offers at 2,205 lb). Band = 10th–90th percentile of points around the trend; beyond 20 gal the top follows vendors' volume ladders flattening (~8%/doubling from $2.32 at 20 gal); floor = SNP's $0.75 (no US-delivered lot seen cheaper).</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="17" t="inlineStr">
+        <is>
+          <t>Trend coefficient A ($/lb at 1 lb)</t>
+        </is>
+      </c>
+      <c r="C5" s="14" t="n">
+        <v>8.301220449729895</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="17" t="inlineStr">
+        <is>
+          <t>Trend exponent b</t>
+        </is>
+      </c>
+      <c r="C6" s="68" t="n">
+        <v>-0.2949856235683102</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="17" t="inlineStr">
+        <is>
+          <t>Price change per doubling of lot</t>
+        </is>
+      </c>
+      <c r="C7" s="13" t="n">
+        <v>-0.1849195453748944</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="17" t="inlineStr">
+        <is>
+          <t>Band: 10th-percentile ratio to trend</t>
+        </is>
+      </c>
+      <c r="C8" s="14" t="n">
+        <v>0.603671955514413</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="17" t="inlineStr">
+        <is>
+          <t>Band: 90th-percentile ratio to trend</t>
+        </is>
+      </c>
+      <c r="C9" s="14" t="n">
+        <v>1.711030467025052</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="17" t="inlineStr">
+        <is>
+          <t>Points used in fit</t>
+        </is>
+      </c>
+      <c r="C10" s="69" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="70" t="inlineStr">
+        <is>
+          <t>Quantity per order</t>
+        </is>
+      </c>
+      <c r="C12" s="70" t="inlineStr">
+        <is>
+          <t>lb</t>
+        </is>
+      </c>
+      <c r="D12" s="70" t="inlineStr">
+        <is>
+          <t>Trend $/lb</t>
+        </is>
+      </c>
+      <c r="E12" s="70" t="inlineStr">
+        <is>
+          <t>Band low $/lb</t>
+        </is>
+      </c>
+      <c r="F12" s="70" t="inlineStr">
+        <is>
+          <t>Band high $/lb</t>
+        </is>
+      </c>
+      <c r="G12" s="70" t="inlineStr">
+        <is>
+          <t>Real quote / point</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="11" t="inlineStr">
+        <is>
+          <t>1 gal</t>
+        </is>
+      </c>
+      <c r="C13" s="51" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="D13" s="67" t="n">
+        <v>4.415467839760789</v>
+      </c>
+      <c r="E13" s="67" t="n">
+        <v>2.665494105339397</v>
+      </c>
+      <c r="F13" s="67" t="n">
+        <v>7.555</v>
+      </c>
+      <c r="G13" s="52" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="B14" s="11" t="inlineStr">
+        <is>
+          <t>5 gal</t>
+        </is>
+      </c>
+      <c r="C14" s="51" t="n">
+        <v>42.5</v>
+      </c>
+      <c r="D14" s="67" t="n">
+        <v>2.746569691723967</v>
+      </c>
+      <c r="E14" s="67" t="n">
+        <v>1.658027096759626</v>
+      </c>
+      <c r="F14" s="67" t="n">
+        <v>4.699464422347312</v>
+      </c>
+      <c r="G14" s="52" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="B15" s="11" t="inlineStr">
+        <is>
+          <t>20 gal (largest US lot)</t>
+        </is>
+      </c>
+      <c r="C15" s="51" t="n">
+        <v>170</v>
+      </c>
+      <c r="D15" s="67" t="n">
+        <v>1.824700459266596</v>
+      </c>
+      <c r="E15" s="67" t="n">
+        <v>1.101520494473514</v>
+      </c>
+      <c r="F15" s="67" t="n">
+        <v>3.12211807899975</v>
+      </c>
+      <c r="G15" s="52" t="inlineStr">
+        <is>
+          <t>$2.32 US Composites</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="11" t="inlineStr">
+        <is>
+          <t>1 drum</t>
+        </is>
+      </c>
+      <c r="C16" s="51" t="n">
+        <v>450</v>
+      </c>
+      <c r="D16" s="67" t="n">
+        <v>1.369248895991172</v>
+      </c>
+      <c r="E16" s="67" t="n">
+        <v>0.826577158628942</v>
+      </c>
+      <c r="F16" s="67" t="n">
+        <v>3.530934857171929</v>
+      </c>
+      <c r="G16" s="52" t="inlineStr">
+        <is>
+          <t>PCI $6.00 below batch; APV ≥$3 est.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="11" t="inlineStr">
+        <is>
+          <t>SNP lot (~3 drums/week)</t>
+        </is>
+      </c>
+      <c r="C17" s="51" t="n">
+        <v>1350</v>
+      </c>
+      <c r="D17" s="67" t="n">
+        <v>0.9902354927869617</v>
+      </c>
+      <c r="E17" s="67" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="F17" s="67" t="n">
+        <v>3.093818054556199</v>
+      </c>
+      <c r="G17" s="52" t="inlineStr">
+        <is>
+          <t>SNP $0.75 delivered</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="11" t="inlineStr">
+        <is>
+          <t>5-drum batch</t>
+        </is>
+      </c>
+      <c r="C18" s="51" t="n">
+        <v>2250</v>
+      </c>
+      <c r="D18" s="67" t="n">
+        <v>0.8517189241626537</v>
+      </c>
+      <c r="E18" s="67" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="F18" s="67" t="n">
+        <v>2.909428201514443</v>
+      </c>
+      <c r="G18" s="52" t="inlineStr">
+        <is>
+          <t>PCI $3.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="11" t="inlineStr">
+        <is>
+          <t>50 drums</t>
+        </is>
+      </c>
+      <c r="C19" s="51" t="n">
+        <v>22500</v>
+      </c>
+      <c r="D19" s="67" t="n">
+        <v>0.4318278751553078</v>
+      </c>
+      <c r="E19" s="67" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="F19" s="67" t="n">
+        <v>2.205532239477101</v>
+      </c>
+      <c r="G19" s="52" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="B20" s="11" t="inlineStr">
+        <is>
+          <t>150 drums (a year)</t>
+        </is>
+      </c>
+      <c r="C20" s="51" t="n">
+        <v>67600</v>
+      </c>
+      <c r="D20" s="67" t="n">
+        <v>0.3121598974418646</v>
+      </c>
+      <c r="E20" s="67" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="F20" s="67" t="n">
+        <v>1.9321513147772</v>
+      </c>
+      <c r="G20" s="52" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="B2:I39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -6892,7 +7396,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7129,7 +7633,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7532,7 +8036,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7905,197 +8409,4 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="B2:G10"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-  </cols>
-  <sheetData>
-    <row r="2">
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t>If SNP Inc. raises price on the volume it keeps (Year 1, PCI quote $3.50, 50 drums to PCI)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>Losing a third of our volume may cost SNP its batch efficiency. A surcharge on the retained ~2/3 compounds the premium.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="30" customHeight="1">
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>SNP surcharge</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>SNP $/lb</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>SNP annual (retained)</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>PCI annual</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t>Premium vs today</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="B6" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C6" s="21">
-        <f>SNPlb*(1+B6)</f>
-        <v/>
-      </c>
-      <c r="D6" s="15">
-        <f>LbWk*Weeks*(1-EffShare)*C6</f>
-        <v/>
-      </c>
-      <c r="E6" s="15">
-        <f>LbWk*Weeks*EffShare*PCImid</f>
-        <v/>
-      </c>
-      <c r="F6" s="15">
-        <f>D6+E6</f>
-        <v/>
-      </c>
-      <c r="G6" s="15">
-        <f>F6-LbWk*Weeks*SNPlb</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7">
-      <c r="B7" s="24" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="C7" s="21">
-        <f>SNPlb*(1+B7)</f>
-        <v/>
-      </c>
-      <c r="D7" s="15">
-        <f>LbWk*Weeks*(1-EffShare)*C7</f>
-        <v/>
-      </c>
-      <c r="E7" s="15">
-        <f>LbWk*Weeks*EffShare*PCImid</f>
-        <v/>
-      </c>
-      <c r="F7" s="15">
-        <f>D7+E7</f>
-        <v/>
-      </c>
-      <c r="G7" s="15">
-        <f>F7-LbWk*Weeks*SNPlb</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8">
-      <c r="B8" s="24" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="C8" s="21">
-        <f>SNPlb*(1+B8)</f>
-        <v/>
-      </c>
-      <c r="D8" s="15">
-        <f>LbWk*Weeks*(1-EffShare)*C8</f>
-        <v/>
-      </c>
-      <c r="E8" s="15">
-        <f>LbWk*Weeks*EffShare*PCImid</f>
-        <v/>
-      </c>
-      <c r="F8" s="15">
-        <f>D8+E8</f>
-        <v/>
-      </c>
-      <c r="G8" s="15">
-        <f>F8-LbWk*Weeks*SNPlb</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9">
-      <c r="B9" s="24" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="C9" s="21">
-        <f>SNPlb*(1+B9)</f>
-        <v/>
-      </c>
-      <c r="D9" s="15">
-        <f>LbWk*Weeks*(1-EffShare)*C9</f>
-        <v/>
-      </c>
-      <c r="E9" s="15">
-        <f>LbWk*Weeks*EffShare*PCImid</f>
-        <v/>
-      </c>
-      <c r="F9" s="15">
-        <f>D9+E9</f>
-        <v/>
-      </c>
-      <c r="G9" s="15">
-        <f>F9-LbWk*Weeks*SNPlb</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10">
-      <c r="B10" s="24" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="C10" s="21">
-        <f>SNPlb*(1+B10)</f>
-        <v/>
-      </c>
-      <c r="D10" s="15">
-        <f>LbWk*Weeks*(1-EffShare)*C10</f>
-        <v/>
-      </c>
-      <c r="E10" s="15">
-        <f>LbWk*Weeks*EffShare*PCImid</f>
-        <v/>
-      </c>
-      <c r="F10" s="15">
-        <f>D10+E10</f>
-        <v/>
-      </c>
-      <c r="G10" s="15">
-        <f>F10-LbWk*Weeks*SNPlb</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/PVA second supplier initiative/PVA_Second_Supplier_Leadership_Model.xlsx
+++ b/PVA second supplier initiative/PVA_Second_Supplier_Leadership_Model.xlsx
@@ -826,7 +826,7 @@
         </is>
       </c>
       <c r="C13" s="55">
-        <f>B12-B10</f>
+        <f>C12-C10</f>
         <v/>
       </c>
       <c r="D13" s="56" t="inlineStr">
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="C14" s="57">
-        <f>B13/B10</f>
+        <f>C13/C10</f>
         <v/>
       </c>
       <c r="D14" s="52" t="inlineStr">
@@ -906,7 +906,7 @@
         </is>
       </c>
       <c r="C18" s="54">
-        <f>B13/0.10</f>
+        <f>C13/0.10</f>
         <v/>
       </c>
       <c r="D18" s="52" t="inlineStr">
@@ -922,7 +922,7 @@
         </is>
       </c>
       <c r="C19" s="54">
-        <f>B13/0.05</f>
+        <f>C13/0.05</f>
         <v/>
       </c>
       <c r="D19" s="52" t="inlineStr">
@@ -938,7 +938,7 @@
         </is>
       </c>
       <c r="C20" s="54">
-        <f>B13/0.02</f>
+        <f>C13/0.02</f>
         <v/>
       </c>
       <c r="D20" s="52" t="inlineStr">
@@ -1530,7 +1530,7 @@
         </is>
       </c>
       <c r="C7" s="29">
-        <f>B6-LbWk*Weeks*SNPlb</f>
+        <f>C6-LbWk*Weeks*SNPlb</f>
         <v/>
       </c>
       <c r="D7" s="30" t="inlineStr">
@@ -1847,9 +1847,10 @@
         <f>PCIq</f>
         <v/>
       </c>
-      <c r="D16" s="2">
-        <f> the real quote (row 27). Every 'MID' figure in the legacy tabs now uses $3.50.</f>
-        <v/>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Points to the real quote (row 27). Every 'MID' figure in the legacy tabs now uses $3.50.</t>
+        </is>
       </c>
     </row>
     <row r="17">
@@ -7227,7 +7228,7 @@
         </is>
       </c>
       <c r="C29" s="48">
-        <f>B28/(LbWk/7)</f>
+        <f>C28/(LbWk/7)</f>
         <v/>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -7243,7 +7244,7 @@
         </is>
       </c>
       <c r="C30" s="48">
-        <f>B28/(LbWk/3)</f>
+        <f>C28/(LbWk/3)</f>
         <v/>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -7259,7 +7260,7 @@
         </is>
       </c>
       <c r="C31" s="48">
-        <f>B30-B28/LbWk</f>
+        <f>C30-C28/LbWk</f>
         <v/>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -7290,7 +7291,7 @@
         </is>
       </c>
       <c r="C33" s="48">
-        <f>18-B32</f>
+        <f>18-C32</f>
         <v/>
       </c>
       <c r="D33" s="2" t="inlineStr"/>
@@ -7302,7 +7303,7 @@
         </is>
       </c>
       <c r="C34" s="48">
-        <f>B33-B29</f>
+        <f>C33-C29</f>
         <v/>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -7318,7 +7319,7 @@
         </is>
       </c>
       <c r="C35" s="48">
-        <f>B28/(LbWk*2/3/7)</f>
+        <f>C28/(LbWk*2/3/7)</f>
         <v/>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -7334,7 +7335,7 @@
         </is>
       </c>
       <c r="C36" s="48">
-        <f>B28/(LbWk/3/7)</f>
+        <f>C28/(LbWk/3/7)</f>
         <v/>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -7350,7 +7351,7 @@
         </is>
       </c>
       <c r="C37" s="24">
-        <f>B28/((30-B32)*LbWk/7)</f>
+        <f>C28/((30-C32)*LbWk/7)</f>
         <v/>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -7366,7 +7367,7 @@
         </is>
       </c>
       <c r="C38" s="15">
-        <f>B28*PCIq</f>
+        <f>C28*PCIq</f>
         <v/>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -7382,7 +7383,7 @@
         </is>
       </c>
       <c r="C39" s="15">
-        <f>B28*(PCIq-SNPlb)</f>
+        <f>C28*(PCIq-SNPlb)</f>
         <v/>
       </c>
       <c r="D39" s="2" t="inlineStr">

--- a/PVA second supplier initiative/PVA_Second_Supplier_Leadership_Model.xlsx
+++ b/PVA second supplier initiative/PVA_Second_Supplier_Leadership_Model.xlsx
@@ -50,7 +50,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="7">
+  <numFmts count="8">
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
     <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0"/>
@@ -58,6 +58,7 @@
     <numFmt numFmtId="168" formatCode="0.00&quot;x&quot;"/>
     <numFmt numFmtId="169" formatCode="0.0"/>
     <numFmt numFmtId="170" formatCode="0.000"/>
+    <numFmt numFmtId="171" formatCode="&quot;$&quot;0.000"/>
   </numFmts>
   <fonts count="10">
     <font>
@@ -189,7 +190,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="71">
+  <cellXfs count="72">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -303,6 +304,7 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="171" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -668,7 +670,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:D29"/>
+  <dimension ref="B2:D34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="58" customWidth="1" min="2" max="2"/>
@@ -1078,14 +1080,94 @@
     <row r="29">
       <c r="B29" s="11" t="inlineStr">
         <is>
+          <t>Blended $/lb, all our PVA — today</t>
+        </is>
+      </c>
+      <c r="C29" s="71">
+        <f>C10/C6</f>
+        <v/>
+      </c>
+      <c r="D29" s="52" t="inlineStr">
+        <is>
+          <t>Blended-cost slide</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="11" t="inlineStr">
+        <is>
+          <t>Blended $/lb — 1 PCI batch a year</t>
+        </is>
+      </c>
+      <c r="C30" s="71">
+        <f>((C6-PCIbatch*DrumLb)*SNPlb+PCIbatch*DrumLb*PCIq)/C6</f>
+        <v/>
+      </c>
+      <c r="D30" s="52" t="inlineStr">
+        <is>
+          <t>Blended-cost slide</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" s="11" t="inlineStr">
+        <is>
+          <t>Blended $/lb — 2 PCI batches a year</t>
+        </is>
+      </c>
+      <c r="C31" s="71">
+        <f>((C6-2*PCIbatch*DrumLb)*SNPlb+2*PCIbatch*DrumLb*PCIq)/C6</f>
+        <v/>
+      </c>
+      <c r="D31" s="52" t="inlineStr">
+        <is>
+          <t>Blended-cost slide</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="11" t="inlineStr">
+        <is>
+          <t>Blended $/lb — 3 PCI batches a year</t>
+        </is>
+      </c>
+      <c r="C32" s="71">
+        <f>((C6-3*PCIbatch*DrumLb)*SNPlb+3*PCIbatch*DrumLb*PCIq)/C6</f>
+        <v/>
+      </c>
+      <c r="D32" s="52" t="inlineStr">
+        <is>
+          <t>Blended-cost slide</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" s="11" t="inlineStr">
+        <is>
+          <t>Blended $/lb — Option 1 (one-third from PCI)</t>
+        </is>
+      </c>
+      <c r="C33" s="71">
+        <f>C12/C6</f>
+        <v/>
+      </c>
+      <c r="D33" s="52" t="inlineStr">
+        <is>
+          <t>Blended-cost slide</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" s="11" t="inlineStr">
+        <is>
           <t>Option 3 — share of volume at 1 / 2 batches</t>
         </is>
       </c>
-      <c r="C29" s="52">
+      <c r="C34" s="52">
         <f>TEXT(PCIbatch*DrumLb/(LbWk*Weeks),"0.0%")&amp;" / "&amp;TEXT(2*PCIbatch*DrumLb/(LbWk*Weeks),"0.0%")</f>
         <v/>
       </c>
-      <c r="D29" s="52" t="inlineStr">
+      <c r="D34" s="52" t="inlineStr">
         <is>
           <t>Options slide</t>
         </is>
